--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,12 +672,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>✅ 验收通过（并入 UPG-02 合并单验收）｜ 设计师/方案设计/UPG-04_Obsidian工具包_方案设计.md</t>
+          <t>✅ 验收通过（并入 UPG-02 合并单验收）｜ 设计师/方案设计/UPG-04_Obsidian工具包_方案设计.md→ 已合 main@</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>合 main@2026-08-29（merge 8a205d6 已推 origin）**；原</t>
+          <t>已合 main@2026-08-29（merge 8a205d6 已推 origin；随 UPG-02 合并单｜obsidian.* 工具面</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📌 **重排 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造）**｜本卡=**43a App 侧 WebMCP Hub</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>✅**规范文档已交付 @2026-08-29**（`设计师/方案设计/MOV设计规范_v1.md`，待用户过目）</t>
+          <t>❌ **已作废 @2026-09-02**（用户拍板：设计规范 v1 文档已删｜由 v2/v2.1+UPG-50 外观组件体系接替；本卡销账</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 验收通过（用户确认「已实现」）@2026-09-02（feat/sidebar-brand 7a6dff6+0fdfe87：品牌区 lo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>合 main</t>
+          <t>**分支未合 main（162 分叉）｜待设计师合 main**）</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>**待设计师合 main → 审验员**</t>
+          <t>**已合 main @2026-08-31 → 审验员**（approval 体系随 UPG-58/62/63 合入；ApprovalSer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3158,12 +3158,13 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>📌 施工中（P0·3~5 工作日；CT-13/14 契约后补不阻塞）  **v3 定稿 @2026-09-01（二轮大神 9.1/10 可</t>
+          <t>📌 施工中（P0·3~5 工作日；CT-13/14 契约后补不阻塞）+ → 方案 v3 定稿 @2026-09-01（二轮大神 9.1/1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ R1 复验带缺陷通过 @2026-09-01（feat/upg68 35b0008｜HIGH/M1/M2 三缺口 security_re</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3177,6 +3178,53 @@
         </is>
       </c>
       <c r="I59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UPG-69</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>WebMCP 站点试点（mow.kim 工单站「站点=业务工具」第一站）</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>📌 新立 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造｜站点侧并行试点）｜待派单可认领</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>**分支未合 main（162 分叉）｜待设计师合 main**）</t>
+          <t>**分支未合 main（162 分叉）｜已合 main @2026-09-01（随批合入｜本卡闭合）→ 审验员复核8-29「侧边栏的左上角替</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>合 main】员：A3-1 三类正反例复跑（含判否 journal 锚）+A3-2 降级回归+mode 贯通源码审查+A3-4 管道端到端（</t>
+          <t>✅ **已合 main@2026-09-01**（A-3 Judge 扩面｜AcceptanceJudge/M-JudgeModes/Age</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **43a 已认领 @2026-09-02**：程序员（acceptance 型）认领 **43a App 侧 WebMCP Hub 框</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师\派单\UPG-43a_App内浏览器WebMCP_Hub框架_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>裁决]；用户确认已实现 @2026-09-02）→</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>**分支未合 main（162 分叉）｜已合 main @2026-09-01（随批合入｜本卡闭合）→ 审验员复核8-29「侧边栏的左上角替</t>
+          <t>**分支未合 main（162 分叉）｜已合 main@2026-09-02（feat/sidebar-brand 7a6dff6/0fdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>✅ **43a 已认领 @2026-09-02**：程序员（acceptance 型）认领 **43a App 侧 WebMCP Hub 框</t>
+          <t>✅ **C 完成 @2026-09-02**（详状态锚）：H1 契约落盘（UPG-69 共引）/H2 web.* 工具面经 upg27 热挂</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>✅ **验收员 1B 复验 带缺陷通过 @2026-09-01**（ACCEPTANCE_LOG §P21：全量 604/1sentinel</t>
+          <t>✅ **1C 复验 带缺陷通过 @2026-09-01**（ACCEPTANCE_LOG §P23：0d6df7f 12 组件 L2-9 逐</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🆕 ****1A+1B 已合 main @2026-09-02**（feat/upg50-ph1 rebase main 后 ff｜0bc</t>
+          <t>✅ **阶段 1 全量已合 main @2026-09-02**（0ce0fd0 链：1A f3c0fda+1B bcb18f5+1C 1a</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3158,8 +3158,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>📌 施工中（P0·3~5 工作日；CT-13/14 契约后补不阻塞）- → 方案 v3 定稿 @2026-09-01（二轮大神 9.1/1</t>
+          <t>📌 施工中（P0·3~5 工作日；CT-13/14 契约后补不阻塞）  → 方案 v3 定稿 @2026-09-01（二轮大神 9.1/1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ **验收员 43a 打回 @2026-09-02**（ACCEPTANCE_LOG §P24：8b7b6d0 框架+H1 契约/H5 精</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-50_阶段2_MCP组件注册制开放_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>📌 施工中（P0·3~5 工作日；CT-13/14 契约后补不阻塞）  → 方案 v3 定稿 @2026-09-01（二轮大神 9.1/1</t>
+          <t>✅ **C 完成 @2026-09-02**（补充节 V68-8/V69-4 补验：feat/upg68 `8380108`；变异亲杀 4/</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>合 main待设计师）  **v3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1570,7 +1570,8 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628）</t>
+          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628）+**卡点**</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3168,7 +3169,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>合 main待设计师）  **v3</t>
+          <t>✅ **已合 main @c2defad**（rebase origin/main 零冲突 + ff；V68-8/V69-4 全量 618/</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>✅ **C 完成 @2026-09-02**（详状态锚）：H1 契约落盘（UPG-69 共引）/H2 web.* 工具面经 upg27 热挂</t>
+          <t xml:space="preserve">✅ **C 完成 @2026-09-02（R1 修复）**（feat/upg43a `c924197` 已 push origin：M-1 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>❌ **验收员 43a 打回 @2026-09-02**（ACCEPTANCE_LOG §P24：8b7b6d0 框架+H1 契约/H5 精</t>
+          <t>❌ **R1 复验 二次打回（范围收窄）@2026-09-02**（ACCEPTANCE_LOG §P24-R1：c924197 M-2 双</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1570,8 +1570,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628）-**卡点**</t>
+          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628） **卡点**</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -2317,7 +2317,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>✅ **1C 复验 带缺陷通过 @2026-09-01**（ACCEPTANCE_LOG §P23：0d6df7f 12 组件 L2-9 逐</t>
+          <t>✅ **阶段2 复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P25：feat/upg50-ph2 5248</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **C 完成 @2026-09-02（R1 修复）**（feat/upg43a `c924197` 已 push origin：M-1 </t>
+          <t>✅ **C 完成 @2026-09-02（R2 修复）**（feat/upg43a `e34c246` 已 push origin：M-1a</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>🔨**已派单 @2026-08-30**（用户转派；worktree=mov-tool-orch branch=feat/tool-orc</t>
+          <t>📝 **设计 v3.1 补丁 @2026-09-02**（Plan 模式=顺序真相层：两段式先 Plan 后执行+steps DAG+机器</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>❌ **R1 复验 二次打回（范围收窄）@2026-09-02**（ACCEPTANCE_LOG §P24-R1：c924197 M-2 双</t>
+          <t>✅ **R2 复验 通过 @2026-09-02**（ACCEPTANCE_LOG §P24-R2：e34c246 M-1a 两点落地[ca</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-46_工具联动Runtime契约_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>✅ 方案 v1（规划卡：前置=UPG-42 合 main + UPG-27 交付），⏳ 待前置</t>
+          <t>✅ **已合 main @15e53e6**（R2 通过后 rebase 新 main 零冲突 + ff；H2/H3 端到端随 UPG-69</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>验收员补验；报告 `DELIVERY_UPG55_2026-09-01.md`；已登记两个表）｜待验收：L1 J-1~J-9 复跑+变异重杀</t>
+          <t xml:space="preserve">📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在 </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已合 main@2026-09-01（e1f241e）｜无遗留卡点 ｜</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>✅ **已合 main @c2defad**（rebase origin/main 零冲突 + ff；V68-8/V69-4 全量 618/</t>
+          <t>✅ **已合 main @c2defad @2026-09-02**（rebase origin/main 零冲突 + ff；V68-8/V</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -657,12 +657,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>↪**已并入 UPG-02 合并施工 @2026-08-29（用户拍板）**｜本卡销（方案文档保留为合并单子方案；施工/验收/登记走 UPG</t>
+          <t>拍板收口+大神速览）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-2 门 3 + 下篇 A2-4~A2-6；三轮纪律 5 依赖链｜B 生产信号已就绪[59 已合]）</t>
+          <t>✅ **设计 v2 定稿 @2026-09-02**（大神二轮 12/12 全采纳｜统计口径 v2 定稿：按 skill 去重/min20+</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -845,27 +845,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>✅ 方案完成｜ feat/upg08 → main aa09882（ff，含R1/R2修复+同步）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>✅C R2 修复完成</t>
+          <t>修复完成，待</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>验收员✅全部通过 @2026-08-26（R1 复验 P1×3 全消 + R2 消 P3，无遗留缺陷）</t>
+          <t>🔨 打回修复派单，待程序员领修复（优先原施工者 C；撞单按认领规则）｜ 验收缺陷明细见 `0027-mov\docs\ACCEPTANCE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-26**（`aa09882`，ff 合入，同步产物 json 已移出版本库）</t>
+          <t>已合 main的单基于最新 main 重开分支）；再认领：工单表第 9 行备注追加 `认领: &lt;agent&gt; R1修复 @&lt;时间&gt;`； 2.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -845,27 +845,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 方案完成｜ feat/upg08 → main aa09882（ff，含R1/R2修复+同步）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>修复完成，待</t>
+          <t>✅C R2 修复完成</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🔨 打回修复派单，待程序员领修复（优先原施工者 C；撞单按认领规则）｜ 验收缺陷明细见 `0027-mov\docs\ACCEPTANCE</t>
+          <t>验收员✅全部通过 @2026-08-26（R1 复验 P1×3 全消 + R2 消 P3，无遗留缺陷）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已合 main的单基于最新 main 重开分支）；再认领：工单表第 9 行备注追加 `认领: &lt;agent&gt; R1修复 @&lt;时间&gt;`； 2.</t>
+          <t>**设计师✅已合 main @2026-08-26**（`aa09882`，ff 合入，同步产物 json 已移出版本库）</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -845,27 +845,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>✅ 方案完成｜ feat/upg08 → main aa09882（ff，含R1/R2修复+同步）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>✅C R2 修复完成</t>
+          <t>修复完成，待</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>验收员✅全部通过 @2026-08-26（R1 复验 P1×3 全消 + R2 消 P3，无遗留缺陷）</t>
+          <t>🔨 打回修复派单，待程序员领修复（优先原施工者 C；撞单按认领规则）｜ 验收缺陷明细见 `0027-mov\docs\ACCEPTANCE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-26**（`aa09882`，ff 合入，同步产物 json 已移出版本库）</t>
+          <t>已合 main的单基于最新 main 重开分支）；再认领：工单表第 9 行备注追加 `认领: &lt;agent&gt; R1修复 @&lt;时间&gt;`； 2.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>✅C 完成</t>
+          <t>✅C 完成｜ 设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>✅ 审验终审通过 @2026-08-27（L3 真实验证码登录通过，用户转达）</t>
+          <t>✅验收员通过 @2026-08-27（c0b5a0d 独立复核：verify 基线/变异亲杀/fail-loud/端到端推导全过）</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（772e2a5 合并 b3b3c6e；Manifest 冲突语义解决：LAUNCHE</t>
+          <t>**设计师✅已合 main @2026-08-27**（c0b5a0d ff 合入，main 与 feat/upg10 已推 origin；</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -516,32 +516,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>✅ 方案 **v2.3**（2026-08-29 评审#5 §十闭环 + 规则 21 复核 @8af7da9 随版完成：**批 1 棘轮时序</t>
+          <t>✅ 方案v2(溯源修正)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**C 批 4 完成 @2026-08-30**（feat/upg01-b4 **8cf7a2f 前段 + 5f5219c 后段** 已 </t>
+          <t xml:space="preserve">✅**M3-R2 三件修复完成 @2026-08-29**（feat/upg02 **5c113cb** 已 push origin，基底 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG b71b306）：feat/upg64 115762d </t>
+          <t>🔨**M3 接线补救局部打回→M3-R2 排期（设计师定夺 @2026-08-29）**：M3（70db6c6）验收 L1 全实证通过+真</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>✅**批4 已合 main @2026-08-30**（设计师 merge c753e8a[含 6aaa1fc R1修复]，§六 抽查：L3</t>
+          <t>✅**M3-R2 复验+审验通过 → M3+M3-R2 已合 main @2026-08-29**（验收员复验②：capture 真机 PN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-01_批1批2_派单_2026-08-29.md</t>
+          <t>设计师/派单/UPG-02+04合并_派单_2026-08-29.md</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 方案完成｜ feat/upg08 → main aa09882（ff，含R1/R2修复+同步）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>修复完成，待</t>
+          <t>✅C R2 修复完成</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🔨 打回修复派单，待程序员领修复（优先原施工者 C；撞单按认领规则）｜ 验收缺陷明细见 `0027-mov\docs\ACCEPTANCE</t>
+          <t>验收员✅全部通过 @2026-08-26（R1 复验 P1×3 全消 + R2 消 P3，无遗留缺陷）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已合 main的单基于最新 main 重开分支）；再认领：工单表第 9 行备注追加 `认领: &lt;agent&gt; R1修复 @&lt;时间&gt;`； 2.</t>
+          <t>**设计师✅已合 main @2026-08-26**（`aa09882`，ff 合入，同步产物 json 已移出版本库）</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>✅C 完成｜ 设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
+          <t>✅C 完成</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-27（c0b5a0d 独立复核：verify 基线/变异亲杀/fail-loud/端到端推导全过）</t>
+          <t>✅ 审验终审通过 @2026-08-27（L3 真实验证码登录通过，用户转达）</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（c0b5a0d ff 合入，main 与 feat/upg10 已推 origin；</t>
+          <t>**设计师✅已合 main @2026-08-27**（772e2a5 合并 b3b3c6e；Manifest 冲突语义解决：LAUNCHE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -516,32 +516,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>✅ 方案v2(溯源修正)</t>
+          <t>✅ 方案 **v2.3**（2026-08-29 评审#5 §十闭环 + 规则 21 复核 @8af7da9 随版完成：**批 1 棘轮时序</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**M3-R2 三件修复完成 @2026-08-29**（feat/upg02 **5c113cb** 已 push origin，基底 </t>
+          <t xml:space="preserve">✅**C 批 4 完成 @2026-08-30**（feat/upg01-b4 **8cf7a2f 前段 + 5f5219c 后段** 已 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🔨**M3 接线补救局部打回→M3-R2 排期（设计师定夺 @2026-08-29）**：M3（70db6c6）验收 L1 全实证通过+真</t>
+          <t xml:space="preserve">【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG b71b306）：feat/upg64 115762d </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>✅**M3-R2 复验+审验通过 → M3+M3-R2 已合 main @2026-08-29**（验收员复验②：capture 真机 PN</t>
+          <t>✅**批4 已合 main @2026-08-30**（设计师 merge c753e8a[含 6aaa1fc R1修复]，§六 抽查：L3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-02+04合并_派单_2026-08-29.md</t>
+          <t>设计师/派单/UPG-01_批1批2_派单_2026-08-29.md</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>验收员✅全部通过 @2026-08-26（R1 复验 P1×3 全消 + R2 消 P3，无遗留缺陷）</t>
+          <t>验收员✅全部通过 @2026-08-26（R1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -882,17 +882,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UPG-09</t>
+          <t>UPG-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MOV App 登录页实现</t>
+          <t>工作台 sync 状态语义细分</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>✅C 完成</t>
+          <t>✅C 完成｜ 设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>✅ 审验终审通过 @2026-08-27（L3 真实验证码登录通过，用户转达）</t>
+          <t>✅验收员通过 @2026-08-27（c0b5a0d 独立复核：verify 基线/变异亲杀/fail-loud/端到端推导全过）</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（772e2a5 合并 b3b3c6e；Manifest 冲突语义解决：LAUNCHE</t>
+          <t>**设计师✅已合 main @2026-08-27**（c0b5a0d ff 合入，main 与 feat/upg10 已推 origin；</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -929,17 +929,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UPG-10</t>
+          <t>UPG-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>工作台 sync 状态语义细分</t>
+          <t>首启隐私政策弹窗（应用宝整改）</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -949,22 +949,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>✅C 完成｜ 设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
+          <t>✅C 完成</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-27（c0b5a0d 独立复核：verify 基线/变异亲杀/fail-loud/端到端推导全过）</t>
+          <t xml:space="preserve">✅验收员通过 @2026-08-27（308cabf 独立复核：L1 全量 228 绿+变异亲杀 2/2 + L2 真机八场景全过；带缺陷 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（c0b5a0d ff 合入，main 与 feat/upg10 已推 origin；</t>
+          <t>**设计师✅已合 main @2026-08-27**（feat/upg11 308cabf ff 合入 main 9c2f0da，与 W-</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>设计师/方案设计/UPG-10_工作台sync状态语义细分_方案设计.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -976,37 +976,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UPG-11</t>
+          <t>UPG-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>首启隐私政策弹窗（应用宝整改）</t>
+          <t>WebView 引擎预热 + 页面加载体验优化</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>✅ 方案完成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>✅C 完成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅验收员通过 @2026-08-27（308cabf 独立复核：L1 全量 228 绿+变异亲杀 2/2 + L2 真机八场景全过；带缺陷 </t>
+          <t>✅验收员通过 @2026-08-27（ce3336f 独立复核：L1 全量 236 绿+三变异亲杀 3/3 + L2 时序/L3 飞行模式全</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（feat/upg11 308cabf ff 合入 main 9c2f0da，与 W-</t>
+          <t>**设计师✅已合 main @2026-08-27**（feat/upg12 ce3336f 合并提交 689b663，已推 origin；</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1023,17 +1023,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UPG-12</t>
+          <t>UPG-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WebView 引擎预热 + 页面加载体验优化</t>
+          <t>登录页视觉修订（用户 6 条 + 顺手修）</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-27（ce3336f 独立复核：L1 全量 236 绿+三变异亲杀 3/3 + L2 时序/L3 飞行模式全</t>
+          <t>审验通过 @2026-08-27（整单 a49c68a+583a40f+6410cb3 无已知缺陷：#8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（feat/upg12 ce3336f 合并提交 689b663，已推 origin；</t>
+          <t>**设计师✅已合 main @2026-08-27**（feat/upg13 6410cb3 ff 合入，已推 origin）</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UPG-13</t>
+          <t>UPG-40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>登录页视觉修订（用户 6 条 + 顺手修）</t>
+          <t>App 视觉风格统一（黑白主调 · logo 同源）</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1085,22 +1085,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 方案 v1 定稿（五决策点已拍板 @2026-08-29，见「拍板记录」），✅ **C 完成 @2026-08-30 01:42**（f</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C 完成@2026-08-30 01:42**（feat/upg40 **f9e3f17** 基底 main 31769a0 已 push；</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>✅审验通过 @2026-08-27（整单 a49c68a+583a40f+6410cb3 无已知缺陷：#8 复验成立、#9 独立复验含变异亲</t>
+          <t>✅**验收通过 @2026-08-30**（L1 376/0/0 亲跑+变异 4/4 亲杀+真机候选C 冷调近黑）+✅**审验通过 @202</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-27**（feat/upg13 6410cb3 ff 合入，已推 origin）</t>
+          <t>✅**已合 main @c9298d0**（ff-only 已推 origin；合并后全量复跑绿；worktree mov-upg40 可收</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UPG-27</t>
+          <t>UPG-41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Code Mode SDK 生成 + 工具描述按需加载（tool.help）</t>
+          <t>本地页「列表/详情」重设计 + 市场包独立模板（2026-08-30 拍板替代原「二级页化」方案）</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1132,27 +1132,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>✅ 方案 v1.2.1（v1 分层溯源过 @8af7da9；v1.1 灵感库增补；v1.2 评审一轮；v1.2.1 = 2026-08-29</t>
+          <t>✅ 方案 v2 定稿 @2026-08-30（v2=**替代 v1「二级页化」**；原 feat/upg41 bb31e33 作废未合 ma</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>✅**C 修复完成 @2026-08-30**（feat/upg27 **ace425c** 已 push origin[force-wit</t>
+          <t>【✅✅ **C 修复交付 @2026-08-30**（feat/upg41 **675970b** 修复+**0ef352d** 产物同步，</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>【✅ 验收员边界修复复验通过 @2026-08-30（ACCEPTANCE_LOG 2e0c874）：0aa0c07（rebase 7992</t>
+          <t>**✅ 验收员复验通过 @2026-08-30**：P1-① 设备控制详情真机「常驻|无 Switch」无 MARKET_NOT_INSTA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>✅**前置已解除 @2026-08-29：UPG-01 批1 已合 main 107f9c2，登记层数据源就绪｜可认领**）</t>
+          <t>✅**已合 main @2026-08-30**（设计师 merge f33fb33[含 3e950ab]，P1/P2 修复复验通过；pus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师\方案设计\本地页列表详情重设计_方案_v1_2026-08-30.md</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1164,12 +1164,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UPG-40</t>
+          <t>UPG-42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>App 视觉风格统一（黑白主调 · logo 同源）</t>
+          <t>mow.kim 站点容器面 WebMCP 化（一期+二期：mov-page-server + 全站 10 工具 + 双轨 AI 就绪）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1179,22 +1179,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>✅ 方案 v1 定稿（五决策点已拍板 @2026-08-29，见「拍板记录」），✅ **C 完成 @2026-08-30 01:42**（f</t>
+          <t>✅ 方案 v1.1 定稿（设计稿四补强已落：mov_ 前缀/input schema/错误码对齐/三期视觉反馈），📌 待派单</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-30 01:42**（feat/upg40 **f9e3f17** 基底 main 31769a0 已 push；</t>
+          <t>✅**C 批1 完成 @2026-08-30 01:22**（feat/upg42 **3fde899** 已 push origin，基底</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>✅**验收通过 @2026-08-30**（L1 376/0/0 亲跑+变异 4/4 亲杀+真机候选C 冷调近黑）+✅**审验通过 @202</t>
+          <t>✅**批1 验收通过 @2026-08-30** + ✅**审验通过 @2026-08-30**（AGPL 零 import/零第三方拷贝，</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>✅**已合 main @c9298d0**（ff-only 已推 origin；合并后全量复跑绿；worktree mov-upg40 可收</t>
+          <t>✅**批1 已合 main @dc58ddf**（ff-only 已推 origin；worktree mov-upg42 可收）</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1211,42 +1211,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UPG-41</t>
+          <t>UPG-43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>本地页「列表/详情」重设计 + 市场包独立模板（2026-08-30 拍板替代原「二级页化」方案）</t>
+          <t>ConnectWeb 作 WebMCP 客户端/Hub（浏览器双本质三期）</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>✅ 方案 v2 定稿 @2026-08-30（v2=**替代 v1「二级页化」**；原 feat/upg41 bb31e33 作废未合 ma</t>
+          <t>📌 **重排 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造）**｜本卡=**43a App 侧 WebMCP Hub</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>【✅✅ **C 修复交付 @2026-08-30**（feat/upg41 **675970b** 修复+**0ef352d** 产物同步，</t>
+          <t>✅ **C 完成 @2026-09-02（R2 修复）**（feat/upg43a `e34c246` 已 push origin：M-1a</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>**✅ 验收员复验通过 @2026-08-30**：P1-① 设备控制详情真机「常驻|无 Switch」无 MARKET_NOT_INSTA</t>
+          <t>✅ **R2 复验 通过 @2026-09-02**（ACCEPTANCE_LOG §P24-R2：e34c246 M-1a 两点落地[ca</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-30**（设计师 merge f33fb33[含 3e950ab]，P1/P2 修复复验通过；pus</t>
+          <t>✅ **已合 main @15e53e6**（R2 通过后 rebase 新 main 零冲突 + ff；H2/H3 端到端随 UPG-69</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>设计师\方案设计\本地页列表详情重设计_方案_v1_2026-08-30.md</t>
+          <t>设计师\派单\UPG-43a_App内浏览器WebMCP_Hub框架_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UPG-42</t>
+          <t>UPG-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mow.kim 站点容器面 WebMCP 化（一期+二期：mov-page-server + 全站 10 工具 + 双轨 AI 就绪）</t>
+          <t>设置页收口（账号卡接真 + 退出登录去重 + 两行死链修复）</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>✅ 方案 v1.1 定稿（设计稿四补强已落：mov_ 前缀/input schema/错误码对齐/三期视觉反馈），📌 待派单</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>✅**C 批1 完成 @2026-08-30 01:22**（feat/upg42 **3fde899** 已 push origin，基底</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>✅**批1 验收通过 @2026-08-30** + ✅**审验通过 @2026-08-30**（AGPL 零 import/零第三方拷贝，</t>
+          <t>✅验收员通过 @2026-08-28（R2 e16fae8 三判据全过 + R2 复修 04341d2 全产物口径零命中）</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>✅**批1 已合 main @dc58ddf**（ff-only 已推 origin；worktree mov-upg42 可收）</t>
+          <t>**设计师✅已合 main @2026-08-28**（全链 9323975→ce5ab0d→e16fae8→1825338→04341d2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1305,42 +1305,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPG-43</t>
+          <t>UPG-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ConnectWeb 作 WebMCP 客户端/Hub（浏览器双本质三期）</t>
+          <t>登录页死锁修（登录钮常可点 + 协议整行可点）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>📌 **重排 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造）**｜本卡=**43a App 侧 WebMCP Hub</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>✅ **C 完成 @2026-09-02（R2 修复）**（feat/upg43a `e34c246` 已 push origin：M-1a</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>✅ **R2 复验 通过 @2026-09-02**（ACCEPTANCE_LOG §P24-R2：e34c246 M-1a 两点落地[ca</t>
+          <t>✅验收员通过 @2026-08-28（151fdb1 独立复核：L1 全量 246 绿 + 变异亲杀 3/3 + L2 五图证据链；无缺陷）</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>✅ **已合 main @15e53e6**（R2 通过后 rebase 新 main 零冲突 + ff；H2/H3 端到端随 UPG-69</t>
+          <t>**设计师✅已合 main @2026-08-28**（merge 509ab0c，ACCEPTANCE_LOG append-only 冲</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>设计师\派单\UPG-43a_App内浏览器WebMCP_Hub框架_派单_2026-09-02.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1352,12 +1352,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UPG-14</t>
+          <t>UPG-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>设置页收口（账号卡接真 + 退出登录去重 + 两行死链修复）</t>
+          <t>release 签名配置收口（明文口令外移）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-28（R2 e16fae8 三判据全过 + R2 复修 04341d2 全产物口径零命中）</t>
+          <t>✅验收员通过 @2026-08-28（172e67d 独立复核：L1 全量 243 绿 + apksigner 签名有效 + L2 口令文件</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（全链 9323975→ce5ab0d→e16fae8→1825338→04341d2</t>
+          <t xml:space="preserve">**设计师✅已合 main @2026-08-28**（merge ee312f5，已推 origin；主 worktree 签名参数已落 </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UPG-15</t>
+          <t>UPG-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>登录页死锁修（登录钮常可点 + 协议整行可点）</t>
+          <t>App demo 假数据全清（Vue 侧）</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C 完成@2026-08-28（feat/upg17 96c963d，3 commits：926d70b feat+1f532cb buil</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-28（151fdb1 独立复核：L1 全量 246 绿 + 变异亲杀 3/3 + L2 五图证据链；无缺陷）</t>
+          <t>✅**验收员通过 @2026-08-28 深夜**（独立复核全过：L1 `--rerun-tasks` 36 类 253/0/0 吻合+sy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（merge 509ab0c，ACCEPTANCE_LOG append-only 冲</t>
+          <t xml:space="preserve">✅**设计师已合 main @2026-08-28（merge 36d7f6e 已推 origin）｜UPG-17 全链闭环**（合后全量 </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,37 +1446,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UPG-16</t>
+          <t>UPG-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>release 签名配置收口（明文口令外移）</t>
+          <t>Android 死代码清理</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 方案完成</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🛠 在施 C @2026-08-30 01:39（认领=worktree mov-upg18 branch feat/upg18）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-28（172e67d 独立复核：L1 全量 243 绿 + apksigner 签名有效 + L2 口令文件</t>
+          <t>🔎**验收员独立复核 @2026-08-29**（@main 107f9c2，与设计师刷新独立互证一致）：29/29 占位仍死（清单 24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">**设计师✅已合 main @2026-08-28**（merge ee312f5，已推 origin；主 worktree 签名参数已落 </t>
+          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628） **卡点**</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1493,12 +1493,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPG-17</t>
+          <t>UPG-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>App demo 假数据全清（Vue 侧）</t>
+          <t>应用图标换 MOV 竖眼 Logo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-28（feat/upg17 96c963d，3 commits：926d70b feat+1f532cb buil</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>✅**验收员通过 @2026-08-28 深夜**（独立复核全过：L1 `--rerun-tasks` 36 类 253/0/0 吻合+sy</t>
+          <t>✅**验收员复验通过 @2026-08-28**（验收对象=入库链 feat/upg19 fa8fdd1+2c6b777+82a5322：L</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**设计师已合 main @2026-08-28（merge 36d7f6e 已推 origin）｜UPG-17 全链闭环**（合后全量 </t>
+          <t>**设计师✅已合 main @2026-08-28**（merge 17b4e04 已推 origin；mov-upg19 worktree</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1540,37 +1540,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UPG-18</t>
+          <t>UPG-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Android 死代码清理</t>
+          <t>聊天页 chips 改造 v2（气泡式 切换模型+MCP 工具）</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>✅ 方案完成</t>
+          <t>**转派 @2026-08-28 18:35（用户拍板）**：C 认领后零提交 11h（分支仍 8aaa999）、主线在 UPG-17｜转派</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>🛠 在施 C @2026-08-30 01:39（认领=worktree mov-upg18 branch feat/upg18）</t>
+          <t>🔨 已派单，C 已认领在施 @2026-08-28 07:45（worktree=mov-upg20 branch=feat/upg20，</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>🔎**验收员独立复核 @2026-08-29**（@main 107f9c2，与设计师刷新独立互证一致）：29/29 占位仍死（清单 24</t>
+          <t>✅验收员复验通过 @2026-08-28 深夜（装机实证：二级 refit 重锚底部 2062≤chip 顶 2113 贴上沿不悬空、MCP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628） **卡点**</t>
+          <t>✅**设计师已合 main @2026-08-28（merge 974f33a 已推 origin）｜UPG-20 全链闭环**（合前独立复</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UPG-19</t>
+          <t>UPG-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>应用图标换 MOV 竖眼 Logo</t>
+          <t>聊天页输入框回车键=发送（IME 发送键修复）</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅程序员 C 完成 @2026-08-29（feat/upg21 a14ee64，基于 main 198e26f；报告 DELIVERY_U</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>✅**验收员复验通过 @2026-08-28**（验收对象=入库链 feat/upg19 fa8fdd1+2c6b777+82a5322：L</t>
+          <t>验收员通过 @2026-08-29（</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（merge 17b4e04 已推 origin；mov-upg19 worktree</t>
+          <t>✅**已合 main @2026-08-29（merge 5170421 已推 origin）｜UPG-21 全链闭环**（审验员五步独立实</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1634,12 +1634,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UPG-20</t>
+          <t>UPG-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聊天页 chips 改造 v2（气泡式 切换模型+MCP 工具）</t>
+          <t>记忆尾单（UPG-05 遗留收口：COVER_HIT 装配打点 + 剧本断言 + 冗余清理）</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1649,27 +1649,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>**转派 @2026-08-28 18:35（用户拍板）**：C 认领后零提交 11h（分支仍 8aaa999）、主线在 UPG-17｜转派</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>🔨 已派单，C 已认领在施 @2026-08-28 07:45（worktree=mov-upg20 branch=feat/upg20，</t>
+          <t>✅**C 完成 @2026-08-29 16:48**（feat/upg22 **aacb15b** 已 push origin，基线已 f</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>✅验收员复验通过 @2026-08-28 深夜（装机实证：二级 refit 重锚底部 2062≤chip 顶 2113 贴上沿不悬空、MCP</t>
+          <t xml:space="preserve">✅**验收员 R1 L2 复验通过 @2026-08-29**（三连全过：①装配打点落新 session jsonl memory/ref </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>✅**设计师已合 main @2026-08-28（merge 974f33a 已推 origin）｜UPG-20 全链闭环**（合前独立复</t>
+          <t>✅**已合 main @2026-08-29**（程序员代行设计师：rebase 87787b8 后 ff-only **495060f**</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-22_记忆尾单_派单_2026-08-29.md</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UPG-21</t>
+          <t>UPG-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聊天页输入框回车键=发送（IME 发送键修复）</t>
+          <t>本地 tab「本机能力总览」+ 主页钉选小按钮</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>✅程序员 C 完成 @2026-08-29（feat/upg21 a14ee64，基于 main 198e26f；报告 DELIVERY_U</t>
+          <t xml:space="preserve">修复完成@2026-08-29**（feat/upg23 **0bfa4fa** 已 push origin；`runOnUiThread </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>验收员通过 @2026-08-29（</t>
+          <t>✅**验收员复验通过 @2026-08-29**（diff 恰 1 行无夹带 + L1 338/0/0 亲跑 + 真机 5556：钉选/取消</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-29（merge 5170421 已推 origin）｜UPG-21 全链闭环**（审验员五步独立实</t>
+          <t>✅**审验通过 → 已合 main @2026-08-29**（查验员逐项亲核确认；设计师 §六抽查：R1_05 主页钉选排免重启当场可见亲</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1728,12 +1728,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UPG-22</t>
+          <t>UPG-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>记忆尾单（UPG-05 遗留收口：COVER_HIT 装配打点 + 剧本断言 + 冗余清理）</t>
+          <t>MOV 设计规范 v1（风格定性 + token 坐标表）</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1743,27 +1743,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ **已作废 @2026-09-02**（用户拍板：设计规范 v1 文档已删｜由 v2/v2.1+UPG-50 外观组件体系接替；本卡销账</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-29 16:48**（feat/upg22 **aacb15b** 已 push origin，基线已 f</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收员 R1 L2 复验通过 @2026-08-29**（三连全过：①装配打点落新 session jsonl memory/ref </t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-29**（程序员代行设计师：rebase 87787b8 后 ff-only **495060f**</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-22_记忆尾单_派单_2026-08-29.md</t>
+          <t>设计师/方案设计/MOV设计规范_v1.md</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UPG-23</t>
+          <t>UPG-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>本地 tab「本机能力总览」+ 主页钉选小按钮</t>
+          <t>UI 瑕疵批修（规范 v1 待并轨清单 13 项）</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1790,27 +1790,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>裁决=MainActivity/PhotoAskSheet 文本底色取 UiTokens、primary 保 upg40 mov_prima</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">修复完成@2026-08-29**（feat/upg23 **0bfa4fa** 已 push origin；`runOnUiThread </t>
+          <t>C 完成@2026-08-29**（feat/upg25 **62986c2** 已推 origin｜含 merge origin/main</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>✅**验收员复验通过 @2026-08-29**（diff 恰 1 行无夹带 + L1 338/0/0 亲跑 + 真机 5556：钉选/取消</t>
+          <t>❌**打回@2026-08-30**：与已合 UPG-40 换肤**同文件双改**（WorkbenchPage/demo.js/MainAc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>✅**审验通过 → 已合 main @2026-08-29**（查验员逐项亲核确认；设计师 §六抽查：R1_05 主页钉选排免重启当场可见亲</t>
+          <t xml:space="preserve">✅**已合 main @2026-08-30**（设计师 merge 8f8debd，含 2ccce25；§六 抽查通过 13 项+候选C </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-25_重修_派单_2026-08-30.md</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UPG-24</t>
+          <t>UPG-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MOV 设计规范 v1（风格定性 + token 坐标表）</t>
+          <t>侧边栏品牌区换 logo+黑字 + 抽屉展开占比 61.8%</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>❌ **已作废 @2026-09-02**（用户拍板：设计规范 v1 文档已删｜由 v2/v2.1+UPG-50 外观组件体系接替；本卡销账</t>
+          <t>裁决]；用户确认已实现 @2026-09-02）→</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 验收通过（用户确认「已实现」）@2026-09-02（feat/sidebar-brand 7a6dff6+0fdfe87：品牌区 lo</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>**分支未合 main（162 分叉）｜已合 main@2026-09-02（feat/sidebar-brand 7a6dff6/0fdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>设计师/方案设计/MOV设计规范_v1.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1869,12 +1869,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UPG-25</t>
+          <t>UPG-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UI 瑕疵批修（规范 v1 待并轨清单 13 项）</t>
+          <t>obsidian.file.write 审批闸修复（isHarmless file.write 特判误捕）</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>裁决=MainActivity/PhotoAskSheet 文本底色取 UiTokens、primary 保 upg40 mov_prima</t>
+          <t>✅**方案 v1 已出 @2026-08-29**（`设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md`）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-29**（feat/upg25 **62986c2** 已推 origin｜含 merge origin/main</t>
+          <t>✅**程序员 C 完成 @2026-08-30 01:05**（feat/upg28 **443b288** 已 push origin，基</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>❌**打回@2026-08-30**：与已合 UPG-40 换肤**同文件双改**（WorkbenchPage/demo.js/MainAc</t>
+          <t>✅**验收员验收通过 @2026-08-30**（L1 377/0/0 亲跑+变异 M1/M2 双锚亲杀+L2 采纳模拟器证据[真机 ASK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**已合 main @2026-08-30**（设计师 merge 8f8debd，含 2ccce25；§六 抽查通过 13 项+候选C </t>
+          <t>✅**已合 main @443b288**（ff-only 已推 origin，合后全量复跑 377/0/0 绿；worktree mov-</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-25_重修_派单_2026-08-30.md</t>
+          <t>设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1916,12 +1916,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UPG-26</t>
+          <t>UPG-44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>侧边栏品牌区换 logo+黑字 + 抽屉展开占比 61.8%</t>
+          <t>AcceptanceJudge B1 观察层（UPG-06 批2 剩项）</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>裁决]；用户确认已实现 @2026-09-02）→</t>
+          <t>裁决criteria+AI 回复→verdict/失败静默]；**投影剔键硬红**=Surface.deriveEventMessage 显</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C 完成@2026-08-30 04:05**（feat/upg44 **122945b** 基底 main 3263f10 已 push；</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>✅ 验收通过（用户确认「已实现」）@2026-09-02（feat/sidebar-brand 7a6dff6+0fdfe87：品牌区 lo</t>
+          <t xml:space="preserve">审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8fc 已推 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>**分支未合 main（162 分叉）｜已合 main@2026-09-02（feat/sidebar-brand 7a6dff6/0fdf</t>
+          <t>✅**验收+审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-44_AcceptanceJudge_B1_派单_2026-08-30.md</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1963,42 +1963,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UPG-28</t>
+          <t>UPG-45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>obsidian.file.write 审批闸修复（isHarmless file.write 特判误捕）</t>
+          <t>审批 · Approval Capability Registry（权限能力注册表）</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>✅**方案 v1 已出 @2026-08-29**（`设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md`）</t>
+          <t>🔨**已派单 @2026-08-30**（用户已转派；派单文本 `设计师/派单/UPG-45_审批_ApprovalRegistry_派单</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>✅**程序员 C 完成 @2026-08-30 01:05**（feat/upg28 **443b288** 已 push origin，基</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>✅**验收员验收通过 @2026-08-30**（L1 377/0/0 亲跑+变异 M1/M2 双锚亲杀+L2 采纳模拟器证据[真机 ASK</t>
+          <t>✅**验收员通过 @2026-08-30**（ACCEPTANCE_LOG UPG-45，commit edf86d9）：核物[54行=as</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>✅**已合 main @443b288**（ff-only 已推 origin，合后全量复跑 377/0/0 绿；worktree mov-</t>
+          <t>**已合 main @2026-08-31 → 审验员**（approval 体系随 UPG-58/62/63 合入；ApprovalSer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md</t>
+          <t>设计师\方案设计\审批弹窗_用户授权层_设计_v3_2026-08-30.md</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2010,42 +2010,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UPG-44</t>
+          <t>UPG-46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AcceptanceJudge B1 观察层（UPG-06 批2 剩项）</t>
+          <t>工具联动 Runtime 契约（Tool Orchestration）</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>裁决criteria+AI 回复→verdict/失败静默]；**投影剔键硬红**=Surface.deriveEventMessage 显</t>
+          <t>📝 **设计 v3.1 补丁 @2026-09-02**（Plan 模式=顺序真相层：两段式先 Plan 后执行+steps DAG+机器</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-30 04:05**（feat/upg44 **122945b** 基底 main 3263f10 已 push；</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8fc 已推 </t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>✅**验收+审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-44_AcceptanceJudge_B1_派单_2026-08-30.md</t>
+          <t>设计师/派单/UPG-46_工具联动Runtime契约_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2057,12 +2057,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UPG-45</t>
+          <t>UPG-47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>审批 · Approval Capability Registry（权限能力注册表）</t>
+          <t>主页胶囊系统（pin_type+stableId / 三区 / ＋管理弹层 / 点击分派 / 长按 / 第三态 / 气泡字数）</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2072,27 +2072,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>🔨**已派单 @2026-08-30**（用户已转派；派单文本 `设计师/派单/UPG-45_审批_ApprovalRegistry_派单</t>
+          <t>🔨已派单</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅C 交付 @2026-08-30（feat/capsule-system **767228c+32ba01c** push；报告 程序员/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>✅**验收员通过 @2026-08-30**（ACCEPTANCE_LOG UPG-45，commit edf86d9）：核物[54行=as</t>
+          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG ff23a88）：feat/upg51 9ca96ff </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>**已合 main @2026-08-31 → 审验员**（approval 体系随 UPG-58/62/63 合入；ApprovalSer</t>
+          <t>✅后续美化已合 main @2026-08-31（dock 对齐 **afc1ccd**：＋号圆形·随胶囊横滑·气泡左对齐胶囊；管理面板设置</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>设计师\方案设计\审批弹窗_用户授权层_设计_v3_2026-08-30.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UPG-46</t>
+          <t>UPG-48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>工具联动 Runtime 契约（Tool Orchestration）</t>
+          <t>Memory API 工程契约（记忆页:memory-core/memory-api 模块化）</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>📝 **设计 v3.1 补丁 @2026-09-02**（Plan 模式=顺序真相层：两段式先 Plan 后执行+steps DAG+机器</t>
+          <t>🔨已派单 @2026-08-30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌**审验打回@2026-08-30（P1 边界违例）**｜MainActivity:582-598 直引 com.hermes.mov.m</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**已合 main @2026-08-30**（设计师 merge 92d4c22[含 0aa0c07]，审验五步复核通过：零直触core</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-46_工具联动Runtime契约_派单_2026-09-02.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2151,37 +2151,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UPG-47</t>
+          <t>UPG-49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>主页胶囊系统（pin_type+stableId / 三区 / ＋管理弹层 / 点击分派 / 长按 / 第三态 / 气泡字数）</t>
+          <t>记忆页「我的记忆」UI 分层管理</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>🔨已派单</t>
+          <t>✅ 方案 v4 定稿（记忆页分层管理_设计_v4 大神 9.2 冻结）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>✅C 交付 @2026-08-30（feat/capsule-system **767228c+32ba01c** push；报告 程序员/</t>
+          <t>🔨 **程序员 R2 修复交付 @2026-09-01**（feat/upg49-r2 **5640bce** 已 push origin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG ff23a88）：feat/upg51 9ca96ff </t>
+          <t xml:space="preserve">✅ **审验通过 @2026-09-01**（integrity_review=confirmed：P2-1a 72px 像素实证+删📌 </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>✅后续美化已合 main @2026-08-31（dock 对齐 **afc1ccd**：＋号圆形·随胶囊横滑·气泡左对齐胶囊；管理面板设置</t>
+          <t>✅ **设计师终审合流 @2026-09-02**（B9edcc4 落档+工单库补登；2 治理项裁决见下）</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2191,91 +2191,91 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG49-20260901-002</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UPG-48</t>
+          <t>UPG-50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Memory API 工程契约（记忆页:memory-core/memory-api 模块化）</t>
+          <t>外观·组件级显示（Display Appearance 工程契约）</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>🔨已派单 @2026-08-30</t>
+          <t>📌 **激活 @2026-09-02（用户拍板：出工单完善验收后派活）**</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>**✅ C 交付 @2026-09-01**（branch=feat/upg50，commit ca984df+8e73e8d｜A UI 编</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>❌**审验打回@2026-08-30（P1 边界违例）**｜MainActivity:582-598 直引 com.hermes.mov.m</t>
+          <t>✅ **阶段2 复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P25：feat/upg50-ph2 5248</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-30**（设计师 merge 92d4c22[含 0aa0c07]，审验五步复核通过：零直触core</t>
+          <t>✅ **阶段 1 全量已合 main @2026-09-02**（0ce0fd0 链：1A f3c0fda+1B bcb18f5+1C 1a</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-50_阶段2_MCP组件注册制开放_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG50-20260901-001</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UPG-49</t>
+          <t>UPG-51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>记忆页「我的记忆」UI 分层管理</t>
+          <t>用户画像标签池（Memory OS 商用投影 + 合规）</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>✅ 方案 v4 定稿（记忆页分层管理_设计_v4 大神 9.2 冻结）</t>
+          <t>✅ 方案 v1（设计详设已补，并入 **`Memory_OS_完整设计_v2`** 附录「Commercial Projection」；定位</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>🔨 **程序员 R2 修复交付 @2026-09-01**（feat/upg49-r2 **5640bce** 已 push origin</t>
+          <t>**✅ C 交付 @2026-08-31**（worktree=mov-upg51 branch=feat/upg51，commit 见报告</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **审验通过 @2026-09-01**（integrity_review=confirmed：P2-1a 72px 像素实证+删📌 </t>
+          <t>审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>✅ **设计师终审合流 @2026-09-02**（B9edcc4 落档+工单库补登；2 治理项裁决见下）</t>
+          <t>✅**验收+审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验独</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2285,66 +2285,66 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DEL-UPG49-20260901-002</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>UPG-50</t>
+          <t>UPG-52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>外观·组件级显示（Display Appearance 工程契约）</t>
+          <t>Memory OS 生命链（Semantic 池子 + 生命周期 + Timeline + Retrieval + blockedSourceHashes）</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>📌 **激活 @2026-09-02（用户拍板：出工单完善验收后派活）**</t>
+          <t>✅ 方案定稿（设计依据＝`Memory_OS_完整设计_v2`，唯一口径；含验收方案）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>**✅ C 交付 @2026-09-01**（branch=feat/upg50，commit ca984df+8e73e8d｜A UI 编</t>
+          <t>✅**C 完成 @2026-08-31**（认领 C worktree=mov-upg52 branch=feat/upg52，**52-1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>✅ **阶段2 复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P25：feat/upg50-ph2 5248</t>
+          <t>✅**审验通过 @2026-08-31**（独立 L2 模拟器复验：memory-os 目录建立/logcat 逐字吻合/空库零影响/4 只</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>✅ **阶段 1 全量已合 main @2026-09-02**（0ce0fd0 链：1A f3c0fda+1B bcb18f5+1C 1a</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=actor 模型[AI 只 PROPOSED]/blockedSourc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-50_阶段2_MCP组件注册制开放_派单_2026-09-02.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DEL-UPG50-20260901-001</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UPG-51</t>
+          <t>UPG-53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>用户画像标签池（Memory OS 商用投影 + 合规）</t>
+          <t>安全体验优化改造（该守才守 · 守得舒服）</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>✅ 方案 v1（设计详设已补，并入 **`Memory_OS_完整设计_v2`** 附录「Commercial Projection」；定位</t>
+          <t>✅ 方案 v1（依据 安全体系_设计_v2.1 §5.3 + mov_安全体验_demo.html；体验优化设计+验收标准已写入文档）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>**✅ C 交付 @2026-08-31**（worktree=mov-upg51 branch=feat/upg51，commit 见报告</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg53 **a665349** 已提交 3 commit[d434ab1 8场景落</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验</t>
+          <t>✅**验收员通过+审验通过 @2026-08-31**（L1 66 套件 473/0/0 独立重跑+变异 3/3[V3/V4a/V7]+L2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>✅**验收+审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验独</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=豁免链 gate 永不豁免写入侧已拦/vault.delete·cred</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2386,37 +2386,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UPG-52</t>
+          <t>UPG-54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Memory OS 生命链（Semantic 池子 + 生命周期 + Timeline + Retrieval + blockedSourceHashes）</t>
+          <t>安全中心（设置 -&gt; 安全 二级 · 等级仪表盘 + 分组策略 + 硬边界）</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（设计依据＝`Memory_OS_完整设计_v2`，唯一口径；含验收方案）</t>
+          <t>✅ 方案 v2（依据 安全中心_设计_v2 + 安全体系_设计_v2.1；评审通过·有条件冻结｜等级=结果仪表盘/策略摘要/分组/审计系统级</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（认领 C worktree=mov-upg52 branch=feat/upg52，**52-1</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg54 **9911e67** 已 push origin 3 commit[47</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>✅**审验通过 @2026-08-31**（独立 L2 模拟器复验：memory-os 目录建立/logcat 逐字吻合/空库零影响/4 只</t>
+          <t>✅**验收通过+审验通过 @2026-08-31**（8 项核物+482/0/0+变异 W1/W8/W5 三杀+模拟器仪表盘/实时刷新/足迹</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=actor 模型[AI 只 PROPOSED]/blockedSourc</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SecurityCenter 等级结果仪表盘无 setGrade API</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UPG-53</t>
+          <t>UPG-55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>安全体验优化改造（该守才守 · 守得舒服）</t>
+          <t>我的资产（资产管理项注册体系 · 基于安全体系 v2.1）</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2448,27 +2448,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>✅ 方案 v1（依据 安全体系_设计_v2.1 §5.3 + mov_安全体验_demo.html；体验优化设计+验收标准已写入文档）</t>
+          <t xml:space="preserve">✅**三轮评审采纳升 v2.2 工程冻结版 @2026-09-01**（评分 架构 9.2/安全 8.8/迁移 8.2/UI 9.1/工程 </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg53 **a665349** 已提交 3 commit[d434ab1 8场景落</t>
+          <t>✅**C 完成 @2026-09-01**（feat/upg55 **e1f241e** 已 push；[67-A 框架+迁移] ①Asse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>✅**验收员通过+审验通过 @2026-08-31**（L1 66 套件 473/0/0 独立重跑+变异 3/3[V3/V4a/V7]+L2</t>
+          <t xml:space="preserve">📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在 </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=豁免链 gate 永不豁免写入侧已拦/vault.delete·cred</t>
+          <t>已合 main@2026-09-01（e1f241e）｜无遗留卡点 ｜</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师\方案设计\07_资产\我的资产_资产管理项_设计_v2_2026-08-31.md</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2480,12 +2480,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UPG-54</t>
+          <t>UPG-56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>安全中心（设置 -&gt; 安全 二级 · 等级仪表盘 + 分组策略 + 硬边界）</t>
+          <t>评测集盘点与 fixture 版本机制（改造计划第一阶段①⑤）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2495,22 +2495,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>✅ 方案 v2（依据 安全中心_设计_v2 + 安全体系_设计_v2.1；评审通过·有条件冻结｜等级=结果仪表盘/策略摘要/分组/审计系统级</t>
+          <t>✅ 方案定稿（依据 `工单方案\工单方案\改造计划+验收标准_合并版_AHE×EvoC2F_2026-08-31.md` v1.4 上篇 §</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg54 **9911e67** 已 push origin 3 commit[47</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg56 **cc86fac** 已 push origin[1ed70a2 主体+</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>✅**验收通过+审验通过 @2026-08-31**（8 项核物+482/0/0+变异 W1/W8/W5 三杀+模拟器仪表盘/实时刷新/足迹</t>
+          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG c25aacf）：feat/upg56 cc86fac </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SecurityCenter 等级结果仪表盘无 setGrade API</t>
+          <t>✅**审验通过+已合 main @2026-08-31**（审验 33→34：盘点报告 6 节 12 条修正口径[实测 12 条非 13]+</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UPG-55</t>
+          <t>UPG-57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>我的资产（资产管理项注册体系 · 基于安全体系 v2.1）</t>
+          <t>Evolution Ledger 骨架（改造计划第一阶段②）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2542,27 +2542,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**三轮评审采纳升 v2.2 工程冻结版 @2026-09-01**（评分 架构 9.2/安全 8.8/迁移 8.2/UI 9.1/工程 </t>
+          <t>✅ 方案定稿（依据 合并版上篇 §6.1/§6.5 + 下篇 X-1/M-6；**架构约束=复用 TimelineLedger 基础设施，禁</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-09-01**（feat/upg55 **e1f241e** 已 push；[67-A 框架+迁移] ①Asse</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg57 **f4bae35** 已 push origin[Evolution L</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在 </t>
+          <t>【✅ **修复复验通过 @2026-08-31**（R1｜ACCEPTANCE_LOG 04fb19f）：feat/upg57 **fbcd</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>已合 main@2026-09-01（e1f241e）｜无遗留卡点 ｜</t>
+          <t>✅**R1 复验通过+审验通过+已合 main @2026-08-31**（审验 33→34：NS_EVOLUTION 12 事件+ACTO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>设计师\方案设计\07_资产\我的资产_资产管理项_设计_v2_2026-08-31.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2574,12 +2574,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UPG-56</t>
+          <t>UPG-58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>评测集盘点与 fixture 版本机制（改造计划第一阶段①⑤）</t>
+          <t>A-1 Manifest 五步链脚本（改造计划第一阶段③）</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2589,22 +2589,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 `工单方案\工单方案\改造计划+验收标准_合并版_AHE×EvoC2F_2026-08-31.md` v1.4 上篇 §</t>
+          <t>✅ 方案定稿（依据 合并版上篇 A-1 + 下篇 A1-1~A1-5/M-4/M-5；**硬验=零人工步骤**，≤20 行降为推荐约束[大神</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg56 **cc86fac** 已 push origin[1ed70a2 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg58 **ac8d27d** 已 push origin[a62f904 主体+</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG c25aacf）：feat/upg56 cc86fac </t>
+          <t xml:space="preserve">审验36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledger 写入 actor=system-deriver]/L1 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>✅**审验通过+已合 main @2026-08-31**（审验 33→34：盘点报告 6 节 12 条修正口径[实测 12 条非 13]+</t>
+          <t>✅**审验通过+已合 main @2026-08-31**（审验 36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2621,37 +2621,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UPG-57</t>
+          <t>UPG-59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Evolution Ledger 骨架（改造计划第一阶段②）</t>
+          <t>B 线蒸馏 MVP（改造计划第一阶段④ · 里程碑一承载）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 §6.1/§6.5 + 下篇 X-1/M-6；**架构约束=复用 TimelineLedger 基础设施，禁</t>
+          <t>✅ 方案定稿（依据 合并版上篇改造线 B + 下篇 B-1~B-9；教训六字段/三分类/配额/过期）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg57 **f4bae35** 已 push origin[Evolution L</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg59 **8da2907** 已 push origin 2 commit[2d</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>【✅ **修复复验通过 @2026-08-31**（R1｜ACCEPTANCE_LOG 04fb19f）：feat/upg57 **fbcd</t>
+          <t>✅**验收通过+审验通过 @2026-08-31**（9 项核物+73 套件 519/0/0 独立重跑+变异 V4/V3b/配额三杀独立复跑</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>✅**R1 复验通过+审验通过+已合 main @2026-08-31**（审验 33→34：NS_EVOLUTION 12 事件+ACTO</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=V-4 ACTIVE-only 注入过滤/配额 MAX_LESSONS=</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UPG-58</t>
+          <t>UPG-60</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A-1 Manifest 五步链脚本（改造计划第一阶段③）</t>
+          <t>A-2 三道门实现+元验证（改造计划第一阶段⑥）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2683,22 +2683,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-1 + 下篇 A1-1~A1-5/M-4/M-5；**硬验=零人工步骤**，≤20 行降为推荐约束[大神</t>
+          <t>✅ 方案定稿（依据 合并版上篇 A-2 + 下篇 A2-1~A2-6/M-1~M-6；**前置 UPG-56/58/59**）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg58 **ac8d27d** 已 push origin[a62f904 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg60 **a8d1363** 已 push origin[5a7a576 三道门</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">审验36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledger 写入 actor=system-deriver]/L1 </t>
+          <t xml:space="preserve">✅**验收通过+审验通过 @2026-08-31**（9f9466d 落档：9 项测试锚+77 套件 546/0/0+变异 M1/M3v2 </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>✅**审验通过+已合 main @2026-08-31**（审验 36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledg</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SkillGate JS_ARTIFACT 直接拒收[A2-2 落地]/</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2715,37 +2715,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UPG-59</t>
+          <t>UPG-61</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B 线蒸馏 MVP（改造计划第一阶段④ · 里程碑一承载）</t>
+          <t>vault.get 伪放行修（记住豁免与 fail-closed handler 不一致 · UI 禁用豁免勾选）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇改造线 B + 下篇 B-1~B-9；教训六字段/三分类/配额/过期）</t>
+          <t>定稿（UPG-53</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg59 **8da2907** 已 push origin 2 commit[2d</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg61 **b7c2e9d** 已 push origin；**修法②落地·四范围</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>✅**验收通过+审验通过 @2026-08-31**（9 项核物+73 套件 519/0/0 独立重跑+变异 V4/V3b/配额三杀独立复跑</t>
+          <t>✅ 方案定稿（UPG-53 审验员 L2 实测新发现 P1 + 设计师定夺修法；源码锚 @main 2780961：`MainActivit</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=V-4 ACTIVE-only 注入过滤/配额 MAX_LESSONS=</t>
+          <t xml:space="preserve">✅**审验通过+已合 main @2026-08-31**（审验 35→36：四范围核物+L1 74 套件 523/0/0 独立重跑+变异 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2762,12 +2762,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UPG-60</t>
+          <t>UPG-62</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A-2 三道门实现+元验证（改造计划第一阶段⑥）</t>
+          <t>多轮对话输入框失焦修（markstream WebView 抢焦点 · 焦点归还兜底）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-2 + 下篇 A2-1~A2-6/M-1~M-6；**前置 UPG-56/58/59**）</t>
+          <t>✅ 方案定稿（用户真机实测报障 + 设计师溯源 @main f975437）</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg60 **a8d1363** 已 push origin[5a7a576 三道门</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收通过+审验通过 @2026-08-31**（9f9466d 落档：9 项测试锚+77 套件 546/0/0+变异 M1/M3v2 </t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SkillGate JS_ARTIFACT 直接拒收[A2-2 落地]/</t>
+          <t>✅**已合 main @2026-08-31**（ff-only **82c778b** 已推 origin[feat/upg61-rb 链</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UPG-61</t>
+          <t>UPG-63</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>vault.get 伪放行修（记住豁免与 fail-closed handler 不一致 · UI 禁用豁免勾选）</t>
+          <t>第二阶段收口：弹窗基线 Z-5 + MULTI_CALL 分布统计 + M-1 真实重放补跑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>定稿（UPG-53</t>
+          <t xml:space="preserve">🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批 </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg61 **b7c2e9d** 已 push origin；**修法②落地·四范围</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（UPG-53 审验员 L2 实测新发现 P1 + 设计师定夺修法；源码锚 @main 2780961：`MainActivit</t>
+          <t xml:space="preserve">✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**审验通过+已合 main @2026-08-31**（审验 35→36：四范围核物+L1 74 套件 523/0/0 独立重跑+变异 </t>
+          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2856,12 +2856,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UPG-62</t>
+          <t>UPG-64</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>多轮对话输入框失焦修（markstream WebView 抢焦点 · 焦点归还兜底）</t>
+          <t>C 线效应注解首批（改造计划第二阶段·C 线）</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2871,22 +2871,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（用户真机实测报障 + 设计师溯源 @main f975437）</t>
+          <t xml:space="preserve">🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批 </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t xml:space="preserve">✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（ff-only **82c778b** 已推 origin[feat/upg61-rb 链</t>
+          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2903,12 +2903,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UPG-63</t>
+          <t>UPG-65</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>第二阶段收口：弹窗基线 Z-5 + MULTI_CALL 分布统计 + M-1 真实重放补跑</t>
+          <t>A-2 门 3 灰度自动化（改造计划第二阶段·接 B 生产信号）</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2918,22 +2918,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批 </t>
+          <t>✅ **设计 v2 定稿 @2026-09-02**（大神二轮 12/12 全采纳｜统计口径 v2 定稿：按 skill 去重/min20+</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg65 **f709ed9** 已 push origin[e4aa2a6 主体+</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b </t>
+          <t>】；【⛔ **部分打回 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg63 0580fa8 基</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
+          <t>合 main</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2950,37 +2950,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UPG-64</t>
+          <t>UPG-66</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C 线效应注解首批（改造计划第二阶段·C 线）</t>
+          <t>A-3 Judge 扩面（改造计划第二阶段·判定三类+反哺管道）</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批 </t>
+          <t>✅ 方案定稿（依据 合并版上篇 A-3 + 下篇 A3-1~A3-4；独立可随时插队）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg66 **1e604c7** 已 push origin[0438049 主体+</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b </t>
+          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg66 1e604c7 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
+          <t>✅ **已合 main@2026-09-01**（A-3 Judge 扩面｜AcceptanceJudge/M-JudgeModes/Age</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2997,37 +2997,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UPG-65</t>
+          <t>UPG-67</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A-2 门 3 灰度自动化（改造计划第二阶段·接 B 生产信号）</t>
+          <t>D 线 DAG 编排试点（改造计划第三阶段 · 预立待前置）</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>✅ **设计 v2 定稿 @2026-09-02**（大神二轮 12/12 全采纳｜统计口径 v2 定稿：按 skill 去重/min20+</t>
+          <t>✅ 方案定稿（依据 合并版上篇改造线 D + 下篇 D-1~D-5 + §十三 执行细则）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg65 **f709ed9** 已 push origin[e4aa2a6 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg67 **040c9d9** 已 push origin[a88510a 主体+</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>】；【⛔ **部分打回 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg63 0580fa8 基</t>
+          <t>【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG 6f330b5）：feat/upg67 040c9d9；</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>合 main</t>
+          <t>✅**已合 main @2026-08-31**（§六抽查=DagPlanner cycle 拒绝[Kahn 失败→Reject 不 han</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3044,42 +3044,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>UPG-66</t>
+          <t>UPG-68</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A-3 Judge 扩面（改造计划第二阶段·判定三类+反哺管道）</t>
+          <t>商业安全闸（原「商业防线批」——W2 白名单自动闸 + 商业面 fail-open 集中收口）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-3 + 下篇 A3-1~A3-4；独立可随时插队）</t>
+          <t>✅ **设计 v1 定稿 @2026-09-01**（`设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg66 **1e604c7** 已 push origin[0438049 主体+</t>
+          <t>✅ **C 完成 @2026-09-02**（补充节 V68-8/V69-4 补验：feat/upg68 `8380108`；变异亲杀 4/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg66 1e604c7 </t>
+          <t>✅ R1 复验带缺陷通过 @2026-09-01（feat/upg68 35b0008｜HIGH/M1/M2 三缺口 security_re</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>✅ **已合 main@2026-09-01**（A-3 Judge 扩面｜AcceptanceJudge/M-JudgeModes/Age</t>
+          <t>✅ **已合 main @c2defad @2026-09-02**（rebase origin/main 零冲突 + ff；V68-8/V</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026-09-01.md</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3091,37 +3091,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UPG-67</t>
+          <t>UPG-69</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>D 线 DAG 编排试点（改造计划第三阶段 · 预立待前置）</t>
+          <t>WebMCP 站点试点（mow.kim 工单站「站点=业务工具」第一站）</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇改造线 D + 下篇 D-1~D-5 + §十三 执行细则）</t>
+          <t>📌 新立 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造｜站点侧并行试点）｜待派单可认领</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg67 **040c9d9** 已 push origin[a88510a 主体+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG 6f330b5）：feat/upg67 040c9d9；</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（§六抽查=DagPlanner cycle 拒绝[Kahn 失败→Reject 不 han</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3138,92 +3138,46 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UPG-68</t>
+          <t>UPG-70</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>商业安全闸（原「商业防线批」——W2 白名单自动闸 + 商业面 fail-open 集中收口）</t>
+          <t>UI 组件化改造 · 地基（单一数据源/形态类归层/规范对齐）</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2
+→ **依据**：2026-09-02 调研 GitHub 成熟方案</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>✅ **设计 v1 定稿 @2026-09-01**（`设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026</t>
+          <t>✅ 方案 v1 定稿（用户调研后拍板「先修地基」）｜ 未派单</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>✅ **C 完成 @2026-09-02**（补充节 V68-8/V69-4 补验：feat/upg68 `8380108`；变异亲杀 4/</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>✅ R1 复验带缺陷通过 @2026-09-01（feat/upg68 35b0008｜HIGH/M1/M2 三缺口 security_re</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>✅ **已合 main @c2defad @2026-09-02**（rebase origin/main 零冲突 + ff；V68-8/V</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026-09-01.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>UPG-69</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>WebMCP 站点试点（mow.kim 工单站「站点=业务工具」第一站）</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>📌 新立 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造｜站点侧并行试点）｜待派单可认领</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>✅ 方案 v1 定稿（用户调研后拍板「先修地基」）｜ 未派单</t>
+          <t>✅ 方案 v2 定稿（2026-09-02：v1 经大神外部评审全部采纳｜5 补强+3 实施前置）｜ 未派单</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>✅ 方案 v2 定稿（2026-09-02：v1 经大神外部评审全部采纳｜5 补强+3 实施前置）｜ 未派单</t>
+          <t>✅ 方案 v2.1 定稿（大神二轮 9.2/10 建议可开工；4 口子全部钉死）｜ 未派单</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3149,12 +3149,15 @@
       <c r="C59" t="inlineStr">
         <is>
           <t>P2
+→ **验收**：验收员复验 带缺陷通过 @2026-09-02（ACCEPTANCE_LOG §P26：b47ecb8 隔离 worktree 复验 683/2/1 亲跑——基线 2 失败实证预存[merge-base b3fdcf9 对照 16/2 同红=收拢版带病，非本单引入]；A1 单一数据源+audit 亲跑[27 页/52 档/scoped 冲突 0]）
+→ **裁决**（用户拍板 2026-09-02）：基线 2 失败=**契约锚同步修**（AppearanceContractTest 适配收拢版硬编码 px 现实）→ 归属**阶段 1 维护单**；收拢版带病合入**责任链另查**（挂账）；记录=UPG70_裁决记录_2026-09-02.md
+→ **合入链**：15e53e6 → b3fdcf9（收拢版）→ 33ed4d9（assets 全量同步）→ 667cc80（UPG-70）；install-upg70-hooks.sh 已装（core.hooksPath=.githooks）
 → **依据**：2026-09-02 调研 GitHub 成熟方案</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>✅ 方案 v2.1 定稿（大神二轮 9.2/10 建议可开工；4 口子全部钉死）｜ 未派单</t>
+          <t>**裁决**（用户拍板 2026-09-02）：基线 2 失败=**契约锚同步修**（AppearanceContractTest 适配收拢</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3164,12 +3167,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>**验收**：验收员复验 带缺陷通过 @2026-09-02（ACCEPTANCE_LOG §P26：b47ecb8 隔离 worktree</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 已合 main @667cc80（feat/upg70 b47ecb8 cherry-pick 667cc80）｜ DONE（CI 首跑</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3149,6 +3149,7 @@
       <c r="C59" t="inlineStr">
         <is>
           <t>P2
+→ **审验**：✅ 通过 @2026-09-02（integrity_review=confirmed，与 ACCEPTANCE_LOG §P26 一致——合入版 667cc80 与 b47ecb8 patch-id 等价逐字节一致；基线 2 失败亲跑对照坐实=收拢版带病预存、UPG-70 零新增失败；A1/A2 核物全坐实）；3 条 P3 不阻塞（①交付报告落点已移 程序员\交付报告\ ②manifest 缺口→挂账 ③autocrlf 误报→CI 权威）
 → **验收**：验收员复验 带缺陷通过 @2026-09-02（ACCEPTANCE_LOG §P26：b47ecb8 隔离 worktree 复验 683/2/1 亲跑——基线 2 失败实证预存[merge-base b3fdcf9 对照 16/2 同红=收拢版带病，非本单引入]；A1 单一数据源+audit 亲跑[27 页/52 档/scoped 冲突 0]）
 → **裁决**（用户拍板 2026-09-02）：基线 2 失败=**契约锚同步修**（AppearanceContractTest 适配收拢版硬编码 px 现实）→ 归属**阶段 1 维护单**；收拢版带病合入**责任链另查**（挂账）；记录=UPG70_裁决记录_2026-09-02.md
 → **合入链**：15e53e6 → b3fdcf9（收拢版）→ 33ed4d9（assets 全量同步）→ 667cc80（UPG-70）；install-upg70-hooks.sh 已装（core.hooksPath=.githooks）

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3173,7 +3173,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>✅ 已合 main @667cc80（feat/upg70 b47ecb8 cherry-pick 667cc80）｜ DONE（CI 首跑</t>
+          <t>✅ 已合 main @667cc80（feat/upg70 b47ecb8 cherry-pick 667cc80）｜ DONE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3182,6 +3182,53 @@
         </is>
       </c>
       <c r="I59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UPG-71</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>元能力注册表 · 地基（MVP 资产 + Schema + 校验脚本）</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **审验 通过 @2026-09-02**（integrity_review 与 §P27 一致｜L1①/②/④/⑤ 亲跑全坐实；观察 </t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>✅ 已合 main @43fd00a（feat/upg71 快进合入+已 push）｜ DONE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,100 @@
         </is>
       </c>
       <c r="I60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>UPG-72</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>执行引擎 · S2 JobSpec+SchemaGate+READ 直跑（契约 v0.4 首接线单）</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>✅ **审验 通过 @2026-09-02**（§P28 一致：红线边界 diff 17 文件全模块零触碰、mov-exec-engine:</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>✅ **设计师合 main**：bd958d2（父=main 43fd00a，快进） **前置**：✅ UPG-71 已合 main @43</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>UPG-73</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>执行引擎 · S3 审批双快照核心（ApprovalSnapshot+首决胜+STALE）+ WRITE/MONEY 接审批（契约 v0.4 第二条接线单）</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>✅ **R1 修复交付 @2026-09-02**（程序员 feat/upg73 **add9e8c**：HIGH ApprovalBook</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>✅ **审验 通过 @2026-09-02**（§P29-R1 consistent：R1 范围 5 文件+273/-31 限 approv</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **已合 main @add9e8c**（快进合入+已 push；元能力线合序 71→72→73 完成）｜ DONE **前置**：✅ </t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3323,6 +3323,54 @@
         </is>
       </c>
       <c r="I62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UPG-75</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>审批交互收口（弹窗队列/待办列表/渠道统一）</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>P1
+→ **依据**：审批安全语义</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>✅ 方案 v1（用户拍板「立正式工单」｜2026-09-02 平板实测触发：fulfill.track 审批请求被 shell.exec 弹</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>✅ 方案 v1（用户拍板「立正式工单」｜2026-09-02 平板实测触发：fulfill.track 审批请求被 shell.exec 弹</t>
+          <t>📌 **已派 @2026-09-02**（用户拍板已派；认领人/分支以派单方为准）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **C 交付 @2026-09-02**（程序员 feat/upg75 **014c10f**，worktree mov-upg75，基</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>审验</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>待设计师合 main</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3371,6 +3371,54 @@
         </is>
       </c>
       <c r="I63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UPG-76</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>审批预审单模式（先扫一遍→审批单→同意就做）</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>P1
+→ **依据**：用户原话「运行中随时来个弹窗审批，多麻烦」——现行=运行中碎片审批；预审单=运行前一张单。与 UPG-75</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>✅ 方案 v1 概览（用户拍板「另立」｜审批体验方向升级：先扫描汇总一张审批单，同意=整批执行，不同意=不做；付钱不能先批=支付无论单子同意</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -3342,12 +3342,14 @@
       <c r="C63" t="inlineStr">
         <is>
           <t>P1
+→ **验收链**：验收员复验 带缺陷通过（§P30：A1 首决胜真 CAS[ApprovalService:196-200 AtomicReference + compareAndSet 非 check-then-act——UPG-73 教训内化]+FIFO 队列+待办 chip/面板+单源收口；A3-1 渠道端到端 JVM 无法覆盖[远程面触发不达 UI——模拟器环境阻塞]）→ ✅ 审验通过（014c10f 4 文件+650/-109 纯交互层；A1-1 变异亲杀[keep-latest→A1-1 红→还原复绿]；红线边界[only-once/fail-closed 零改动]）
+→ **残余**：A3 渠道端到端真机补验（留平板）；审批 UI 呈现通道缺口→转 UPG-76 统一设计；生成器派生项漂移→并入挂账-生成器产物漂移防护 → ✅ **验收员复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P30：014c10f 隔离 worktree——A1 首决胜真 CAS[AtomicReference+compareAndSet——UPG-73 教训内化]+A1-1 变异亲杀+定向 50/0 亲跑+red-line 8 条复核；**A3-1 真机端到端环境阻塞**[MCP 直调不达通知/弹窗 UI=UPG-73 呈现通道缺口延续+对话内触发器需 AI key]——待环境恢复补验；观察 2 建议派生项一次性入库+CI diff=0；**达待合→审验员→设计师**）
 → **依据**：审批安全语义</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>📌 **已派 @2026-09-02**（用户拍板已派；认领人/分支以派单方为准）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3357,12 +3359,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>审验</t>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P30：014c10f 隔离 worktree｜</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>待设计师合 main</t>
+          <t>✅ 已合 main @014c10f（feat/upg75 ff 合入；本地合入完成｜push 待网络恢复）｜ DONE（待 push）</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3391,36 +3391,818 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>📎 **方案 v2 增补 @2026-09-03**（设计师B「四钉子」，用户已认可：`设计师\方案设计\审批预审单_UPG-76_方案v</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03**（程序员 feat/upg76 **ed5088c**，worktree mov-upg76，基</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P32：ed5088c 隔离 worktree｜</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @6dd9161 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-76_审批预审单_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>DEL-UPG76-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UPG-77</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>审批判定单源化 + MCP 面死信通道处置 + SDK 契约纠偏（P0 安全）</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>📌 已派单·待认领（派单 `设计师\派单\UPG-77_审批判定单源化_派单_2026-09-03.md`；验收标准已冻结 `STD-UP</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03**（程序员 feat/upg77 **a7736b3**，worktree mov-upg77，基</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P31：a7736b3 隔离 worktree｜全量 </t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @a7736b3 @2026-09-03**（设计师B：ff-only 合入 + **已 push origin/m</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-77_审批判定单源化_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>DEL-UPG77-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UPG-78</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>生成器派生项入库保鲜 + CI diff=0 门禁（ApprovalRegistry 系）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P33：f1e2067 隔离 worktree 三锚行为级复现——A1 删 inventory→dependsOn 自动重建+722/2/1[GeneratorTest 不再红=**§P25 P2-A2 闭环**]+A3 连跑两遍 md5 一致+内容零 drift[status M=CRLF 假差异]+A2 CI git diff --exit-code 门禁；manifest_sha 一致 ok:True；**§P25/§P27/§P30 三处生成器漂移遗留根治闭环**；**达待合→设计师**[CI 首跑回看=A2 终证]）
+→ ✅ **已合 main @f1e2067 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（用户拍板「一起干了」；派单 `设计师\派单\UPG-78_生成器门禁_派单_2026-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P33：f1e2067 隔离 worktree 三锚行</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @f1e2067 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-78_生成器门禁_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UPG-79</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>审批呈现层组件化（ApprovalSurface + CardShell v1 视觉 + 渠道三修）</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P34：3925561 隔离 worktree——全量 734/2/1 亲跑一致+ApprovalLogic 9 用例+**变异④ 亲杀**[only-once 勾选禁则]+红线零改动；L2 CARD v2 采信程序员 4 图实证[同 AVD+呈现机制 UPG-77 已实证]+验收员抽验受阻如实记录；受限 3 项真机复验专项待环境恢复；**达待合→审验员→设计师**）
+→ ✅ **已合 main @5cf546d @2026-09-03**（设计师B：rebase f1e2067 后 ff-only 合入+**已 push origin/main**——rebase 前后 patch-id 4d645861 逐字节等价实证[3925561≡5cf546d]，合后定向 ApprovalLogic/ComponentContract/ApprovalQueue BUILD SUCCESSFUL；合前抽查[红线 15/§六]——STD-UPG-79-v1 sha=97f756ff 对账一致、§P34 证据=代码核物+变异亲杀实物；**用户视觉反馈处置**：截图灰带（#ECECEC）经网格采样+colors.xml+最终代码三方核对=**3925561 已无此灰带**（卡体纯白、勾选行无背景，与用户要求一致，截图疑为 WIP 版）——若新包仍见灰带按 P3 新单追）
+→ ⚖️ **审验发现两件裁决 @2026-09-03（设计师B）**：①**交付登记缺口**（DELIVERY_UPG79 报告/manifest/evidence 未落盘）=**程序员补证待办**（UPG-77 P3 先例，补齐后审验对账销项）；②**冷启动进程死语义**=设计内不可达（results 内存表随进程灭——completeFromBroadcast 空表空操作=fail-closed 不批准，安全方向成立），STD 场景②「杀进程→决策生效」口径不可达，转 挂账-upg79-冷启动语义补验（真机补验=Activity 存活冷路径 onNewIntent 决策生效+进程死=点击无效不批准，补验后 STD 派生 v2 修订口径）
+→ **依据**：总纲 v1「L2 呈现层=体系唯一黑洞」+ 评审增补——UPG-75 呈现为散装内联实现</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（总纲 R1=审批体系最后一块，用户拍板派出；派单 `设计师\派单\UPG-79_审批呈</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P34：3925561 隔离 worktree｜</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @5cf546d @2026-09-03**（设计师B：rebase f1e2067 后 ff-only 合入+**</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-79_审批呈现层组件化_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UPG-80</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AI 对话链路诊断修复（模拟器 DeepSeek 链路）+ 联动补验</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>P1（验证环境根） → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P36：零代码诊断单复核通过——A1 诊断证据在档[AI 未回复挂账可销]；**A3 UPG-76 场景① 全链实证补入**[预审单四段全实证——§P32 场景① 阻塞解除]；场景③④✅+② ⛔ payment mock 待接；**removeAll 缺陷实锤转单**[批量写同工具名被砍单——MainActivity:5543]）
+→ ✅ **已闭环 @2026-09-03**（零代码单无合 main 对象：验收员 §P36 + 审验 confirmed——A1 诊断 logcat 全链路健康在档[首查截断误判取全文核实]、联动 UPG-76 L3 ①③④ 全实证[预审单六锚/已批执行+未批阻断+计划外新窗/门槛单步弹窗]、脱敏闸 54 文件零非打码 key；挂账-模拟器AI未回复 已销、挂账-upg76-L3 ①③④ 已实证仅剩② MONEY 转 挂账-payment.pay handler缺失；审验发现① removeAll 缺陷已转 UPG-85 P1）
+→ **依据**：挂账-模拟器AI未回复（2026-08-26，P1）+ 挂账-upg76-L3真机补验四场景（随 main 联动裁决）——同环境根；阻塞全部对话面真机验收
+→ 🆕 **已认领 @2026-09-03**（程序员 Claude/wmw0027，主仓库 0027-mov 诊断先行[可能零代码]；如需改代码开 worktree mov-upg80 / branch feat/upg80，基 main f1e2067[UPG-78 已合入]；A1 诊断[emulator-5556 logcat 证据链→根因] → A2 修复[配置/代码] → A3 实证+UPG-76 L3 四场景联动补验；脱敏红线全程
+→ ✅ **C 交付 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-80_AI对话链路修复_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03**（程序员 Claude/wmw0027，**零代码改动**｜A2 判定纯环境/配置面，无代码缺陷</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P36：零代码诊断单复核通过｜A1 诊断证据在档[AI</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>✅ **已闭环 @2026-09-03**（零代码单无合 main 对象：验收员 §P36 + 审验 confirmed｜A1 诊断 log</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-80_AI对话链路修复_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UPG-81</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>基线 2 失败契约锚同步修（AppearanceContractTest 适配收拢版现实）</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P37：3339c4b 隔离 worktree——全量 **734/0/1 亲跑终验，基线预存 2 失败消除**+契约锚与现实对齐非消音[L1-10 认账收拢现实+M-U50-5 改锚 render-only 真实表达]+**K1 亲杀**[旧断言回潮红→还原]+manifest_sha 一致；**达待合→设计师**——合后全量回归=0 失败基线） → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39：8609d69 隔离 worktree——**§P36 转单 P1 闭环**：removeAll→indexOfFirst+removeAt+&gt;=0 守卫[同 tool 后续保留可勾选]+取舍论证实锤+全量 730/2/1 亲跑一致[PlanApproval 35]+**M1 亲杀**[failed=3 与申报一致]；L2 真机呈现环境阻塞登记[需 AI key]；**达待合→审验员→设计师**）
+→ **依据**：用户拍板裁决（UPG70_裁决记录 裁决项 1）——基线 2 失败（L2-9 1B + M-U50-5，收拢版带病合入遗留）处置=契约锚同步修，归属阶段 1 维护单；消灭「pre-existing」口径恢复全量 0 失败
+→ 🆕 **已认领 @2026-09-03 08:55**（程序员 Claude/wmw0027，worktree mov-upg81，branch feat/upg81，2026-09-03 认领登记，基 main 5cf546d[UPG-79 已合入]；按派单施工：修前复跑实证 L2-9 1B + M-U50-5 两红留 XML → 逐案断言适配收拢版现实（来源文件:行号）→ 修后全量 --rerun-tasks 0 失败 → 亲杀锚断言破坏必红 → Token/KV 0/0 → 交付报告 + 登记两表）
+→ ✅ **C 交付 @2026-09-03 09:19**</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-81_基线契约锚同步修_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03 09:19**（程序员 Claude/wmw0027，commit 3339c4b @feat/u</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39：8609d69 隔离 worktree</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>合 main</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-81_基线契约锚同步修_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>DEL-UPG81-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UPG-82</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>执行引擎 S4：ApprovalGroup 双状态机 + EXPIRED + EdgePolicy 失败传播（能力级）</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree——模块 88/0 亲跑[S2/S3 60 零回归+S4 28]+组簿 compute 单桶锁（§P29 教训前置）+**M3 亲杀**[组闸删除→2 红——S3 绕道封死]+M1/M2/M4 采信+S2/S3 零改动辨析+coverage FULL；**达待合→审验员→设计师[合序 71→72→73R1→82]**）
+→ ✅ **已合 main @fe8cd45 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-82_执行引擎S4_派单_2026-09-03.md`；</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 10:17**（feat/upg82 **6e9f90e** 已 push origin，基底 ma</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree｜模块 </t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @fe8cd45 @2026-09-03**（设计师B：验收 §P38+审验 confirmed 达待合后｜reba</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-82_执行引擎S4_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DEL-UPG82-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UPG-83</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CODE 模式 tool.call 受控通道（SDK 弃 curl 匝道）</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>❌ **已取消 @2026-09-03**（用户拍板「只要两种模式：经典+极简，极简只是画面极简不阉割能力」｜5→2 模式收敛转 UPG-8</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UPG-84</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>模式收敛 5→2（工具面去模式化 + SDK 匝道段删除）</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P35：e95472f 隔离 worktree——全量 724/2/1 亲跑一致[UPG-81 未开工口径成立]+Upg84ModeConverge 6 锚全绿+五模式零残留[ToolSdkGenerator 部分保留=tool.help 零缩减待追认]+set_mode 全链路退役+生成器重生成同步+**变异锚① 亲杀**+快速/深思 reasoning 绑模式；用户平板 L3 留用户；**达待合→审验员→设计师**）
+→ **依据**：五模式循环（both/code/native/hardware/causal，E3 时代工程产物）从用户面退役——工具面固定全量 both；code 模式退役 → UPG-83（tool.call 补丁单）取消（根因消除优于补丁）；两态开关「经典⇄极简」归极简批阶段 1（送审稿入口决策点，不在本单）
+→ 🆕 **已认领 @2026-09-03 08:04**（程序员 Claude/wmw0027，worktree mov-upg84，branch feat/upg84，2026-09-03 认领登记，基 main 5cf546d[UPG-79 已合入]；按派单 A1-A5 施工——工具面固定全量+SDK 匝道段删除+快速/深思收敛[STD v2]+两态开关本单不断[归极简批]）
+→ ✅ **C 交付 @2026-09-03 08:33**</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（用户拍板「只要两种模式：经典+极简，极简只是画面极简不能阉割能力」；派单 `设计师\派</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03 08:33**（程序员 Claude/wmw0027，commit e95472f @feat/u</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P35 + 审验 confirmed：e9547</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @8647ee9 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-84_模式收敛_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>DEL-UPG84-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UPG-85</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>预审单 removeAll 缺陷修复（同 tool 多步骤被误移除）</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>P1
-→ **依据**：用户原话「运行中随时来个弹窗审批，多麻烦」——现行=运行中碎片审批；预审单=运行前一张单。与 UPG-75</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>✅ 方案 v1 概览（用户拍板「另立」｜审批体验方向升级：先扫描汇总一张审批单，同意=整批执行，不同意=不做；付钱不能先批=支付无论单子同意</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
+→ ✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39 + 审验 confirmed：8609d69 修复坐实[indexOfFirst+removeAt+守卫]、取舍论证亲读成立、契约锚含防脱钩绑定、M1 亲杀独立复验 3 红→还原零残留、全量 730/2/1 一致；§P36 转单 P1「发现→转单→修复→验收」全链闭环；**达待合→设计师**）
+→ ✅ **已合 main @ad1e0a8 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-85_预审单removeAll缺陷修复_派单_2026-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 17:05**（feat/upg85 **8609d69** 已 push origin，基底 ma</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39 + 审验 confirmed：8609d</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @ad1e0a8 @2026-09-03**（设计师B：rebase fab7d29 零冲突+patch-id 37</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-85_预审单removeAll缺陷修复_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>DEL-UPG85-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UPG-86</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>manifest 治理（存量补齐 + 审验.py 机器可验性强化）</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>P2
+→ ✅ **已闭环 @2026-09-03**（验收+审验通过：--manifest-self-test PASS 4/4+存量治理亲验[82/85/87 重验 ok:True 三连+缺失显式 missing 不造假]+双挂账销项落表；工单系统侧无合 main 对象）
+→ 🆕 **已认领 @2026-09-03 18:50**</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-86_manifest治理_派单_2026-09-03.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 19:0x**（治理 commit **13434e7**[工单系统仓库]；三件全交：①**审验.p</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>✅ **已闭环 @2026-09-03**（验收+审验通过：--manifest-self-test PASS 4/4+存量治理亲验[82/</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>合 main对象）</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-86_manifest治理_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>DEL-UPG86-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UPG-87</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>内置包启停真实生效（宿主工具组纳入 builtin 包机制）</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree——全量 **741/0/1 亲跑[0 失败基线兑现首单]**+四件核物[三宿主组纳入/hostPackTools 单源/syncHostBuiltinTools 启停链/默认全量]+McpMarketTest 2→5 零回归[挂账-upg41v2 销项]+**变异复杀如实**[M3 机制采信/M1 未复现红采信 XML 口径]；真机启停 UI 走查=验收员持有待办；**达待合→审验员→设计师[verify-hash 终态]**）
+→ ✅ **已合 main @fea2fae @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（设计师B 溯源实证后出卡；派单 `设计师\派单\UPG-87_内置包启停_派单_202</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 18:4x**（feat/upg87 **fea2fae** 已 push origin，基底 ma</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree｜全量 </t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @fea2fae @2026-09-03**（设计师B：验收 §P41+审验 confirmed[变异环 M1/M3</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-87_内置包启停_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>DEL-UPG87-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>UPG-88</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>极简批阶段 1（ASR + 极简主页生产化 + 两态开关点亮 + 快速提示词）</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P42：43e5756 三提交链隔离 worktree——全量 **748/0/1 亲跑一致**+Upg84ModeConverge 6 锚全绿[契约升级非消音复核]+R1 自纠实锤+**变异复验 5 轮未复现红如实标注**[采信程序员红案]+L2 四场景采信[未独立复跑如实标注]；coverage PARTIAL 裁决位维持[ASR 真人发声]；**达待合→审验员→设计师**）
+→ ✅ **已合 main @43e5756 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（产品主线；设计文=极简送审稿+用户拍板「两模式/不阉割能力」；派单 `设计师\派单\U</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 23:0x**（feat/upg88 **43e5756** 已 push origin[施工 90</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>**用户指示模拟器自测**（ASR 真实语音转写=物理受限转验收员持有｜coverage PARTIAL 设计师裁决位申报在报告 §七）；T</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @43e5756 @2026-09-03**（设计师B：验收 §P42+审验 confirmed[契约升级非消音精读</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-88_极简批阶段1_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>DEL-UPG88-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UPG-89</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>极简呈现引擎（PresentationRegistry + core.js 呈现栈 + Intent Router + Response Splitter + 三骨架）</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>P1
+→ **依据**：极简呈现交互体系 v1.1（大神评审 8.8/10 吸收版：Surface 抽象/Transient-Persistent/PresentationPolicy/Intent Router/Voice EOU/解析隔离/presentation_intent 全落）+ 用户四条拍板（两模式/不阉割/引擎规则驱动/卡片浮于主页+输入能力常驻）；demo v3 视觉基准
+→ **防撞**：与 UPG-88 同主页面——建议 88 先合或同程序员串行；与 85/87 零重叠</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>⏸️ **挂单 @2026-09-03**（用户拍板：先不派，收前面尾巴｜尾批清完再启；派单/STD 已备妥 [原派单 @2026-09-0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-89_极简呈现引擎_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>UPG-90</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>尾巴批修（S-06 打回项 ②⑧ + C7 基线测试非确定性）</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>P2
+→ 🆕 **已认领 @2026-09-03 23:22**（程序员 Claude/wmw0027，worktree mov-upg90，branch feat/upg90，基 main fea2fae；按派单施工：S-06 ②引号闭合+⑧四死文件 git rm+C7 确定性治理——零 app 代码面）→ ✅**C 完成 @2026-09-04 00:1x**（feat/upg90 **1845cb7** 已 push origin，基 main fea2fae；三件全交：①**S-06 ②**[index.html:199 `href="explorer.html&gt;`→引号闭合+**链接断言测试**（提取 href 可解析——未闭合引号吞标签尾即红+explorer.html 目标在库不 404）] ②**S-06 ⑧**[make_guide.py/make_merchant.py git rm 真实删除；sms-probe.js/run-pc.sh git ls-files 实证**库内已不存在**（历史已删=现状满足真实删除语义）；契约测试四名零残留] ③**C7 确定性治理（STD 方案①）**[jsonl 剔除 time 字段（实时时钟非确定源——事件序/类型/seq 保留基线比对价值不降）；generateBaselineInto 可重入抽取+**守卫测试**「连跑两遍产物字节一致」[写回 time 即红]；**取舍声明**：不选方案②[产物归 build/ 失去入库可追溯]——报告 §一.3]；**亲杀 2 锚**[M1 恢复未闭合引号→链接断言红/M2 写回 time→守卫红；还原复绿]；**两跑零 M**[--rerun-tasks×2 全绿+c7_baseline 30 文件零 M 实证；工作区余 5 CRLF 假差异[diff 实质零，worktree checkout 行尾现象如实申报]]；全量 **101 套件 744/0/1 全绿**[0 失败基线；U90 基于不含 U88 的 main 数字自洽]；Token/KV 0/0；S-06 卡 ②⑧+挂账-C7 销项对应报告 §五；DEL-UPG90-20260903-001[code=1845cb7/artifact 不适用/manifest 见案]；报告 DELIVERY_UPG90_2026-09-03.md；**已登记两个表**）——待验收员验收（L1 复核+变异复杀+mow.kim 部署后 explorer 链接点验[或本地静态点验]+合后 verify-hash 终态复核）
+→ **依据**：S-06 打回项 ②⑧（index.html:199 引号未闭合申报失实+四死文件未 git rm；ACCEPTANCE_LOG ef3ad38）+ 挂账-C7基线测试非确定性输出（C7BaselineGenerationTest:106 产物每次全量重跑变 M）；零 app 代码面与在施单全不撞
+→ **排程注**：UPG-41 v2 两 P3</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（尾巴清零批；派单 `设计师\派单\UPG-90_尾巴批修_派单_2026-09-03.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-04 00:1x**（feat/upg90 **1845cb7** 已 push origin，基 mai</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>**依据**：S-06 打回项 ②⑧（index.html:199 引号未闭合申报失实+四死文件未 git rm；ACCEPTANCE_LO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-90_尾巴批修_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>DEL-UPG90-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UPG-91</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>我的资产页注册制重排（tab 导航+二级收缩裸列表+点值脱敏+诚实空态+假数据回落删除+令牌迁移）</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>P2
+→ 🆕 **已认领 @2026-09-04 00:3x**（程序员 Claude/wmw0027，worktree mov-upg91，branch feat/upg91，基 main 43e5756[含 UPG-88 合入]；按派单施工：demo v6 重排+demoBridge 删除+令牌迁移+4 变异锚——真机实拍五场景尽力/受限如实）→ ✅**C 完成 @2026-09-04 01:4x**（feat/upg91 **34a2dda** 已 push origin[远端顶=4dc19e7 锚④强化 ls-remote 铁证；施工 4d1449b→R1 形态消费修复 34a2dda→锚④断言强化 4dc19e7]，基 main 43e5756；六件全交：①**tab 导航**[demo v6 下划线 tab：凭据真实计数 credGrouped 求和/证件照 0/2/未上线灰显 tab.off——锚④双断言：模板插值 {{ c.count }}+reduce 求和逻辑] ②**二级收缩组行**[opened=ref({}) 默认收起——平台·N 项›+chev 旋转+明细行 hairline；**忠实真实桥**：asset.credentials 仅返回 platform+mask 单行明细/平台——不造 demo 明细假结构] ③**点值脱敏往返**[删👁按钮——点脱敏值=asset.credPeek（→vault.get 审批链零改动）真值 white-space:pre-line 显示（values[cred.平台]=账号/密码多行）再点收回 mask；revealed 往返态] ④**诚实空态**[桥空=「还没有任何资产」+「只存在这台设备上，读取时每次需你确认」+「添加凭据」主按钮——demoBridge 假数据回落**整段删除**（红线 18 同族；浏览器预览态同样诚实）] ⑤**令牌迁移**[硬编码色值全清：#eef7f4/#1c7a5f 绿横幅**消亡**+#fff/#eceff4/#222/#999/#f4f7fa/#eef1f5/#f2f4f8/#dfe4ea/#334/#98a2b3/#4c88ff/#cfd6df/#05070a 及 CSS var fallback hex 全清——样式全走 tokens 变量（var(--text/text2/text3/line/primary/bg)）] ⑥**零图标**[Icon 组件 import+全部 &lt;Icon&gt; 删除——**产物 Icon chunk 消失实证**（vite build 后 assets 页产物无 Icon-*.js）]；**变异 4 锚亲杀**[M1 恢复 demoBridge→契约红/M2 塞回 hex→红/M3 opened 初始展开→红/M4 删 tab 计数渲染→红[首版锚④断言弱被实测暴露逃逸→**强化为渲染插值+求和逻辑双断言补杀**——测试有效性升级在案]；还原复绿]；**R1 修复**[全量回归发现 AppearanceContractTest L2-9 红（首版删除 acard/alist 形态消费）——**v6 结构不弃机制**：acardCls 绑 tab 条+alistCls 绑组行列表+ui.getProfile 回读恢复 commit 34a2dda——L2-9 零回归]；产物链[vite build+sync-pages 103 文件入库哨兵零越界+assembleDebug 绿]；全量 **103 套件 752/0/1 全绿**[748[U88]+4[U91 契约]=752]；真机实拍五场景**转验收员持有**[如实申报：L2 定级真机走查属验收员职责+开发时段平板被占——不虚报]；不动 AssetsSheet 宿主/白名单/vault.get 审批链/credPeek 桥语义[红线 2 兑现]；Token/KV 0/0[页面 WebView 内不经 agent 面]；coverage_status=**FULL**[共享面=资产页面+产物+UPG-50 1C 形态消费面（R1 恢复）——AppearanceContract 零回归实证]；verify-hash not-ancestor 如实申报；DEL-UPG91-20260904-001[code=34a2dda/manifest 见案]；报告 DELIVERY_UPG91_2026-09-04.md；**已登记两个表**）——待验收员验收（L1 复核+变异复杀+真机实拍五场景[持有]+合后 verify-hash 终态复核）
+→ **依据**：四病灶实证——大片黑/空白（空态缺失+tokens body #05070a 透出）/类目卡硬三列挤压截断/硬编码绿横幅+卡色值（AssetsPage.vue:169-173）/**demoBridge 假数据回落（桥空显示演示凭据=红线 18 同族）**；视觉基准=demo v6（tab 导航+二级收缩+点值脱敏+零图标+诚实空态）
+→ **拍板记录**：注册制结构归 tab 栏</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（用户实测「体验感很差」→ 四病灶诊断 → 六轮迭代 demo v6 拍板；派单 `设计</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-04 01:4x**（feat/upg91 **34a2dda** 已 push origin[远端顶=4</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>验收员验收（L1 复核+变异复杀+真机实拍五场景[持有]+合后 verify-hash 终态复核）</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-91_我的资产页重排_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>DEL-UPG91-20260904-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>UPG-92</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>manifest 硬闸化（deliver-gen 源头合规 + 自检内置）</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>P1
+→ 🆕 **已认领 @2026-09-03 23:46**（程序员 Kimi/kimi-cli，worktree mov-upg92，branch feat/upg92，基 main 607bf4e；按派单施工：deliver-gen 源头合规[路径裸串/条带 sha256/绑定值写入]+自检内置硬闸[不合规=拒绝产出]——工单系统侧工具链，零 app 代码面）
+→ **依据**：UPG-86 治理完成 4 小时后 UPG-88 交付 manifest 再度失效</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（manifest 同族第六现｜红线 23 自检步声称未执行，改机制硬闸；派单 `设计师</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>🆕 **已认领 @2026-09-03 23:46**（程序员 Kimi/kimi-cli，worktree mov-upg92，bran</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>审验员三建议取最硬：deliver-gen 源头合规+自检内置（机器产出即合规不靠人）；本单自身 manifest 必须经新闸产出（吃自己狗</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-92_manifest硬闸化_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3391,36 +3391,864 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>📎 **方案 v2 增补 @2026-09-03**（设计师B「四钉子」，用户已认可：`设计师\方案设计\审批预审单_UPG-76_方案v</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03**（程序员 feat/upg76 **ed5088c**，worktree mov-upg76，基</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P32：ed5088c 隔离 worktree｜</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @6dd9161 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-76_审批预审单_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>DEL-UPG76-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UPG-77</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>审批判定单源化 + MCP 面死信通道处置 + SDK 契约纠偏（P0 安全）</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>📌 已派单·待认领（派单 `设计师\派单\UPG-77_审批判定单源化_派单_2026-09-03.md`；验收标准已冻结 `STD-UP</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03**（程序员 feat/upg77 **a7736b3**，worktree mov-upg77，基</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P31：a7736b3 隔离 worktree｜全量 </t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @a7736b3 @2026-09-03**（设计师B：ff-only 合入 + **已 push origin/m</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-77_审批判定单源化_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>DEL-UPG77-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UPG-78</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>生成器派生项入库保鲜 + CI diff=0 门禁（ApprovalRegistry 系）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P33：f1e2067 隔离 worktree 三锚行为级复现——A1 删 inventory→dependsOn 自动重建+722/2/1[GeneratorTest 不再红=**§P25 P2-A2 闭环**]+A3 连跑两遍 md5 一致+内容零 drift[status M=CRLF 假差异]+A2 CI git diff --exit-code 门禁；manifest_sha 一致 ok:True；**§P25/§P27/§P30 三处生成器漂移遗留根治闭环**；**达待合→设计师**[CI 首跑回看=A2 终证]）
+→ ✅ **已合 main @f1e2067 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（用户拍板「一起干了」；派单 `设计师\派单\UPG-78_生成器门禁_派单_2026-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P33：f1e2067 隔离 worktree 三锚行</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @f1e2067 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-78_生成器门禁_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UPG-79</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>审批呈现层组件化（ApprovalSurface + CardShell v1 视觉 + 渠道三修）</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P34：3925561 隔离 worktree——全量 734/2/1 亲跑一致+ApprovalLogic 9 用例+**变异④ 亲杀**[only-once 勾选禁则]+红线零改动；L2 CARD v2 采信程序员 4 图实证[同 AVD+呈现机制 UPG-77 已实证]+验收员抽验受阻如实记录；受限 3 项真机复验专项待环境恢复；**达待合→审验员→设计师**）
+→ ✅ **已合 main @5cf546d @2026-09-03**（设计师B：rebase f1e2067 后 ff-only 合入+**已 push origin/main**——rebase 前后 patch-id 4d645861 逐字节等价实证[3925561≡5cf546d]，合后定向 ApprovalLogic/ComponentContract/ApprovalQueue BUILD SUCCESSFUL；合前抽查[红线 15/§六]——STD-UPG-79-v1 sha=97f756ff 对账一致、§P34 证据=代码核物+变异亲杀实物；**用户视觉反馈处置**：截图灰带（#ECECEC）经网格采样+colors.xml+最终代码三方核对=**3925561 已无此灰带**（卡体纯白、勾选行无背景，与用户要求一致，截图疑为 WIP 版）——若新包仍见灰带按 P3 新单追）
+→ ⚖️ **审验发现两件裁决 @2026-09-03（设计师B）**：①**交付登记缺口**（DELIVERY_UPG79 报告/manifest/evidence 未落盘）=**程序员补证待办**（UPG-77 P3 先例，补齐后审验对账销项）；②**冷启动进程死语义**=设计内不可达（results 内存表随进程灭——completeFromBroadcast 空表空操作=fail-closed 不批准，安全方向成立），STD 场景②「杀进程→决策生效」口径不可达，转 挂账-upg79-冷启动语义补验（真机补验=Activity 存活冷路径 onNewIntent 决策生效+进程死=点击无效不批准，补验后 STD 派生 v2 修订口径）
+→ **依据**：总纲 v1「L2 呈现层=体系唯一黑洞」+ 评审增补——UPG-75 呈现为散装内联实现</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（总纲 R1=审批体系最后一块，用户拍板派出；派单 `设计师\派单\UPG-79_审批呈</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P34：3925561 隔离 worktree｜</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @5cf546d @2026-09-03**（设计师B：rebase f1e2067 后 ff-only 合入+**</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-79_审批呈现层组件化_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UPG-80</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AI 对话链路诊断修复（模拟器 DeepSeek 链路）+ 联动补验</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>P1（验证环境根） → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P36：零代码诊断单复核通过——A1 诊断证据在档[AI 未回复挂账可销]；**A3 UPG-76 场景① 全链实证补入**[预审单四段全实证——§P32 场景① 阻塞解除]；场景③④✅+② ⛔ payment mock 待接；**removeAll 缺陷实锤转单**[批量写同工具名被砍单——MainActivity:5543]）
+→ ✅ **已闭环 @2026-09-03**（零代码单无合 main 对象：验收员 §P36 + 审验 confirmed——A1 诊断 logcat 全链路健康在档[首查截断误判取全文核实]、联动 UPG-76 L3 ①③④ 全实证[预审单六锚/已批执行+未批阻断+计划外新窗/门槛单步弹窗]、脱敏闸 54 文件零非打码 key；挂账-模拟器AI未回复 已销、挂账-upg76-L3 ①③④ 已实证仅剩② MONEY 转 挂账-payment.pay handler缺失；审验发现① removeAll 缺陷已转 UPG-85 P1）
+→ **依据**：挂账-模拟器AI未回复（2026-08-26，P1）+ 挂账-upg76-L3真机补验四场景（随 main 联动裁决）——同环境根；阻塞全部对话面真机验收
+→ 🆕 **已认领 @2026-09-03**（程序员 Claude/wmw0027，主仓库 0027-mov 诊断先行[可能零代码]；如需改代码开 worktree mov-upg80 / branch feat/upg80，基 main f1e2067[UPG-78 已合入]；A1 诊断[emulator-5556 logcat 证据链→根因] → A2 修复[配置/代码] → A3 实证+UPG-76 L3 四场景联动补验；脱敏红线全程
+→ ✅ **C 交付 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-80_AI对话链路修复_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03**（程序员 Claude/wmw0027，**零代码改动**｜A2 判定纯环境/配置面，无代码缺陷</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P36：零代码诊断单复核通过｜A1 诊断证据在档[AI</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>✅ **已闭环 @2026-09-03**（零代码单无合 main 对象：验收员 §P36 + 审验 confirmed｜A1 诊断 log</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-80_AI对话链路修复_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UPG-81</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>基线 2 失败契约锚同步修（AppearanceContractTest 适配收拢版现实）</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P37：3339c4b 隔离 worktree——全量 **734/0/1 亲跑终验，基线预存 2 失败消除**+契约锚与现实对齐非消音[L1-10 认账收拢现实+M-U50-5 改锚 render-only 真实表达]+**K1 亲杀**[旧断言回潮红→还原]+manifest_sha 一致；**达待合→设计师**——合后全量回归=0 失败基线） → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39：8609d69 隔离 worktree——**§P36 转单 P1 闭环**：removeAll→indexOfFirst+removeAt+&gt;=0 守卫[同 tool 后续保留可勾选]+取舍论证实锤+全量 730/2/1 亲跑一致[PlanApproval 35]+**M1 亲杀**[failed=3 与申报一致]；L2 真机呈现环境阻塞登记[需 AI key]；**达待合→审验员→设计师**）
+→ **依据**：用户拍板裁决（UPG70_裁决记录 裁决项 1）——基线 2 失败（L2-9 1B + M-U50-5，收拢版带病合入遗留）处置=契约锚同步修，归属阶段 1 维护单；消灭「pre-existing」口径恢复全量 0 失败
+→ 🆕 **已认领 @2026-09-03 08:55**（程序员 Claude/wmw0027，worktree mov-upg81，branch feat/upg81，2026-09-03 认领登记，基 main 5cf546d[UPG-79 已合入]；按派单施工：修前复跑实证 L2-9 1B + M-U50-5 两红留 XML → 逐案断言适配收拢版现实（来源文件:行号）→ 修后全量 --rerun-tasks 0 失败 → 亲杀锚断言破坏必红 → Token/KV 0/0 → 交付报告 + 登记两表）
+→ ✅ **C 交付 @2026-09-03 09:19**</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-81_基线契约锚同步修_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03 09:19**（程序员 Claude/wmw0027，commit 3339c4b @feat/u</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39：8609d69 隔离 worktree</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>合 main</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-81_基线契约锚同步修_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>DEL-UPG81-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UPG-82</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>执行引擎 S4：ApprovalGroup 双状态机 + EXPIRED + EdgePolicy 失败传播（能力级）</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree——模块 88/0 亲跑[S2/S3 60 零回归+S4 28]+组簿 compute 单桶锁（§P29 教训前置）+**M3 亲杀**[组闸删除→2 红——S3 绕道封死]+M1/M2/M4 采信+S2/S3 零改动辨析+coverage FULL；**达待合→审验员→设计师[合序 71→72→73R1→82]**）
+→ ✅ **已合 main @fe8cd45 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-82_执行引擎S4_派单_2026-09-03.md`；</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 10:17**（feat/upg82 **6e9f90e** 已 push origin，基底 ma</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree｜模块 </t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @fe8cd45 @2026-09-03**（设计师B：验收 §P38+审验 confirmed 达待合后｜reba</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-82_执行引擎S4_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DEL-UPG82-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UPG-83</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CODE 模式 tool.call 受控通道（SDK 弃 curl 匝道）</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>❌ **已取消 @2026-09-03**（用户拍板「只要两种模式：经典+极简，极简只是画面极简不阉割能力」｜5→2 模式收敛转 UPG-8</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UPG-84</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>模式收敛 5→2（工具面去模式化 + SDK 匝道段删除）</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P35：e95472f 隔离 worktree——全量 724/2/1 亲跑一致[UPG-81 未开工口径成立]+Upg84ModeConverge 6 锚全绿+五模式零残留[ToolSdkGenerator 部分保留=tool.help 零缩减待追认]+set_mode 全链路退役+生成器重生成同步+**变异锚① 亲杀**+快速/深思 reasoning 绑模式；用户平板 L3 留用户；**达待合→审验员→设计师**）
+→ **依据**：五模式循环（both/code/native/hardware/causal，E3 时代工程产物）从用户面退役——工具面固定全量 both；code 模式退役 → UPG-83（tool.call 补丁单）取消（根因消除优于补丁）；两态开关「经典⇄极简」归极简批阶段 1（送审稿入口决策点，不在本单）
+→ 🆕 **已认领 @2026-09-03 08:04**（程序员 Claude/wmw0027，worktree mov-upg84，branch feat/upg84，2026-09-03 认领登记，基 main 5cf546d[UPG-79 已合入]；按派单 A1-A5 施工——工具面固定全量+SDK 匝道段删除+快速/深思收敛[STD v2]+两态开关本单不断[归极简批]）
+→ ✅ **C 交付 @2026-09-03 08:33**</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（用户拍板「只要两种模式：经典+极简，极简只是画面极简不能阉割能力」；派单 `设计师\派</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>✅ **C 交付 @2026-09-03 08:33**（程序员 Claude/wmw0027，commit e95472f @feat/u</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P35 + 审验 confirmed：e9547</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @8647ee9 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-84_模式收敛_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>DEL-UPG84-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UPG-85</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>预审单 removeAll 缺陷修复（同 tool 多步骤被误移除）</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>P1
-→ **依据**：用户原话「运行中随时来个弹窗审批，多麻烦」——现行=运行中碎片审批；预审单=运行前一张单。与 UPG-75</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>✅ 方案 v1 概览（用户拍板「另立」｜审批体验方向升级：先扫描汇总一张审批单，同意=整批执行，不同意=不做；付钱不能先批=支付无论单子同意</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
+→ ✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39 + 审验 confirmed：8609d69 修复坐实[indexOfFirst+removeAt+守卫]、取舍论证亲读成立、契约锚含防脱钩绑定、M1 亲杀独立复验 3 红→还原零残留、全量 730/2/1 一致；§P36 转单 P1「发现→转单→修复→验收」全链闭环；**达待合→设计师**）
+→ ✅ **已合 main @ad1e0a8 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-85_预审单removeAll缺陷修复_派单_2026-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 17:05**（feat/upg85 **8609d69** 已 push origin，基底 ma</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39 + 审验 confirmed：8609d</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @ad1e0a8 @2026-09-03**（设计师B：rebase fab7d29 零冲突+patch-id 37</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-85_预审单removeAll缺陷修复_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>DEL-UPG85-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UPG-86</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>manifest 治理（存量补齐 + 审验.py 机器可验性强化）</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>P2
+→ ✅ **已闭环 @2026-09-03**（验收+审验通过：--manifest-self-test PASS 4/4+存量治理亲验[82/85/87 重验 ok:True 三连+缺失显式 missing 不造假]+双挂账销项落表；工单系统侧无合 main 对象）
+→ 🆕 **已认领 @2026-09-03 18:50**</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-86_manifest治理_派单_2026-09-03.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 19:0x**（治理 commit **13434e7**[工单系统仓库]；三件全交：①**审验.p</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>✅ **已闭环 @2026-09-03**（验收+审验通过：--manifest-self-test PASS 4/4+存量治理亲验[82/</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>合 main对象）</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-86_manifest治理_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>DEL-UPG86-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UPG-87</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>内置包启停真实生效（宿主工具组纳入 builtin 包机制）</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree——全量 **741/0/1 亲跑[0 失败基线兑现首单]**+四件核物[三宿主组纳入/hostPackTools 单源/syncHostBuiltinTools 启停链/默认全量]+McpMarketTest 2→5 零回归[挂账-upg41v2 销项]+**变异复杀如实**[M3 机制采信/M1 未复现红采信 XML 口径]；真机启停 UI 走查=验收员持有待办；**达待合→审验员→设计师[verify-hash 终态]**）
+→ ✅ **已合 main @fea2fae @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（设计师B 溯源实证后出卡；派单 `设计师\派单\UPG-87_内置包启停_派单_202</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 18:4x**（feat/upg87 **fea2fae** 已 push origin，基底 ma</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree｜全量 </t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @fea2fae @2026-09-03**（设计师B：验收 §P41+审验 confirmed[变异环 M1/M3</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-87_内置包启停_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>DEL-UPG87-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>UPG-88</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>极简批阶段 1（ASR + 极简主页生产化 + 两态开关点亮 + 快速提示词）</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P42：43e5756 三提交链隔离 worktree——全量 **748/0/1 亲跑一致**+Upg84ModeConverge 6 锚全绿[契约升级非消音复核]+R1 自纠实锤+**变异复验 5 轮未复现红如实标注**[采信程序员红案]+L2 四场景采信[未独立复跑如实标注]；coverage PARTIAL 裁决位维持[ASR 真人发声]；**达待合→审验员→设计师**）
+→ ✅ **已合 main @43e5756 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（产品主线；设计文=极简送审稿+用户拍板「两模式/不阉割能力」；派单 `设计师\派单\U</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-03 23:0x**（feat/upg88 **43e5756** 已 push origin[施工 90</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>**用户指示模拟器自测**（ASR 真实语音转写=物理受限转验收员持有｜coverage PARTIAL 设计师裁决位申报在报告 §七）；T</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @43e5756 @2026-09-03**（设计师B：验收 §P42+审验 confirmed[契约升级非消音精读</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-88_极简批阶段1_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>DEL-UPG88-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UPG-89</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>极简呈现引擎（PresentationRegistry + core.js 呈现栈 + Intent Router + Response Splitter + 三骨架）</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>P1
+→ **依据**：极简呈现交互体系 v1.1（大神评审 8.8/10 吸收版：Surface 抽象/Transient-Persistent/PresentationPolicy/Intent Router/Voice EOU/解析隔离/presentation_intent 全落）+ 用户四条拍板（两模式/不阉割/引擎规则驱动/卡片浮于主页+输入能力常驻）；demo v3 视觉基准
+→ **防撞**：与 UPG-88 同主页面——建议 88 先合或同程序员串行；与 85/87 零重叠</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>⏸️ **挂单 @2026-09-03**（用户拍板：先不派，收前面尾巴｜尾批清完再启；派单/STD 已备妥 [原派单 @2026-09-0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-89_极简呈现引擎_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>UPG-90</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>尾巴批修（S-06 打回项 ②⑧ + C7 基线测试非确定性）</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>P2
+→ ✅ **已合 main @39b17c4 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（尾巴清零批；派单 `设计师\派单\UPG-90_尾巴批修_派单_2026-09-03.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-04 00:1x**（feat/upg90 **1845cb7** 已 push origin，基 mai</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>**依据**：S-06 打回项 ②⑧（index.html:199 引号未闭合申报失实+四死文件未 git rm；ACCEPTANCE_LO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @39b17c4 @2026-09-03**（设计师B：验收 §P43+审验 confirmed 达待合后｜reba</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-90_尾巴批修_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>DEL-UPG90-20260903-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UPG-91</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>我的资产页注册制重排（tab 导航+二级收缩裸列表+点值脱敏+诚实空态+假数据回落删除+令牌迁移）</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>P2 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P44：4dc19e7 三提交链隔离 worktree——全量 **752/0/1 亲跑一致**+demoBridge 假数据零残留 grep[红线 18 同族根除]+锚④强化实录复核+R1 自纠[1C 形态消费恢复]；变异 M4 未复现如实[采信程序员 4/4 XML]；真机五场景持有维持；**达待合→审验员→设计师**）
+→ ✅ **已合 main @4dc19e7 @2026-09-03**</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（用户实测「体验感很差」→ 四病灶诊断 → 六轮迭代 demo v6 拍板；派单 `设计</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-04 01:4x**（feat/upg91 **34a2dda** 已 push origin[远端顶=4</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P44：4dc19e7 三提交链隔离 workt</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @4dc19e7 @2026-09-03**（设计师B：验收 §P44+审验 confirmed[M4 复杀补强｜验</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-91_我的资产页重排_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>DEL-UPG91-20260904-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>UPG-92</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>manifest 硬闸化（deliver-gen 源头合规 + 自检内置）</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>P1
+→ 🆕 **已认领 @2026-09-03 23:46**（程序员 Kimi/kimi-cli，worktree mov-upg92，branch feat/upg92，基 main 607bf4e；按派单施工：deliver-gen 源头合规[路径裸串/条带 sha256/绑定值写入]+自检内置硬闸[不合规=拒绝产出]——工单系统侧工具链，零 app 代码面）→ ✅**C 完成 @2026-09-04 00:0x**（程序员 Kimi/kimi-cli，feat/upg92 **39039ef** 已 push origin[MOV 仓库，基 main f218abc]；deliver-gen 升级一件：①**源头合规**[--evidence 即产 manifest：路径裸串/条带 sha256 机器实算/evidence_manifest_sha 绑定值写入可重算，canonical 与 审验.py _canon_manifest 逐字节对齐] ②**自检内置硬闸**[产出后自跑 审验.py --manifest，ok:False=删残件+拒出报告+exit 1，非警告] ③--manifest-draft 直通过闸[机器不替人修补语义] ④--self-test 四案 **PASS 4/4**[合规绿/注入路径嵌注释红/注入缺 sha256红/骨架回归]；**狗粮**：本单 manifest 经新闸产出 ok:True 重算一致 802d72e6[8 条全 exists/hash_matches=True，零人工修补]；亲杀双锚实录在案[exit=1+残件清除]；回归 审验.py manifest-self-test 4/4+verify-hash-self-test 2/2+旧骨架 exit 0 零回归；Token/KV 0/0；0027-mov 零接触；DEL-UPG92-20260904-001[code=39039ef/artifact 不适用/manifest 802d72e6]；verify-hash 如实申报 HASH_REJECT not-ancestor[未合分支+origin 落后 8 提交，合后终态复核]；报告 DELIVERY_UPG92_2026-09-04.md；**已登记两个表**）——待验收员验收[--self-test 一键复跑+亲杀复杀]+设计师合 main 后终态复核
+→ **依据**：UPG-86 治理完成 4 小时后 UPG-88 交付 manifest 再度失效</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（manifest 同族第六现｜红线 23 自检步声称未执行，改机制硬闸；派单 `设计师</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-04 00:0x**（程序员 Kimi/kimi-cli，feat/upg92 **39039ef** 已</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>审验员三建议取最硬：deliver-gen 源头合规+自检内置（机器产出即合规不靠人）；本单自身 manifest 必须经新闸产出（吃自己狗</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>合 main后终态复核</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-92_manifest硬闸化_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>DEL-UPG92-20260904-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>UPG-93</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MainActivity 拆分·阶段 1（工具注册面搬移 + 拆分蓝图落档）</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>P1
+→ **实测**（@fea2fae）：MainActivity.kt 7666 行/185 个 mcpHandlers 注册点；区域图：工具注册[大头]/chips:945/胶囊:1352/模型:2352/MemoryOS:2671/页面桥:2906/对话模式:4352/预审单:5317/Markwon:6839/市场:7266
+→ **防撞**：动 MainActivity 大头——88 已合、89 挂单中，当前无在施同面单；与 86/90/92 零重叠
+→ **哲学**：纯搬移零逻辑改动</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-03**（架构图实证「图上分层、代码一锅」｜用户拍板「先解决这个」；派单 `设计师\派单\UPG</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>在施同面单；与 86/90/92 零重叠</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-93_MainActivity拆分阶段1_派单_2026-09-03.md</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4168,7 +4168,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>P1
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P45：39039ef 工单系统仓隔离 worktree——**deliver-gen --self-test 4/4 亲跑 PASS**[源头合规/硬闸注入红×2 exit=1 残件清除/骨架回归]+硬闸「拒绝产出非警告」机制化——**第六现根因闭环**；DEL-UPG92 狗粮自证；观察转办：sync 锚词表「✅K 完成」代号→设计师；**达待合→设计师**）
 → 🆕 **已认领 @2026-09-03 23:46**（程序员 Kimi/kimi-cli，worktree mov-upg92，branch feat/upg92，基 main 607bf4e；按派单施工：deliver-gen 源头合规[路径裸串/条带 sha256/绑定值写入]+自检内置硬闸[不合规=拒绝产出]——工单系统侧工具链，零 app 代码面）→ ✅**C 完成 @2026-09-04 00:0x**（程序员 Kimi/kimi-cli，feat/upg92 **39039ef** 已 push origin[MOV 仓库，基 main f218abc]；deliver-gen 升级一件：①**源头合规**[--evidence 即产 manifest：路径裸串/条带 sha256 机器实算/evidence_manifest_sha 绑定值写入可重算，canonical 与 审验.py _canon_manifest 逐字节对齐] ②**自检内置硬闸**[产出后自跑 审验.py --manifest，ok:False=删残件+拒出报告+exit 1，非警告] ③--manifest-draft 直通过闸[机器不替人修补语义] ④--self-test 四案 **PASS 4/4**[合规绿/注入路径嵌注释红/注入缺 sha256红/骨架回归]；**狗粮**：本单 manifest 经新闸产出 ok:True 重算一致 802d72e6[8 条全 exists/hash_matches=True，零人工修补]；亲杀双锚实录在案[exit=1+残件清除]；回归 审验.py manifest-self-test 4/4+verify-hash-self-test 2/2+旧骨架 exit 0 零回归；Token/KV 0/0；0027-mov 零接触；DEL-UPG92-20260904-001[code=39039ef/artifact 不适用/manifest 802d72e6]；verify-hash 如实申报 HASH_REJECT not-ancestor[未合分支+origin 落后 8 提交，合后终态复核]；报告 DELIVERY_UPG92_2026-09-04.md；**已登记两个表**）——待验收员验收[--self-test 一键复跑+亲杀复杀]+设计师合 main 后终态复核
 → **依据**：UPG-86 治理完成 4 小时后 UPG-88 交付 manifest 再度失效</t>
         </is>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>审验员三建议取最硬：deliver-gen 源头合规+自检内置（机器产出即合规不靠人）；本单自身 manifest 必须经新闸产出（吃自己狗</t>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P45：39039ef 工单系统仓隔离 worktre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4218,6 +4218,7 @@
       <c r="C81" t="inlineStr">
         <is>
           <t>P1
+→ 🆕 **已认领 @2026-09-04 01:5x**（程序员 Claude/wmw0027，worktree mov-upg93，branch feat/upg93，基 main 254d6ca[军规 commit 顶]；按派单施工：185 handler 盘点落蓝图+ToolsRegistry 聚合+分域 Registrar 搬移+3 变异锚+测试金字塔——纯搬移零逻辑改动）
 → **实测**（@fea2fae）：MainActivity.kt 7666 行/185 个 mcpHandlers 注册点；区域图：工具注册[大头]/chips:945/胶囊:1352/模型:2352/MemoryOS:2671/页面桥:2906/对话模式:4352/预审单:5317/Markwon:6839/市场:7266
 → **防撞**：动 MainActivity 大头——88 已合、89 挂单中，当前无在施同面单；与 86/90/92 零重叠
 → **哲学**：纯搬移零逻辑改动</t>
@@ -4230,7 +4231,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>在施同面单；与 86/90/92 零重叠</t>
+          <t>🆕 **已认领 @2026-09-04 01:5x**（程序员 Claude/wmw0027，worktree mov-upg93，bra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4169,8 +4169,7 @@
       <c r="C80" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P45：39039ef 工单系统仓隔离 worktree——**deliver-gen --self-test 4/4 亲跑 PASS**[源头合规/硬闸注入红×2 exit=1 残件清除/骨架回归]+硬闸「拒绝产出非警告」机制化——**第六现根因闭环**；DEL-UPG92 狗粮自证；观察转办：sync 锚词表「✅K 完成」代号→设计师；**达待合→设计师**）
-→ 🆕 **已认领 @2026-09-03 23:46**（程序员 Kimi/kimi-cli，worktree mov-upg92，branch feat/upg92，基 main 607bf4e；按派单施工：deliver-gen 源头合规[路径裸串/条带 sha256/绑定值写入]+自检内置硬闸[不合规=拒绝产出]——工单系统侧工具链，零 app 代码面）→ ✅**C 完成 @2026-09-04 00:0x**（程序员 Kimi/kimi-cli，feat/upg92 **39039ef** 已 push origin[MOV 仓库，基 main f218abc]；deliver-gen 升级一件：①**源头合规**[--evidence 即产 manifest：路径裸串/条带 sha256 机器实算/evidence_manifest_sha 绑定值写入可重算，canonical 与 审验.py _canon_manifest 逐字节对齐] ②**自检内置硬闸**[产出后自跑 审验.py --manifest，ok:False=删残件+拒出报告+exit 1，非警告] ③--manifest-draft 直通过闸[机器不替人修补语义] ④--self-test 四案 **PASS 4/4**[合规绿/注入路径嵌注释红/注入缺 sha256红/骨架回归]；**狗粮**：本单 manifest 经新闸产出 ok:True 重算一致 802d72e6[8 条全 exists/hash_matches=True，零人工修补]；亲杀双锚实录在案[exit=1+残件清除]；回归 审验.py manifest-self-test 4/4+verify-hash-self-test 2/2+旧骨架 exit 0 零回归；Token/KV 0/0；0027-mov 零接触；DEL-UPG92-20260904-001[code=39039ef/artifact 不适用/manifest 802d72e6]；verify-hash 如实申报 HASH_REJECT not-ancestor[未合分支+origin 落后 8 提交，合后终态复核]；报告 DELIVERY_UPG92_2026-09-04.md；**已登记两个表**）——待验收员验收[--self-test 一键复跑+亲杀复杀]+设计师合 main 后终态复核
-→ **依据**：UPG-86 治理完成 4 小时后 UPG-88 交付 manifest 再度失效</t>
+→ ✅ **已合 main</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4190,7 +4189,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>合 main后终态复核</t>
+          <t>✅ **已合 main（工单系统仓）@beb2777 @2026-09-03**（设计师B：验收 §P45+审验 confirmed 后｜f</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4217,7 +4217,8 @@
       <c r="C81" t="inlineStr">
         <is>
           <t>P1
-→ 🆕 **已认领 @2026-09-04 01:5x**（程序员 Claude/wmw0027，worktree mov-upg93，branch feat/upg93，基 main 254d6ca[军规 commit 顶]；按派单施工：185 handler 盘点落蓝图+ToolsRegistry 聚合+分域 Registrar 搬移+3 变异锚+测试金字塔——纯搬移零逻辑改动）
+→ 🆕 **已认领 @2026-09-04 01:5x**（程序员 Claude/wmw0027，worktree mov-upg93，branch feat/upg93，基 main 254d6ca[军规 commit 顶]；按派单施工：185 handler 盘点落蓝图+ToolsRegistry 聚合+分域 Registrar 搬移+3 变异锚+测试金字塔——纯搬移零逻辑改动）→ ⚠️**WIP 回滚 @2026-09-04 02:3x**（程序员 C：盘点/口径闭合/提取器基建完成入库[commit 76c91cb：169 注册点三态扫描盘点+9 域归类+185 口径闭合核对]；**搬移实施中途回滚**——三态提取器跑出的 9 域文件存在块边界错位残片[ModelRegistry 循环/obsidian 段等 5-8 处——三方对账未完成]，**不带入半成品**，工作区已还原 7666 行原始态；工程形态已定案=Kotlin 扩展函数分域文件[receiver=this 零改动零持有]，WIP 资产与修复路径在案[upg93-拆分wip 记忆+upg93_inventory.json]）——**重新认领需独立完整会话**（剩余：错位残片三方对账→测试金字塔→3 变异锚→冷启动锚）
+→ ⚠️ **转 WIP @2026-09-04**（程序员如实申报，设计师核实在案）：基建三件已入库 feat/upg93 @76c91cb（169 注册点盘点[三态扫描块提取器 v3，185 口径修正闭合=169 注册+16 直呼消费]+9 域归类[system23/device52/vault18/page17/chat16/memory11/market11/model8/biz13]+工程形态定案[Kotlin 扩展函数分域文件，handler 体零改动+零 Activity 新增持有，P0-1/3 合规]）；**实施中途回滚**——三态提取器首跑分域文件存在块边界错位残片（三引号串/字符串模板打崩配平同族根因），三方对账需独立完整会话→**不带入半成品，工作区已还原 7666 行原始态**（设计师亲核：mov-upg93 无 MainActivity 改动残留，WIP 资产 gen_tools_v2.py/gen_v3.py 在案）；**重新认领建议开新会话**（上下文充足做三方对账+测试金字塔+冷启动锚），基建可直接复用——主仓 main 零污染（76c91cb 仅在分支）
 → **实测**（@fea2fae）：MainActivity.kt 7666 行/185 个 mcpHandlers 注册点；区域图：工具注册[大头]/chips:945/胶囊:1352/模型:2352/MemoryOS:2671/页面桥:2906/对话模式:4352/预审单:5317/Markwon:6839/市场:7266
 → **防撞**：动 MainActivity 大头——88 已合、89 挂单中，当前无在施同面单；与 86/90/92 零重叠
 → **哲学**：纯搬移零逻辑改动</t>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4023,29 +4023,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>P1
-→ **依据**：极简呈现交互体系 v1.1（大神评审 8.8/10 吸收版：Surface 抽象/Transient-Persistent/PresentationPolicy/Intent Router/Voice EOU/解析隔离/presentation_intent 全落）+ 用户四条拍板（两模式/不阉割/引擎规则驱动/卡片浮于主页+输入能力常驻）；demo v3 视觉基准
-→ **防撞**：与 UPG-88 同主页面——建议 88 先合或同程序员串行；与 85/87 零重叠</t>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P46：f616b38f 分支头隔离 worktree——bun 12/12 亲跑+JVM 759/0/1 亲跑[AssetsHomeEngineContract 4 锚]+**PV-01 变异亲杀**[2 fail→还原]；锚⑥死变异裁决转设计师[测试有效性非产品缺陷]；homeWeb 接线下批申报一致；L2 七场景持有；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 带缺陷通过 @2026-09-04**（PV-01 亲杀独立复验双红+锚⑥更精确定性=layer 死状态只写不读+四项发现登记）→ ✅ **已合 main @fe258949 @2026-09-04**（设计师B：rebase 254d6caf 零冲突[原链 a51238dd→615f3590→f616b38f 重写成 84d11731→1e90bf44→fe258949——DEL 绑 615f359 漂移随 UPG-92 硬规则处置]+ff-only+push origin/main+verify-hash HASH_OK 闭环；MainActivity 零触碰=UPG-93 防撞兑现；L2 真机七场景[含 ASR⑦]验收员持有维持；锚⑥ layer 死字段删除随批 P3）→ ✅ **P3 尾巴合入 @0aad7980 @2026-09-04**（程序员锚⑥处置收尾：①核实「断言无需重设计——z 数值断言直调 zSnapshot=方案 a 本在链」②删 surface.layer 死字段[core.js 2 行纯删除，diff 核实一致]+DEL 按新硬规则重绑分支头 4fd540a6；设计师轻量通道：diff 精读[仅 2 删行]+rebase main 单提交回放[旧三链 patch-id 自动跳过]+ff-only+push+verify-hash HASH_OK；锚⑥本活实证[决策丢失变异→zSnapshot topKind=content→RED]在案——「审批永远压内容」安全不变量有杀）
+→ 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg89，branch feat/upg89，基 main 39b17c4[UPG-90 已合]；按 STD-UPG-89-v2 施工：PresentationRegistry 九字段+style_tokens 白名单+core.js 呈现栈[Surface 四类/Transient-Persistent/z 序置顶/docked/Motion Intent 五词]+Intent Router 四路仲裁+Response Splitter 解析隔离+PV-01 词表闸+Danger 白名单+三骨架——8 变异锚+真机七场景[ASR PARTIAL 随本单补验]；**防撞口径确认**：只动 assets/home 呈现面+新增 core.js/Registry，不碰 MainActivity 工具注册区[UPG-93 拆分在途 WIP]）→ ✅**C 完成 @2026-09-04 04:1x**（feat/upg89 **615f359** 已 push origin[第一批 90aee9f→锚⑥升级 615f359]，基 main 39b17c4[UPG-90 已合]；**引擎全栈落地**：①**core.js 呈现引擎核心**[受信样式词汇表七命名空间 21 词 version 1.2 裸词非法+**PV-01** 原始视觉字面量拒收[视觉键名+hex/px/% 递归扫描]+**Danger 白名单**四词越表拒收+**PresentationRegistry** 九字段+style_tokens 壳级白名单+state 治理 candidate/registered/removed 未登记 fail-closed telemetry+**Response Splitter** 双段解析隔离坏块不塌散文+**SurfaceStack** L0-L4 决策置顶浅栈深度 policy 收叠→Recall+**IntentRouter** 四路仲裁 Cancel/Modify/NewTask/Defer 全足迹+**Motion Intent 五词映射**[enter 300/exit 250/expand 200/docked 450/micro 150+M3 easing]+**三骨架 HTML 生成器** offerCard/timelineList/plain 未登记纯文本回落诚实小字——UMD 双态 node/bun 可测] ②**registry_seed.js** 三骨架登记[offerCard.v1/timelineList.v1/plain.v1 registered+壳白名单] ③**home.html 引擎接入**[core.js/registry_seed 装载+呈现栈容器 present-stack+Recall 圆片条+Intent Router 接线 sendText[cancel/defer 拦截]+docked 态 CSS+v1.2 卡面 token 圆角 22/无描边/--card-shadow-lg/caps 10.5·700·.12em/pill 主钮纯黑+prefers-reduced-motion 退化] ④**测试双层**[bun tests/upg89_core.test.mjs **12/12**[逻辑级 8 锚全对应]+JVM 源码锚 AssetsHomeEngineContractTest **4**[Registry 九字段/三道闸/Motion 五词/Splitter 形态]]；**变异 8 锚：7 实杀 RED**[M1 renderRaw 不抛/M2 扫描恒空/M3 词表恒 ok/M4 Danger 恒放行/M5 未登记不回落/M7 仲裁恒 normal/M8 栈深不收叠——全部 bun RED]+**锚⑥死变异暴露→测试有效性升级**[zSnapshot layer-aware 排序+z 数值断言（决策 L3≥30/内容&lt;30）——加强变异仍 NOT-RED 复跑转复验在案 commit 615f359]；全量 **105 套件 759/0/1 全绿**[755[U90]+4 JVM 锚=759]；**逻辑面四场景机制实证**[①底座输入常驻继承 U88/③审批置顶+Danger 红 bun/④仲裁足迹 bun/⑤未登记回落 bun——真机七场景**转验收员持有**[②agent 流接线+⑦ASR 真人发声——如实申报]；**防撞兑现**[MainActivity 零触碰纯 CRLF+UPG-93 工具注册区零交集]；Token 双段零额外轮次+voice_hint 确定性槽/KV 0；coverage_status=**PARTIAL**[JS 引擎逻辑面 FULL[bun 12/12+7 锚实杀]/原生 agent chunk→homeWeb 接线未做=真机批/下批——设计师裁决位申报]；DEL-UPG89-20260904-001[code=**4fd540a6** 锚⑥处置收尾重绑/artifact=ba3d877dad14c566（APK 前 16）/manifest_sha 见案——**按新硬规则分支头重绑 @2026-09-04**（前头 615f359=f616b38f 链已废，本头含 surface.layer 死字段删除+锚⑥ z 数值断言收口）]；报告 DELIVERY_UPG89_2026-09-04.md；**已登记两个表**）——待验收员验收（L1 复核+变异复杀[bun]+真机七场景[含 agent 接线下批]+合后 verify-hash 终态复核）
+→ **依据**：极简呈现交互体系 v1.1（大神评审 8.8/10 吸收版：Surface 抽象/Transient-Persistent/PresentationPolicy/Intent Router/Voice EOU/解析隔离/presentation_intent 全落）+ **v1.2 增补（卡面 token/样式词表 PV-01/动效 intent/Danger 白名单，已冻结）** + 用户四条拍板（两模式/不阉割/引擎规则驱动/卡片浮于主页+输入能力常驻）；demo v4 视觉基准
+→ **防撞**：UPG-88 已合 main</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>⏸️ **挂单 @2026-09-03**（用户拍板：先不派，收前面尾巴｜尾批清完再启；派单/STD 已备妥 [原派单 @2026-09-0</t>
+          <t>📌 **已派单·待认领 @2026-09-04**（**v2 正式派发**：启动条件齐=尾巴批清完+UPG-88 已合 main 43e5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**C 完成 @2026-09-04 04:1x**（feat/upg89 **615f359** 已 push origin[第一批 9</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **审验 confirmed 带缺陷通过 @2026-09-04**（PV-01 亲杀独立复验双红+锚⑥更精确定性=layer 死状态只</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **已合 main @fe258949 @2026-09-04**（设计师B：rebase 254d6caf 零冲突[原链 a51238</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4055,7 +4056,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG89-20260904-001</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4073,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>P2
+          <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P47：c969b05a 隔离 worktree——全量 **762/0/0 亲跑**[0 失败基线]+ToolsSplitContract 7 锚+9 域拆分+MainActivity 1752 行删减+零行为变化[sha256 双锁]+**M-vault 变异亲杀**[键名变异→3 锚齐红与申报一致→还原；注释式破多行 lambda 编译失败教训三现——拆分类变异用键名/删除式]；冷启动 +5.1%&lt;10%；真机三场景采信；**达待合→审验员→设计师**[阶段 2 后续]）
 → ✅ **已合 main @39b17c4 @2026-09-03**</t>
         </is>
       </c>
@@ -4088,7 +4089,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>**依据**：S-06 打回项 ②⑧（index.html:199 引号未闭合申报失实+四死文件未 git rm；ACCEPTANCE_LO</t>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P47：c969b05a 隔离 worktree｜全量</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4221,7 +4222,8 @@
 → ⚠️ **转 WIP @2026-09-04**（程序员如实申报，设计师核实在案）：基建三件已入库 feat/upg93 @76c91cb（169 注册点盘点[三态扫描块提取器 v3，185 口径修正闭合=169 注册+16 直呼消费]+9 域归类[system23/device52/vault18/page17/chat16/memory11/market11/model8/biz13]+工程形态定案[Kotlin 扩展函数分域文件，handler 体零改动+零 Activity 新增持有，P0-1/3 合规]）；**实施中途回滚**——三态提取器首跑分域文件存在块边界错位残片（三引号串/字符串模板打崩配平同族根因），三方对账需独立完整会话→**不带入半成品，工作区已还原 7666 行原始态**（设计师亲核：mov-upg93 无 MainActivity 改动残留，WIP 资产 gen_tools_v2.py/gen_v3.py 在案）；**重新认领建议开新会话**（上下文充足做三方对账+测试金字塔+冷启动锚），基建可直接复用——主仓 main 零污染（76c91cb 仅在分支）
 → **实测**（@fea2fae）：MainActivity.kt 7666 行/185 个 mcpHandlers 注册点；区域图：工具注册[大头]/chips:945/胶囊:1352/模型:2352/MemoryOS:2671/页面桥:2906/对话模式:4352/预审单:5317/Markwon:6839/市场:7266
 → **防撞**：动 MainActivity 大头——88 已合、89 挂单中，当前无在施同面单；与 86/90/92 零重叠
-→ **哲学**：纯搬移零逻辑改动</t>
+→ **哲学**：纯搬移零逻辑改动（优化另单）；UPG-79 拆分先例（approval/ 包已验证模式）
+→ 🆕 **已认领 @2026-09-04 01:58·重新接管**</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4231,17 +4233,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>🆕 **已认领 @2026-09-04 01:5x**（程序员 Claude/wmw0027，worktree mov-upg93，bra</t>
+          <t xml:space="preserve">✅**C 完成 @2026-09-04 03:3x**（程序员 Kimi/kimi-cli，feat/upg93 **c969b05a** </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **验收员复验通过（§P47）→ 审验 confirmed 通过 @2026-09-04**（M-vault 键名变异亲杀 3 锚齐红独</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **已合 main @3315bff0 @2026-09-04**（设计师B：rebase 0aad7980 零冲突[c969b05a→</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4250,6 +4252,304 @@
         </is>
       </c>
       <c r="I81" t="inlineStr">
+        <is>
+          <t>DEL-UPG93-20260904-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UPG-94</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>极简主页真机观感修复（dock 隐藏 + logo 去框去影 + hint 删除 + 发送钮归 token）</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P48：分支头 25f73fe0[申报 746b20ec≠分支头二现]隔离 worktree——全量 763/0/1 亲跑一致+契约锚 4/4+**M1 删除式亲杀**[failures=1→还原；注释式免疫四现终纳]+四件观感修复核物；**P3×2：U89 引擎恢复自纠未申报**[透明度义务]+logo 168px 追加后截图未更新；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 带缺陷通过 @2026-09-04**（四件坐实+U89 恢复自纠亲核正确完整+四项发现登记）→ ✅ **已合 main @806bb01c @2026-09-04**（设计师B：rebase 3315bff0 三提交重写[25f73fe0→806bb01c——MainActivity 与 93 双改不同区域自动合并 clean]+ff-only+push+verify-hash HASH_OK；**设计师追加项验收缺口实录**：seed 合并进 engine.registry+timelineList 骨架 CSS 两项[2026-09-04 设计师裁决并 94 随批]未随本单落地——转出至 UPG-96 范围[接线单前置一件]，STD-96 追加说明区已注记；4 项发现裁决见问题区）
+→ 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg94，branch feat/upg94，基 main fe258949[UPG-89 已合]；四件按派单行号施工[dock 字段化+applyPresentationMode 路由/logo 零装饰/heroHint 删/btnSend 归 token]+变异锚 2+截图四场景）
+→ **依据**：呈现体系 v1.1 §三 L0 + v1.2 增补 §一；用户两条新拍板（heroHint 删除/logo 零装饰）@2026-09-04
+→ **防撞**：MainActivity 只动 applyPresentationMode/dock 字段化</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（用户真机实测踩中[2026-09-04 03:27 包]：极简态经典 dock 飘顶[</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg94，branch fe</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>✅ **审验 confirmed 带缺陷通过 @2026-09-04**（四件坐实+U89 恢复自纠亲核正确完整+四项发现登记）</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @806bb01c @2026-09-04**（设计师B：rebase 3315bff0 三提交重写[25f73fe</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-94_极简主页真机观感修复_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UPG-95</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>个性化槽位选择（care profile 提炼 + 可选槽池 + LLM 编辑层 + ticketCard/rideCard 骨架落地）</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P49：979bf6bf 三批隔离 worktree——**bun 18/18 亲跑**+全量 **786/0/1 亲跑**[Care 双类 20 用例]+**M-11 变异亲杀**[敏感闸放行→红→还原]+编辑层接线[设计师裁决已接]；其余 3 锚采信；L2 出卡走查持有；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 通过 @2026-09-04**（bun 18/18+全量 786/0/1 双亲跑+M-11 敏感闸亲杀独立复验+DEL 绑定无漂移正面记录[三连回潮后首单做对]）→ ✅ **已合 main @ac7495fb @2026-09-04**（设计师B：rebase 806bb01c 人工解真冲突 2 处[index.html CSS 段取 main 位置+并入 95 amenities/route/driver/pref-chip 装载块+顺带补回 94 恢复时漏网的 docked 态两条 CSS]+解后复跑闸：bun 12+6 全绿+全量 **790/0/1** 绿→ff-only+push+verify-hash HASH_OK；3 项发现裁决见问题区；持有项=L2 出卡 CDP 走查[随 96]+ASR PARTIAL[96 场景⑦]） → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P50：cdf769a9 隔离 worktree——全量 **775/0/1 亲跑一致**+**HomeDeliveryContractTest 5/5 亲跑确认**[homeWeb 接线契约落位——UPI-89/95 遗留闭环]+红线/诚实申报复核；**M2 复杀 3 式未复现如实标注**[多行 evaluateJavascript 适配成本超阈值——采信程序员 XML]+L2 模拟器环境阻塞登记；**达待合→审验员→设计师**）
+→ 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg95，branch feat/upg95，基 main 3315bff0[含 UPG-93 拆分]；施工：提炼层六域规则扩展（hotel/food/rail/ride/travel/shopping 纯函数）+offerCard amenities 槽（≤3）+ticketCard/rideCard candidate 登记+编辑层提示词节[全量事实×画像→槽池内选择；标签注入原文不进]——种子集 11 断言+4 变异锚；与 UPG-94 同 index.html 面按裁决串行）
+→ **防撞**：与 UPG-94 同 index.html 面（amenity chips CSS）——建议 94 先合或同人串行；不动 MainActivity（棘轮军规）；不动 Memory API（只消费）
+→ **复用**：UPG-51 提炼器扩展点 + UPG-89 引擎/Registry + UPG-05 基因红线</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（用户拍板方向「商户信息尽量全+用户侧个性化显示」；设计口径=v1.2 增补附录 B[三</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg95，branch fe</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>✅ **审验 confirmed 通过 @2026-09-04**（bun 18/18+全量 786/0/1 双亲跑+M-11 敏感闸亲杀独</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @ac7495fb @2026-09-04**（设计师B：rebase 806bb01c 人工解真冲突 2 处[in</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-95_个性化槽位选择_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UPG-96</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>homeWeb 呈现回路接线（极简发送不回落 + LLM 回复回流出卡 + 真机批收口）</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>P1
+→ 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg96，branch feat/upg96，基 main 806bb01c[UPG-94 已合=seed 合并前置解除]；施工：sendFromHome 不回落+回复链极简态转发 homeWeb+失败诚实+仲裁 journal+94 转出两件[seed 合并进 engine.registry+timelineList CSS]——3 变异锚+真机七场景收口）→ ✅**C 完成 @2026-09-04**（feat/upg96 **cdf769a9** 已 push origin[远端顶；基 main 806bb01c=UPG-94 已合]；**三处接线**：①**sendFromHome 不回落**[删 applyPresentationMode CLASSIC 切回——极简发送留极简，对话史经典侧照常 GONE 保留可回看] ②**回复转发**[homeDeliveryActive 投递回路开关 volatile+streamChunkSink 消费点 homeDeliveryActive 条件转发 homeWeb MovHomeHost.onLlmChunk[jsString 转义]+**完成文本回流** trimmed 同条件+**回路关闭** homeDeliveryActive=false 不残留至经典发送] ③**仲裁足迹**[HomeBridge.sendText 加 route 二参[JS 端 fp.route 传入]→原生 appendLog「[UPG-96 仲裁] route=…」journal 可查]；**94 转出两件**[index.html 构造 engine 后合并 MovRegistrySeed.entries[ticketCard/rideCard candidate 骨架可被 Intent 分派]+timelineList 骨架 CSS .tl/.tl-item/.tl-dot.done/.tt/.ts]；**失败诚实**[homeWeb 未装配/JS 异常 fail-safe 落经典+appendLog 日志点——不许静默]；**变异 3 锚形态实录**[M1 删 dock GONE 行→MinimalHomePolish 契约红/M2 删三处转发→HomeDelivery 契约红/M3 删 route 参数→仲裁 journal 锚红——还原复绿]；契约锚 **5/5**[锚①不回落/锚②chunk+trimmed 回流/锚③仲裁 journal/94 转出件①②]；全量 **108 套件 775/0/1 全绿**[763[U94]+5[UPG-96 契约]=768+其他自洽]；**模拟器不回落实证**[tap 切极简→发送→画面仍极简：dump texts 无经典 chips/胶囊——经典元素零出现]+经典恢复对照；**真机七场景收口=验收员持有**[②ASR/③出卡目测/⑥小圆片交互——含 UPG-88 PARTIAL 销项、UPG-89 出卡走查销项]；MainActivity 纯 CRLF 保持；Token/KV 0/0[chunk 转发为流转投不进 prompt]；coverage_status=**PARTIAL**[接线面 FULL[契约锚 5/5+模拟器实证]/真机批目测走查=持有——设计师裁决位]；DEL-UPG96-20260904-001[code=cdf769a9/artifact=04f48903/manifest_sha=a376d376]；报告 DELIVERY_UPG96_2026-09-04.md；**已登记两个表**）——待验收员验收（L1+变异复杀+真机七场景目测[持有]+合后 verify-hash 终态复核）
+→ **依赖**：UPG-94 先合（seed 未合并=接线也回落纯文本）；与 95 同 home 面建议串行
+→ **豁免**：MainActivity 棘轮军规注记——改既有对话链路线</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（极简批阶段 2 收口=完全体单：不回落+onLlmChunk 回流+fail-safe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-04**（feat/upg96 **cdf769a9** 已 push origin[远端顶；基 main</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>验收员验收（L1+变异复杀+真机七场景目测[持有]+合后 verify-hash 终态复核）</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-96_homeWeb呈现回路接线_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>DEL-UPG96-20260904-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UPG-97</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>侧边栏工作台三入口接线（我的记忆/我的资产/我的能力）+ comingSoon 兜底可见性</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>P1
+→ **防撞**：纯前端单（mov-vue 源+产物同步）；MainActivity/tools 零行；与 95/96 零交集
+→ 🆕 **已认领 @2026-09-04 05:47**（程序员 Kimi/kimi-cli，worktree mov-upg97，branch feat/upg97，基 origin/main ac7495f；按派单施工：openPage 三 case 接线[先核实槽位键值实证]+comingSoon 兜底可见化+mov-vue 构建同步产物——纯前端零原生）
+→ **教训**：导航类验收须「入口清单全点验」；9-02 openAssets 漏 case 同族——键值对齐须实证</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（用户真机报障「侧边栏有的按钮失灵」→ 设计师 adb 实测复现+根因定位：Sideba</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>🆕 **已认领 @2026-09-04 05:47**（程序员 Kimi/kimi-cli，worktree mov-upg97，bran</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-97_侧边栏三入口接线_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UPG-98</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MainActivity 拆分·批② 市场面搬移（→ market/ 模块）</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>P1
+→ **范围**：市场总览区（buildLocalOverview/启停/安装投影）→ market/ 模块；纯搬移零逻辑改动；保真锚=块归一化 sha256 前后全等
+→ **防撞**：本批独占 MainActivity 市场区；与 95/96/97 零交集</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（拆分主线批②/共 8 批｜串行纪律：一批一派合后再基[UPG-95 真冲突实证后立]；</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-98_MainActivity拆分批2市场面_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UPG-99</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>工单系统工具链硬闸批（DEL 分支头校验 + standard_id 交叉校验 + 报告模板强制段 + 红线 23 落规）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>P2
+→ **范围**：sync-orders DEL==分支头校验 / 审验.py standard_id 交叉校验 / deliver-gen 模板强制段 / 红线 23 两条明文
+→ **纪律**：既有闸零回归；报错人话化；改库卡先备份；sync 后 --check diff=0</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>✅ **设计师直修完成 @2026-09-04**（用户拍板「你自己修吧，不搞工单」｜不走流转流程，设计师直接落地四件：①deliver-g</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>**范围**：sync-orders DEL==分支头校验 / 审验.py standard_id 交叉校验 / deliver-gen 模</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已合 main@hash」在祖先链/存量 cherry-pick 卡豁免/显式豁免跳过]｜首跑即抓 7 条存量异常全归因[5 存量豁免+1 </t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4370,15 +4370,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>P1
-→ 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg96，branch feat/upg96，基 main 806bb01c[UPG-94 已合=seed 合并前置解除]；施工：sendFromHome 不回落+回复链极简态转发 homeWeb+失败诚实+仲裁 journal+94 转出两件[seed 合并进 engine.registry+timelineList CSS]——3 变异锚+真机七场景收口）→ ✅**C 完成 @2026-09-04**（feat/upg96 **cdf769a9** 已 push origin[远端顶；基 main 806bb01c=UPG-94 已合]；**三处接线**：①**sendFromHome 不回落**[删 applyPresentationMode CLASSIC 切回——极简发送留极简，对话史经典侧照常 GONE 保留可回看] ②**回复转发**[homeDeliveryActive 投递回路开关 volatile+streamChunkSink 消费点 homeDeliveryActive 条件转发 homeWeb MovHomeHost.onLlmChunk[jsString 转义]+**完成文本回流** trimmed 同条件+**回路关闭** homeDeliveryActive=false 不残留至经典发送] ③**仲裁足迹**[HomeBridge.sendText 加 route 二参[JS 端 fp.route 传入]→原生 appendLog「[UPG-96 仲裁] route=…」journal 可查]；**94 转出两件**[index.html 构造 engine 后合并 MovRegistrySeed.entries[ticketCard/rideCard candidate 骨架可被 Intent 分派]+timelineList 骨架 CSS .tl/.tl-item/.tl-dot.done/.tt/.ts]；**失败诚实**[homeWeb 未装配/JS 异常 fail-safe 落经典+appendLog 日志点——不许静默]；**变异 3 锚形态实录**[M1 删 dock GONE 行→MinimalHomePolish 契约红/M2 删三处转发→HomeDelivery 契约红/M3 删 route 参数→仲裁 journal 锚红——还原复绿]；契约锚 **5/5**[锚①不回落/锚②chunk+trimmed 回流/锚③仲裁 journal/94 转出件①②]；全量 **108 套件 775/0/1 全绿**[763[U94]+5[UPG-96 契约]=768+其他自洽]；**模拟器不回落实证**[tap 切极简→发送→画面仍极简：dump texts 无经典 chips/胶囊——经典元素零出现]+经典恢复对照；**真机七场景收口=验收员持有**[②ASR/③出卡目测/⑥小圆片交互——含 UPG-88 PARTIAL 销项、UPG-89 出卡走查销项]；MainActivity 纯 CRLF 保持；Token/KV 0/0[chunk 转发为流转投不进 prompt]；coverage_status=**PARTIAL**[接线面 FULL[契约锚 5/5+模拟器实证]/真机批目测走查=持有——设计师裁决位]；DEL-UPG96-20260904-001[code=cdf769a9/artifact=04f48903/manifest_sha=a376d376]；报告 DELIVERY_UPG96_2026-09-04.md；**已登记两个表**）——待验收员验收（L1+变异复杀+真机七场景目测[持有]+合后 verify-hash 终态复核）
-→ **依赖**：UPG-94 先合（seed 未合并=接线也回落纯文本）；与 95 同 home 面建议串行
-→ **豁免**：MainActivity 棘轮军规注记——改既有对话链路线</t>
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-04**</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>📌 **已派单·待认领 @2026-09-04**（极简批阶段 2 收口=完全体单：不回落+onLlmChunk 回流+fail-safe</t>
+          <t>裁决位]；DEL-UPG96-20260904-001[code=cdf769a9/artifact=04f48903/manifest_s</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4388,12 +4385,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>验收员验收（L1+变异复杀+真机七场景目测[持有]+合后 verify-hash 终态复核）</t>
+          <t>✅ **审验 通过 @2026-09-04**（integrity_review=confirmed：与 §P50 一致，变异环比验收员更深</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 已合 main @6dcfbac9（feat/upg96 cdf769a9 合入+已 push；rebase ac7495fb 零冲突实</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4422,7 +4419,7 @@
         <is>
           <t>P1
 → **防撞**：纯前端单（mov-vue 源+产物同步）；MainActivity/tools 零行；与 95/96 零交集
-→ 🆕 **已认领 @2026-09-04 05:47**（程序员 Kimi/kimi-cli，worktree mov-upg97，branch feat/upg97，基 origin/main ac7495f；按派单施工：openPage 三 case 接线[先核实槽位键值实证]+comingSoon 兜底可见化+mov-vue 构建同步产物——纯前端零原生）
+→ 🆕 **已认领 @2026-09-04 05:47**（程序员 Kimi/kimi-cli，worktree mov-upg97，branch feat/upg97，基 origin/main ac7495f；按派单施工：openPage 三 case 接线[先核实槽位键值实证]+comingSoon 兜底可见化+mov-vue 构建同步产物——纯前端零原生）→ ✅**C 完成 @2026-09-04 06:5x**（程序员 Kimi/kimi-cli，feat/upg97 **9010075d** 已 push origin，基 origin/main ac7495f[含 UPG-93 已合 3315bff0]；**键值对齐实证链**：CapsuleResolver 静态表 page 键[tasks→workbench/vault→assets/memory→memory]+openPageByCapsule 分派表+PageTools 注册点三方闭合；**修复**：openBuiltin 补 workbench/assets/memory 三 case+兜底可见化[裸 toast→showDialog「该入口暂未开通」双字典]；**契约锚**：SidebarDispatchContractTest 4 锚[分派/键值对齐/兜底/回归]常驻；**双变异亲杀**红绿闭环[M1 删 memory case→2 锚红/M2 兜底回 toast→兜底锚红；两轮作废教训在案：CRLF 失配+restore 误回 HEAD→定点快照还原]；全量 **794/0/0**[110 套件]+bun 18/18+assembleDebug 绿；**产物链** vite build+sync-pages 103 文件同源同步[bundle sha 在档]；**真机平板五点验全过**[市场/订单/记忆/资产/能力逐点截图]；Token/KV 0/0；MainActivity/tools 零行；DEL-UPG97-20260904-001[code=9010075d/artifact bundle 7e212364/manifest 72035bc9 **deliver-gen 硬闸机制产出**]；verify-hash not-ancestor[未合常态，合后终态复核]；报告 DELIVERY_UPG97_2026-09-04.md；**已登记两个表**）——待验收员验收+设计师合 main
 → **教训**：导航类验收须「入口清单全点验」；9-02 openAssets 漏 case 同族——键值对齐须实证</t>
         </is>
       </c>
@@ -4433,17 +4430,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>🆕 **已认领 @2026-09-04 05:47**（程序员 Kimi/kimi-cli，worktree mov-upg97，bran</t>
+          <t xml:space="preserve">✅**C 完成 @2026-09-04 06:5x**（程序员 Kimi/kimi-cli，feat/upg97 **9010075d** </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>验收员验收+设计师</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>合 main</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4453,7 +4450,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG97-20260904-001</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4547,6 +4547,53 @@
         </is>
       </c>
       <c r="I87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>UPG-100</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>锚②半弱锚升级（count/match 组合断言）</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>✅ 立卡（UPG-96 审验发现项①转正：contains 组合锚对单点破坏免疫）｜ 待派单</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4270,7 +4270,8 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P48：分支头 25f73fe0[申报 746b20ec≠分支头二现]隔离 worktree——全量 763/0/1 亲跑一致+契约锚 4/4+**M1 删除式亲杀**[failures=1→还原；注释式免疫四现终纳]+四件观感修复核物；**P3×2：U89 引擎恢复自纠未申报**[透明度义务]+logo 168px 追加后截图未更新；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 带缺陷通过 @2026-09-04**（四件坐实+U89 恢复自纠亲核正确完整+四项发现登记）→ ✅ **已合 main @806bb01c @2026-09-04**（设计师B：rebase 3315bff0 三提交重写[25f73fe0→806bb01c——MainActivity 与 93 双改不同区域自动合并 clean]+ff-only+push+verify-hash HASH_OK；**设计师追加项验收缺口实录**：seed 合并进 engine.registry+timelineList 骨架 CSS 两项[2026-09-04 设计师裁决并 94 随批]未随本单落地——转出至 UPG-96 范围[接线单前置一件]，STD-96 追加说明区已注记；4 项发现裁决见问题区）
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P48：分支头 25f73fe0[申报 746b20ec≠分支头二现]隔离 worktree——全量 763/0/1 亲跑一致+契约锚 4/4+**M1 删除式亲杀**[failures=1→还原；注释式免疫四现终纳]+四件观感修复核物；**P3×2：U89 引擎恢复自纠未申报**[透明度义务]+logo 168px 追加后截图未更新；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 带缺陷通过 @2026-09-04**（四件坐实+U89 恢复自纠亲核正确完整+四项发现登记）
+→ ⚠️ **WIP 回滚 @2026-09-04**（UPG-98 拆分批②市场面——程序员 C：7 块搬移+13 提升+MarketTools 恢复完成[compileDebugKotlin EXIT=0]；**但 5 个测试失败**[锚定面迁移问题——HostBuiltin 2+ToolMeta 2+SceneWiring 1——非产品缺陷]；**toolFaceSrc 加 market/ 联合读源+MarketTools.kt 恢复 ac7495fb 版已 commit dff0ba8a/push**——**实施转独立会话**（锚定面迁移第二批+全量验证+冷启动锚+真机冒烟——上下文预算耗尽不带入半成品）；WIP 资产在案[upg98-拆分批2市场面交付记忆]）——**重新认领需独立完整会话**→ ✅ **已合 main @806bb01c @2026-09-04**（设计师B：rebase 3315bff0 三提交重写[25f73fe0→806bb01c——MainActivity 与 93 双改不同区域自动合并 clean]+ff-only+push+verify-hash HASH_OK；**设计师追加项验收缺口实录**：seed 合并进 engine.registry+timelineList 骨架 CSS 两项[2026-09-04 设计师裁决并 94 随批]未随本单落地——转出至 UPG-96 范围[接线单前置一件]，STD-96 追加说明区已注记；4 项发现裁决见问题区）
 → 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg94，branch feat/upg94，基 main fe258949[UPG-89 已合]；四件按派单行号施工[dock 字段化+applyPresentationMode 路由/logo 零装饰/heroHint 删/btnSend 归 token]+变异锚 2+截图四场景）
 → **依据**：呈现体系 v1.1 §三 L0 + v1.2 增补 §一；用户两条新拍板（heroHint 删除/logo 零装饰）@2026-09-04
 → **防撞**：MainActivity 只动 applyPresentationMode/dock 字段化</t>
@@ -4417,10 +4418,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>P1
+          <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-04**（ACCEPTANCE_LOG §P51：9010075d 工单系统仓隔离 worktree——全量 794/0/0 亲跑一致+**变异双锚亲杀**[分派锚 failures=2/兜底锚 failures=1→还原]+openBuiltin 三 case+comingSoon showDialog+i18n 双字典；**L2 真机四点验实证**[市场/资产/能力/订单]+**我的记忆行 5556 未呈现疑点转办**[平板五点验过——澄清后终判]；**达待合→审验员→设计师**）
 → **防撞**：纯前端单（mov-vue 源+产物同步）；MainActivity/tools 零行；与 95/96 零交集
 → 🆕 **已认领 @2026-09-04 05:47**（程序员 Kimi/kimi-cli，worktree mov-upg97，branch feat/upg97，基 origin/main ac7495f；按派单施工：openPage 三 case 接线[先核实槽位键值实证]+comingSoon 兜底可见化+mov-vue 构建同步产物——纯前端零原生）→ ✅**C 完成 @2026-09-04 06:5x**（程序员 Kimi/kimi-cli，feat/upg97 **9010075d** 已 push origin，基 origin/main ac7495f[含 UPG-93 已合 3315bff0]；**键值对齐实证链**：CapsuleResolver 静态表 page 键[tasks→workbench/vault→assets/memory→memory]+openPageByCapsule 分派表+PageTools 注册点三方闭合；**修复**：openBuiltin 补 workbench/assets/memory 三 case+兜底可见化[裸 toast→showDialog「该入口暂未开通」双字典]；**契约锚**：SidebarDispatchContractTest 4 锚[分派/键值对齐/兜底/回归]常驻；**双变异亲杀**红绿闭环[M1 删 memory case→2 锚红/M2 兜底回 toast→兜底锚红；两轮作废教训在案：CRLF 失配+restore 误回 HEAD→定点快照还原]；全量 **794/0/0**[110 套件]+bun 18/18+assembleDebug 绿；**产物链** vite build+sync-pages 103 文件同源同步[bundle sha 在档]；**真机平板五点验全过**[市场/订单/记忆/资产/能力逐点截图]；Token/KV 0/0；MainActivity/tools 零行；DEL-UPG97-20260904-001[code=9010075d/artifact bundle 7e212364/manifest 72035bc9 **deliver-gen 硬闸机制产出**]；verify-hash not-ancestor[未合常态，合后终态复核]；报告 DELIVERY_UPG97_2026-09-04.md；**已登记两个表**）——待验收员验收+设计师合 main
-→ **教训**：导航类验收须「入口清单全点验」；9-02 openAssets 漏 case 同族——键值对齐须实证</t>
+→ **教训**：导航类验收须「入口清单全点验」；9-02 openAssets 漏 case 同族——键值对齐须实证
+→ ✅ **已合 main @04ca51ab</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4435,12 +4437,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>验收员验收+设计师</t>
+          <t>✅ **验收员复验 带缺陷通过 @2026-09-04**（ACCEPTANCE_LOG §P51：9010075d 工单系统仓隔离 wor</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>合 main</t>
+          <t xml:space="preserve">✅ **已合 main @04ca51ab（2026-09-04 设计师合入）**：rebase origin/main 6dcfbac9 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4467,9 +4469,10 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>P1
+          <t>P1 → ❌ **验收员打回 @2026-09-03**（ACCEPTANCE_LOG §P51b：**P1 提交版测试文件编译不过**——d96ade5d HostBuiltinPackContractTest mainSrc() 裸换行截断字符串→compileDebugUnitTestKotlin FAILED→全量在提交版无法执行；对照实锤：程序员 worktree 同路径=正确版未提交——**提交版≠验证版实锤**；七块搬移结构核过[工作区读源+MarketTools.kt 恢复 U93 遗漏自查]；修=工作区正确版 commit+新 commit 交付+DEL 重绑+R1 全新检出复验；**打回→程序员**） → ⚠️ **§P51c 中间态核验 @2026-09-03**（ACCEPTANCE_LOG 补记：dff0ba8a mainSrc 修复实锤[:27 单行]采纳 §P51b；全量 795/6/1——4 类失败定性=**锚定面迁移未完成**[HostBuiltin seg 锚失效/MarketSplit 集合缺元素/ToolMeta internal 锚未更新/ToolsSplit 1 红——非产品缺陷]；**维持打回（WIP）**——锚定面迁移完成（0 失败）再交 R1 复验）
 → **范围**：市场总览区（buildLocalOverview/启停/安装投影）→ market/ 模块；纯搬移零逻辑改动；保真锚=块归一化 sha256 前后全等
-→ **防撞**：本批独占 MainActivity 市场区；与 95/96/97 零交集</t>
+→ **防撞**：本批独占 MainActivity 市场区；与 95/96/97 零交集（均已合/他面）；批③页面桥待本批合后派
+→ 🆕 **已认领 @2026-09-04 07:18**</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4479,12 +4482,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🆕 **已认领 @2026-09-04 07:18**（程序员 C/Claude-wmw0027，worktree mov-upg98，b</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ **验收员打回 @2026-09-03**（ACCEPTANCE_LOG §P51b：**P1 提交版测试文件编译不过**｜d96ade</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4594,6 +4597,53 @@
         </is>
       </c>
       <c r="I88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>UPG-101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>侧边栏默认插件种子清单（「我的记忆」入口是否纳入 defaults）</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>拍板@2026-09-04（UPG-97 合 main 随批</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>📌 挂单·待用户拍板 @2026-09-04（UPG-97 合 main 随批裁决转立；产品决策项非缺陷）</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>P1 → ❌ **验收员打回 @2026-09-03**（ACCEPTANCE_LOG §P51b：**P1 提交版测试文件编译不过**——d96ade5d HostBuiltinPackContractTest mainSrc() 裸换行截断字符串→compileDebugUnitTestKotlin FAILED→全量在提交版无法执行；对照实锤：程序员 worktree 同路径=正确版未提交——**提交版≠验证版实锤**；七块搬移结构核过[工作区读源+MarketTools.kt 恢复 U93 遗漏自查]；修=工作区正确版 commit+新 commit 交付+DEL 重绑+R1 全新检出复验；**打回→程序员**） → ⚠️ **§P51c 中间态核验 @2026-09-03**（ACCEPTANCE_LOG 补记：dff0ba8a mainSrc 修复实锤[:27 单行]采纳 §P51b；全量 795/6/1——4 类失败定性=**锚定面迁移未完成**[HostBuiltin seg 锚失效/MarketSplit 集合缺元素/ToolMeta internal 锚未更新/ToolsSplit 1 红——非产品缺陷]；**维持打回（WIP）**——锚定面迁移完成（0 失败）再交 R1 复验）
+          <t>P1 → ❌ **验收员打回 @2026-09-03**（ACCEPTANCE_LOG §P51b：**P1 提交版测试文件编译不过**——d96ade5d HostBuiltinPackContractTest mainSrc() 裸换行截断字符串→compileDebugUnitTestKotlin FAILED→全量在提交版无法执行；对照实锤：程序员 worktree 同路径=正确版未提交——**提交版≠验证版实锤**；七块搬移结构核过[工作区读源+MarketTools.kt 恢复 U93 遗漏自查]；修=工作区正确版 commit+新 commit 交付+DEL 重绑+R1 全新检出复验；**打回→程序员**） → ⚠️ **§P51c 中间态核验 @2026-09-03**（ACCEPTANCE_LOG 补记：dff0ba8a mainSrc 修复实锤[:27 单行]采纳 §P51b；全量 795/6/1——4 类失败定性=**锚定面迁移未完成**[HostBuiltin seg 锚失效/MarketSplit 集合缺元素/ToolMeta internal 锚未更新/ToolsSplit 1 红——非产品缺陷]；**维持打回（WIP）**——锚定面迁移完成（0 失败）再交 R1 复验） → 📌 **二次 WIP 如实申报处置 @2026-09-03**（脚本自动化搬移失败如实[fun 声明复杂度四条根因入册]——工作区还原 04ca51ab；**验收员核出申报不实一项**：6 文件 D 残留[gen93/scan93b/mut93 等 UPG-93 方法论资产被工作区删除未提交]——已代为恢复[git checkout，资产保全]；UPG-98 状态=**待重新认领·人工逐块搬移路径**[程序员建议：IDE 重构或手工 copy-paste 每块编译一次，30 分钟级]；工作树现状=feat/upg98@04ca51ab 干净） → ✅ **交付·待验收 @2026-09-04**（程序员重做完成[用户直派]：cherry-pick 上轮人工搬移 2787b73a[编译实证过的人工件非脚本]+锚定面迁移全收口=4b279e0a+d11509cc——全量 804/0/1（112 套件 --rerun-tasks）+3 变异锚亲杀红绿闭环[保真点名 buildLocalOverview/名单多挂点名 zzMutant/唯一写点点名 syncBuiltinPackTools]+冷启动双侧 5 次中位 940→932ms（Δ-0.9% 在带内）+真机三场景全过[市场页渲染/启停 185↔172 精确-13/logcat 双行/market.status 直呼]+assembleDebug 绿+Token/KV 0/0；**DEL-UPG98-001 绑分支头 d11509cc**（红线 23 推进=重绑）；manifest=deliver-gen 硬闸产出 ok:True[standard_id 内嵌 sha 交叉校验过]；报告 `程序员\交付报告\DELIVERY_UPG98_2026-09-04.md`；R1 复验→审验员→设计师） → ✅ **R1 复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P52：d11509cc 全新检出 **804/0/1 亲跑终验**[P1 提交版编译不过修复闭环]+MarketSplitContract 5 锚全绿[搬移保真契约锁]+变异 3 锚采信如实[验收员注入 3 轮未达真红——XML+契约双证采信]+L2 真机三场景采信[模拟器四度下线环境阻塞登记]；两观察转办[isAppVisible 不稳定/registry 依赖]；**达待合→审验员→设计师**） → ✅ **审验 confirmed 通过 @2026-09-04**（审验员：从零编译 804/0/0+1 跳过亲跑+变异采信升级亲杀[KDoc 改字→保真锚真红]+拆前 sha 独立抽查=冻结值+问题区 3 项） → ✅ **已合 main @d11509cc @2026-09-04**（04ca51ab→d11509cc 直接快进零冲突，verify-hash 通过；问题区 3 项裁决落档[isAppVisible 呈现通道缺口升级 P2 入审批收口议题/registry 依赖挂账残留面登记/3 函数 public 豁免注记入债务清单]；里程碑：上帝文件 7666→6016→5929 行；批③页面桥待派）
 → **范围**：市场总览区（buildLocalOverview/启停/安装投影）→ market/ 模块；纯搬移零逻辑改动；保真锚=块归一化 sha256 前后全等
 → **防撞**：本批独占 MainActivity 市场区；与 95/96/97 零交集（均已合/他面）；批③页面桥待本批合后派
 → 🆕 **已认领 @2026-09-04 07:18**</t>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>❌ **验收员打回 @2026-09-03**（ACCEPTANCE_LOG §P51b：**P1 提交版测试文件编译不过**｜d96ade</t>
+          <t>✅ **审验 confirmed 通过 @2026-09-04**（审验员：从零编译 804/0/0+1 跳过亲跑+变异采信升级亲杀[KDo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **已合 main @d11509cc @2026-09-04**（04ca51ab→d11509cc 直接快进零冲突，verify-h</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4644,6 +4644,58 @@
         </is>
       </c>
       <c r="I89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>UPG-102</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MainActivity 拆分·批③ 页面桥面搬移（→ pages/ 模块）</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>P1 → ✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P53：**真交付=d77dae2a**[申报 cfa7d607 错误——申报 sha 错误 P3]隔离 worktree——全量 **809/0/1 亲跑一致**+PagesSplitContractTest 5 用例[申报 6 差 1 注记]+**M2 亲杀**[browser.forward 行置空→「漏搬 browser handler」红→还原]+approvalService internal 复核；两块搬移纯搬移核物；**达待合→审验员→设计师**）
+→ 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg102，branch feat/upg102，基 main d11509cc；施工：browserHandlers 注册块[14 个 browser.*]+WebMcpHub.mountCallback 块→pages/ 模块顶层扩展——纯搬移零逻辑改动+3 变异锚+锚定面迁移收口[全量 0 失败硬门槛]+搬出函数显式 internal）
+→ ✅ **审验员独立复核 通过 @2026-09-04**（§P53 审验终态：从零编译 809/0/0+1 跳过 + 契约锚 5/5 + M2 亲杀复现一致 + 补强断言目标文本存在性核实[PageBridgeTools url http(s)/ref 有效——真实存在且 809 含它绿 M2 含它红]；**申报 sha 辨析定性修正**：cfa7d607=UPG-102 链契约锚补强[PagesSplitContractTest +3 逻辑级断言]——提交图证明必在 d77dae2a 之后，commit message 标「UPG-89」为误导标注；达待合→设计师）→ ✅ **已合 main @cfa7d607（2026-09-04 设计师合入：fast-forward d11509cc→cfa7d607 全链随批[补强有效自洽]；push `d11509cc..cfa7d607`）**
+→→ **设计师裁决**：①合 main 范围=全链 cfa7d607（采纳审验建议；commit message 误导标注不回溯改历史[force-push 风险]，定性以本卡为准）②P3 契约锚保真强度=登记挂账（搬移类工单统一 sha256 冻结范式——下批④起执行范式统一）③真机冒烟三场景=验收员 L3 持有（未核销）
+→ **范围**：页面桥面两块 → pages/ 模块；纯搬移零逻辑改动；保真锚=块归一化 sha256 前后全等；搬出函数全显式 internal（批② 3 函数漏写事故教训入红线）
+→ **防撞**：本批独占 MainActivity 页面桥区；与在飞单零交集；批④</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（拆分主线批③/共 8 批｜串行纪律：批② d11509cc 已合，本批基=main 顶</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg102，branch f</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>✅ **审验员独立复核 通过 @2026-09-04**（§P53 审验终态：从零编译 809/0/0+1 跳过 + 契约锚 5/5 + M</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ **已合 main @cfa7d607（2026-09-04 设计师合入：fast-forward d11509cc→cfa7d607 </t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-102_MainActivity拆分批3页面桥_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4696,6 +4696,53 @@
         </is>
       </c>
       <c r="I90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>UPG-103</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MainActivity 拆分·批④ chips/胶囊面搬移（→ ui/chips/ + ui/capsule/）</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>📌 **已派单·待认领 @2026-09-04**（拆分主线批④/共 8 批｜串行纪律：批③ cfa7d607 已合，本批基=main 顶</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>设计师\派单\UPG-103_MainActivity拆分批4芯片胶囊_派单_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4714,17 +4714,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 → 🆕 **已认领 @2026-09-04 20:50**</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>📌 **已派单·待认领 @2026-09-04**（拆分主线批④/共 8 批｜串行纪律：批③ cfa7d607 已合，本批基=main 顶</t>
+          <t>📌 **已派单·待认领 @2026-09-04**</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🆕 **已认领 @2026-09-04 20:50**（程序员/Claude-kimi，worktree mov-upg103，branc</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -850,22 +850,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>✅ 方案完成｜ feat/upg08 → main aa09882（ff，含R1/R2修复+同步）</t>
+          <t>❌ **作废 @2026-09-04（用户拍板：「UPG-08 可以删掉了」｜取消；历史上已合 main @aa09882 保留审计，后续以</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>✅C R2 修复完成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>验收员✅全部通过 @2026-08-26（R1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-26**（`aa09882`，ff 合入，同步产物 json 已移出版本库）</t>
+          <t>已合 main@aa09882 保留审计，后续以 UPG-08 相关迭代单/W-09 线承接）**</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>📝 **设计 v3.1 补丁 @2026-09-02**（Plan 模式=顺序真相层：两段式先 Plan 后执行+steps DAG+机器</t>
+          <t>🔄 **瘦身重派 @2026-09-04（用户拍板「建议瘦身转派」）**：本单=段①核心契约（联动机制+Trace+接线+契约语义）；段②</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4743,6 +4743,53 @@
         </is>
       </c>
       <c r="I91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>UPG-104</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>工具联动 Runtime 契约·段②（评测集+安全门+编排+记忆回流）</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>设计 v3/v3.1 全量保留归本单；待 UPG-46 段①</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>合 main后拆派单）</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG ff23a88）：feat/upg51 9ca96ff </t>
+          <t>✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P54：4e5a2f7c 隔离 worktree[申报</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4790,6 +4790,53 @@
         </is>
       </c>
       <c r="I92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>UPG-105</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MOV 官网·容器面（给 AI 读）建设</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>📌 **已立卡·待派 @2026-09-04**（设计 v3 定稿：`设计师/方案设计/工单方案/官网容器面_给AI看内容_设计_v3_2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>设计师/方案设计/工单方案/官网容器面_给AI看内容_设计_v3_2026-09-04.md</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4818,17 +4818,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**C 完成 @2026-09-04**（feat/upg105 **841f591d** 已 push origin，基 main c5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P55：841f591d 隔离 worktree｜全量</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **已合 main @2026-09-04**（设计师 ff `c5bb94af..841f591d` 已推 origin；批二即 UP</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG105-20260904-001</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -2025,17 +2025,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>🔄 **瘦身重派 @2026-09-04（用户拍板「建议瘦身转派」）**：本单=段①核心契约（联动机制+Trace+接线+契约语义）；段②</t>
+          <t>🔄 **用户拍板转交 @2026-09-05 02:19**（原认领程序员 Claude/wmw0027 做不了，用户指令转交）</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🆕 **已认领 @2026-09-05**（程序员 Claude/wmw0027，worktree mov-upg46，branch fe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️ **验收员 WIP 收口确认 @2026-09-04**（ACCEPTANCE_LOG §P56：bf757f9d 隔离 worktr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>❌ **已取消 @2026-09-03**（用户拍板「只要两种模式：经典+极简，极简只是画面极简不阉割能力」｜5→2 模式收敛转 UPG-8</t>
+          <t>拍板「只要两种模式：经典+极简，极简只是画面极简不阉割能力」｜5→2 模式收敛转 UPG-84：code 模式退役，本单修复对象消失，根因消</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>✅ 立卡（UPG-96 审验发现项①转正：contains 组合锚对单点破坏免疫）｜ 待派单</t>
+          <t>📌 已立卡·待派 ⏳ @2026-09-04（UPG-96 审验发现项①转正：contains 组合锚对单点破坏免疫）｜ 待派单</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>🔎**验收员独立复核 @2026-08-29**（@main 107f9c2，与设计师刷新独立互证一致）：29/29 占位仍死（清单 24</t>
+          <t xml:space="preserve">✅ **验收通过 @2026-08-30**（ACCEPTANCE_LOG「验收：UPG-18 死代码清理」段：L1 全量 376/0/0 </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>合 main，现 main 仅 UPG-05 952d035 一路接线）；ACCEPTANCE_LOG 落档（1407628） **卡点**</t>
+          <t>✅ **已合 main @2026-08-30**（merge **6103bb8c**｜批1-4+批2修正全量在链；resolve：Mai</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>🆕 **已认领 @2026-09-05**（程序员 Claude/wmw0027，worktree mov-upg46，branch fe</t>
+          <t xml:space="preserve">✅**C 完成 @2026-09-05 03:02**（程序员 Kimi/kimi-cli，feat/upg46 **a8043aad** </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>⚠️ **验收员 WIP 收口确认 @2026-09-04**（ACCEPTANCE_LOG §P56：bf757f9d 隔离 worktr</t>
+          <t>✅ **验收员复验通过 @2026-09-05**（§P57 落档：六件核物全在/M-cycle 锚链成立/837 差 1 双方 P3 注记</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **审验员确认+设计师合 main @7ccf0446**（2026-09-05：段①核心契约全链合入；段②=UPG-104） **卡点</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3634,10 +3634,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P37：3339c4b 隔离 worktree——全量 **734/0/1 亲跑终验，基线预存 2 失败消除**+契约锚与现实对齐非消音[L1-10 认账收拢现实+M-U50-5 改锚 render-only 真实表达]+**K1 亲杀**[旧断言回潮红→还原]+manifest_sha 一致；**达待合→设计师**——合后全量回归=0 失败基线） → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39：8609d69 隔离 worktree——**§P36 转单 P1 闭环**：removeAll→indexOfFirst+removeAt+&gt;=0 守卫[同 tool 后续保留可勾选]+取舍论证实锤+全量 730/2/1 亲跑一致[PlanApproval 35]+**M1 亲杀**[failed=3 与申报一致]；L2 真机呈现环境阻塞登记[需 AI key]；**达待合→审验员→设计师**）
-→ **依据**：用户拍板裁决（UPG70_裁决记录 裁决项 1）——基线 2 失败（L2-9 1B + M-U50-5，收拢版带病合入遗留）处置=契约锚同步修，归属阶段 1 维护单；消灭「pre-existing」口径恢复全量 0 失败
-→ 🆕 **已认领 @2026-09-03 08:55**（程序员 Claude/wmw0027，worktree mov-upg81，branch feat/upg81，2026-09-03 认领登记，基 main 5cf546d[UPG-79 已合入]；按派单施工：修前复跑实证 L2-9 1B + M-U50-5 两红留 XML → 逐案断言适配收拢版现实（来源文件:行号）→ 修后全量 --rerun-tasks 0 失败 → 亲杀锚断言破坏必红 → Token/KV 0/0 → 交付报告 + 登记两表）
-→ ✅ **C 交付 @2026-09-03 09:19**</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3657,7 +3654,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>合 main</t>
+          <t>✅ **已合 main（补登 @2026-09-05）**（审验员 09-05 核实：3339c4b patch-id≡**fab7d29*</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3829,9 +3826,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>P1
-→ ✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39 + 审验 confirmed：8609d69 修复坐实[indexOfFirst+removeAt+守卫]、取舍论证亲读成立、契约锚含防脱钩绑定、M1 亲杀独立复验 3 红→还原零残留、全量 730/2/1 一致；§P36 转单 P1「发现→转单→修复→验收」全链闭环；**达待合→设计师**）
-→ ✅ **已合 main @ad1e0a8 @2026-09-03**</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3846,7 +3841,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39 + 审验 confirmed：8609d</t>
+          <t>✅ **已闭环（补登 @2026-09-05）**（审验员 09-05 核实：本单实物=8609d69 预审单 removeAll 修复[r</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4724,12 +4719,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>🆕 **已认领 @2026-09-04 20:50**（程序员/Claude-kimi，worktree mov-upg103，branc</t>
+          <t>✅ **C 交付 @2026-09-04 23:05**（feat/upg103 **4e5a2f7c** 已 push origin；设计</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠️ **审验 unresolved @2026-09-05**（实质可信｜审验员独立复现 recon103 9/9 块 ALL_OK；**</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4839,6 +4834,53 @@
       <c r="I93" t="inlineStr">
         <is>
           <t>DEL-UPG105-20260904-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>UPG-106</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>数字人体 V1（2D 全身部位图 + 健身挂点）</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>🆕 **立卡 @2026-09-05**（用户拍板方向：2D 全身正面人形图（简单为先，不做 3D）｜「做就做 2D 全身正面就可以了，简</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4855,7 +4855,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>🆕 **立卡 @2026-09-05**（用户拍板方向：2D 全身正面人形图（简单为先，不做 3D）｜「做就做 2D 全身正面就可以了，简</t>
+          <t>📋 **架构评审稿已出**：`人体载体/数字人体_融入MOV架构_评审稿_2026-09-05.md`（与 MOV 契合度审查+合规红线+</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4739,7 +4739,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG103-20260904-001</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4724,12 +4724,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>⚠️ **审验 unresolved @2026-09-05**（实质可信｜审验员独立复现 recon103 9/9 块 ALL_OK；**</t>
+          <t>✅ **审验员转通过 @2026-09-05**（四断收口逐项复核全绿：STD v2 重冻=51584a7d 一致/DEL 绑定 manif</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ **设计师合 main @97d7ca31**（2026-09-05：批④ chips/胶囊面搬移全链合入；合后 verify-hash</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>📋 **架构评审稿已出**：`人体载体/数字人体_融入MOV架构_评审稿_2026-09-05.md`（与 MOV 契合度审查+合规红线+</t>
+          <t>✅ **大神评审通过 8.8/10（有条件）@2026-09-05 → v2.1 冻结稿已出**：`人体载体/数字人体_融入MOV架构_评审</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>审验通过 @2026-08-27（整单 a49c68a+583a40f+6410cb3 无已知缺陷：#8</t>
+          <t>✅ **审验通过 @2026-08-27（整单 a49c68a+583a40f+6410cb3 无已知缺陷：#8 复验成立、#9 独立复验含</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>】；【⛔ **部分打回 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg63 0580fa8 基</t>
+          <t>⚠️ **错挂注记 @2026-09-05（设计师）**：以下打回段主体=feat/upg63 0580fa8，属 **UPG-63** 卡</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>合 main</t>
+          <t>✅ **已合 main @34c37f54（补登 @2026-09-05，设计师核物）**：=交付提交 e4aa2a6 的 patch-id</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4881,6 +4881,53 @@
       <c r="I94" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>UPG-107</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Memory OS 类型化 payload（Semantic 池子结构化演进）</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>裁决位]；DEL-UPG107-20260905-001[code=31640fc8/artifact=fc07ee63/manifest=</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-09-05**（feat/upg107 **31640fc8** 已 push origin[origin=gi</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>审验ok:true]/报告=程序员/交付报告/DELIVERY_UPG107_2026-09-05.md｜状态区投影锚+交付段详）</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>设计师/方案设计/04_记忆/Memory_OS_类型化payload_设计_v1_2026-09-05.md</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>DEL-UPG107-20260905-001</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,12 +526,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**C 批 4 完成 @2026-08-30**（feat/upg01-b4 **8cf7a2f 前段 + 5f5219c 后段** 已 </t>
+          <t>✅**C 批 4 完成 @2026-08-30**（feat/upg01-b4 **8cf7a2f 前段 + 5f5219c 后段** 已</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG b71b306）：feat/upg64 115762d </t>
+          <t>【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG b71b306）：feat/upg64 115762d</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**M3-R2 三件修复完成 @2026-08-29**（feat/upg02 **5c113cb** 已 push origin，基底 </t>
+          <t>✅**M3-R2 三件修复完成 @2026-08-29**（feat/upg02 **5c113cb** 已 push origin，基底</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**设计师合 main @2026-08-29（merge 66244f4，合后终态 5170421 全量亲跑 45 类 316/0/0 </t>
+          <t>✅**设计师合 main @2026-08-29（merge 66244f4，合后终态 5170421 全量亲跑 45 类 316/0/0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅验收员通过 @2026-08-27（308cabf 独立复核：L1 全量 228 绿+变异亲杀 2/2 + L2 真机八场景全过；带缺陷 </t>
+          <t>✅验收员通过 @2026-08-27（308cabf 独立复核：L1 全量 228 绿+变异亲杀 2/2 + L2 真机八场景全过；带缺陷</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">**设计师✅已合 main @2026-08-28**（merge ee312f5，已推 origin；主 worktree 签名参数已落 </t>
+          <t>**设计师✅已合 main @2026-08-28**（merge ee312f5，已推 origin；主 worktree 签名参数已落</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**设计师已合 main @2026-08-28（merge 36d7f6e 已推 origin）｜UPG-17 全链闭环**（合后全量 </t>
+          <t>✅**设计师已合 main @2026-08-28（merge 36d7f6e 已推 origin）｜UPG-17 全链闭环**（合后全量</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **验收通过 @2026-08-30**（ACCEPTANCE_LOG「验收：UPG-18 死代码清理」段：L1 全量 376/0/0 </t>
+          <t>✅ **验收通过 @2026-08-30**（ACCEPTANCE_LOG「验收：UPG-18 死代码清理」段：L1 全量 376/0/0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收员 R1 L2 复验通过 @2026-08-29**（三连全过：①装配打点落新 session jsonl memory/ref </t>
+          <t>✅**验收员 R1 L2 复验通过 @2026-08-29**（三连全过：①装配打点落新 session jsonl memory/ref</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">修复完成@2026-08-29**（feat/upg23 **0bfa4fa** 已 push origin；`runOnUiThread </t>
+          <t>修复完成@2026-08-29**（feat/upg23 **0bfa4fa** 已 push origin；`runOnUiThread</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**已合 main @2026-08-30**（设计师 merge 8f8debd，含 2ccce25；§六 抽查通过 13 项+候选C </t>
+          <t>✅**已合 main @2026-08-30**（设计师 merge 8f8debd，含 2ccce25；§六 抽查通过 13 项+候选C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8fc 已推 </t>
+          <t>审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8fc 已推</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**C 完成 @2026-09-05 03:02**（程序员 Kimi/kimi-cli，feat/upg46 **a8043aad** </t>
+          <t>✅**C 完成 @2026-09-05 03:02**（程序员 Kimi/kimi-cli，feat/upg46 **a8043aad**</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **审验通过 @2026-09-01**（integrity_review=confirmed：P2-1a 72px 像素实证+删📌 </t>
+          <t>✅ **审验通过 @2026-09-01**（integrity_review=confirmed：P2-1a 72px 像素实证+删📌</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**三轮评审采纳升 v2.2 工程冻结版 @2026-09-01**（评分 架构 9.2/安全 8.8/迁移 8.2/UI 9.1/工程 </t>
+          <t>✅**三轮评审采纳升 v2.2 工程冻结版 @2026-09-01**（评分 架构 9.2/安全 8.8/迁移 8.2/UI 9.1/工程</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在 </t>
+          <t>📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG c25aacf）：feat/upg56 cc86fac </t>
+          <t>【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG c25aacf）：feat/upg56 cc86fac</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">审验36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledger 写入 actor=system-deriver]/L1 </t>
+          <t>审验36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledger 写入 actor=system-deriver]/L1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收通过+审验通过 @2026-08-31**（9f9466d 落档：9 项测试锚+77 套件 546/0/0+变异 M1/M3v2 </t>
+          <t>✅**验收通过+审验通过 @2026-08-31**（9f9466d 落档：9 项测试锚+77 套件 546/0/0+变异 M1/M3v2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**审验通过+已合 main @2026-08-31**（审验 35→36：四范围核物+L1 74 套件 523/0/0 独立重跑+变异 </t>
+          <t>✅**审验通过+已合 main @2026-08-31**（审验 35→36：四范围核物+L1 74 套件 523/0/0 独立重跑+变异</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批 </t>
+          <t>🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b </t>
+          <t>✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批 </t>
+          <t>🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b </t>
+          <t>✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg66 1e604c7 </t>
+          <t>【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg66 1e604c7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>📌 新立 @2026-09-02（用户拍板：App 内浏览器先 MCP 改造｜站点侧并行试点）｜待派单可认领</t>
+          <t>已派单（用户直接外派 @2026-09-05——撤销改向挂起，原 mow.kim 工单站口径继续）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>改向挂起：试点职能由 UPG-105 批二承接，工单三工具留商家后台线</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **审验 通过 @2026-09-02**（integrity_review 与 §P27 一致｜L1①/②/④/⑤ 亲跑全坐实；观察 </t>
+          <t>✅ **审验 通过 @2026-09-02**（integrity_review 与 §P27 一致｜L1①/②/④/⑤ 亲跑全坐实；观察</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **已合 main @add9e8c**（快进合入+已 push；元能力线合序 71→72→73 完成）｜ DONE **前置**：✅ </t>
+          <t>✅ **已合 main @add9e8c**（快进合入+已 push；元能力线合序 71→72→73 完成）｜ DONE **前置**：✅</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P31：a7736b3 隔离 worktree｜全量 </t>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P31：a7736b3 隔离 worktree｜全量</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree｜模块 </t>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree｜模块</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree｜全量 </t>
+          <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree｜全量</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**C 完成 @2026-09-04 03:3x**（程序员 Kimi/kimi-cli，feat/upg93 **c969b05a** </t>
+          <t>✅**C 完成 @2026-09-04 03:3x**（程序员 Kimi/kimi-cli，feat/upg93 **c969b05a**</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅**C 完成 @2026-09-04 06:5x**（程序员 Kimi/kimi-cli，feat/upg97 **9010075d** </t>
+          <t>✅**C 完成 @2026-09-04 06:5x**（程序员 Kimi/kimi-cli，feat/upg97 **9010075d**</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **已合 main @04ca51ab（2026-09-04 设计师合入）**：rebase origin/main 6dcfbac9 </t>
+          <t>✅ **已合 main @04ca51ab（2026-09-04 设计师合入）**：rebase origin/main 6dcfbac9</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">已合 main@hash」在祖先链/存量 cherry-pick 卡豁免/显式豁免跳过]｜首跑即抓 7 条存量异常全归因[5 存量豁免+1 </t>
+          <t>已合 main@hash」在祖先链/存量 cherry-pick 卡豁免/显式豁免跳过]｜首跑即抓 7 条存量异常全归因[5 存量豁免+1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **已合 main @cfa7d607（2026-09-04 设计师合入：fast-forward d11509cc→cfa7d607 </t>
+          <t>✅ **已合 main @cfa7d607（2026-09-04 设计师合入：fast-forward d11509cc→cfa7d607</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已合 main @31640fc8（ff-only；P 段数 56→56 无丢失；验收+审验全链闭环）</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4928,6 +4928,100 @@
       <c r="I95" t="inlineStr">
         <is>
           <t>DEL-UPG107-20260905-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>UPG-108</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>手机即服务器·官网用户面（扫码配对 + 手机内容投影上站）</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>UPG-109</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>第三方站 WebMCP 接入性扫描（agent 浏览器前置探测）</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,22 +1258,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UPG-14</t>
+          <t>W-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>设置页收口（账号卡接真 + 退出登录去重 + 两行死链修复）</t>
+          <t>资产档案表（T6 落地：商标/证书/域名/密钥登记收编）</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>方案完成待派单（P2）</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-28（R2 e16fae8 三判据全过 + R2 复修 04341d2 全产物口径零命中）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（全链 9323975→ce5ab0d→e16fae8→1825338→04341d2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPG-15</t>
+          <t>W-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>登录页死锁修（登录钮常可点 + 协议整行可点）</t>
+          <t>事件日历视图 + 总览仪表盘四组件</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>方案完成待派单（P2）</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-28（151fdb1 独立复核：L1 全量 246 绿 + 变异亲杀 3/3 + L2 五图证据链；无缺陷）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（merge 509ab0c，ACCEPTANCE_LOG append-only 冲</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1352,12 +1352,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UPG-16</t>
+          <t>UPG-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>release 签名配置收口（明文口令外移）</t>
+          <t>设置页收口（账号卡接真 + 退出登录去重 + 两行死链修复）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>✅验收员通过 @2026-08-28（172e67d 独立复核：L1 全量 243 绿 + apksigner 签名有效 + L2 口令文件</t>
+          <t>✅验收员通过 @2026-08-28（R2 e16fae8 三判据全过 + R2 复修 04341d2 全产物口径零命中）</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（merge ee312f5，已推 origin；主 worktree 签名参数已落</t>
+          <t>**设计师✅已合 main @2026-08-28**（全链 9323975→ce5ab0d→e16fae8→1825338→04341d2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UPG-17</t>
+          <t>UPG-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>App demo 假数据全清（Vue 侧）</t>
+          <t>登录页死锁修（登录钮常可点 + 协议整行可点）</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-28（feat/upg17 96c963d，3 commits：926d70b feat+1f532cb buil</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>✅**验收员通过 @2026-08-28 深夜**（独立复核全过：L1 `--rerun-tasks` 36 类 253/0/0 吻合+sy</t>
+          <t>✅验收员通过 @2026-08-28（151fdb1 独立复核：L1 全量 246 绿 + 变异亲杀 3/3 + L2 五图证据链；无缺陷）</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>✅**设计师已合 main @2026-08-28（merge 36d7f6e 已推 origin）｜UPG-17 全链闭环**（合后全量</t>
+          <t>**设计师✅已合 main @2026-08-28**（merge 509ab0c，ACCEPTANCE_LOG append-only 冲</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,37 +1446,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UPG-18</t>
+          <t>UPG-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Android 死代码清理</t>
+          <t>release 签名配置收口（明文口令外移）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>✅ 方案完成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>🛠 在施 C @2026-08-30 01:39（认领=worktree mov-upg18 branch feat/upg18）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>✅ **验收通过 @2026-08-30**（ACCEPTANCE_LOG「验收：UPG-18 死代码清理」段：L1 全量 376/0/0</t>
+          <t>✅验收员通过 @2026-08-28（172e67d 独立复核：L1 全量 243 绿 + apksigner 签名有效 + L2 口令文件</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>✅ **已合 main @2026-08-30**（merge **6103bb8c**｜批1-4+批2修正全量在链；resolve：Mai</t>
+          <t>**设计师✅已合 main @2026-08-28**（merge ee312f5，已推 origin；主 worktree 签名参数已落</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1493,12 +1493,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPG-19</t>
+          <t>UPG-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>应用图标换 MOV 竖眼 Logo</t>
+          <t>App demo 假数据全清（Vue 侧）</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C 完成@2026-08-28（feat/upg17 96c963d，3 commits：926d70b feat+1f532cb buil</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>✅**验收员复验通过 @2026-08-28**（验收对象=入库链 feat/upg19 fa8fdd1+2c6b777+82a5322：L</t>
+          <t>✅**验收员通过 @2026-08-28 深夜**（独立复核全过：L1 `--rerun-tasks` 36 类 253/0/0 吻合+sy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>**设计师✅已合 main @2026-08-28**（merge 17b4e04 已推 origin；mov-upg19 worktree</t>
+          <t>✅**设计师已合 main @2026-08-28（merge 36d7f6e 已推 origin）｜UPG-17 全链闭环**（合后全量</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1540,37 +1540,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UPG-20</t>
+          <t>UPG-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>聊天页 chips 改造 v2（气泡式 切换模型+MCP 工具）</t>
+          <t>Android 死代码清理</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>**转派 @2026-08-28 18:35（用户拍板）**：C 认领后零提交 11h（分支仍 8aaa999）、主线在 UPG-17｜转派</t>
+          <t>✅ 方案完成</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>🔨 已派单，C 已认领在施 @2026-08-28 07:45（worktree=mov-upg20 branch=feat/upg20，</t>
+          <t>🛠 在施 C @2026-08-30 01:39（认领=worktree mov-upg18 branch feat/upg18）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>✅验收员复验通过 @2026-08-28 深夜（装机实证：二级 refit 重锚底部 2062≤chip 顶 2113 贴上沿不悬空、MCP</t>
+          <t>✅ **验收通过 @2026-08-30**（ACCEPTANCE_LOG「验收：UPG-18 死代码清理」段：L1 全量 376/0/0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>✅**设计师已合 main @2026-08-28（merge 974f33a 已推 origin）｜UPG-20 全链闭环**（合前独立复</t>
+          <t>✅ **已合 main @2026-08-30**（merge **6103bb8c**｜批1-4+批2修正全量在链；resolve：Mai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UPG-21</t>
+          <t>W-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聊天页输入框回车键=发送（IME 发送键修复）</t>
+          <t>account-service 安全加固</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>✅程序员 C 完成 @2026-08-29（feat/upg21 a14ee64，基于 main 198e26f；报告 DELIVERY_U</t>
+          <t>✅ C 完成 @2026-09-05（655b148d，9 隐患清零，待验收）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>验收员通过 @2026-08-29（</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-29（merge 5170421 已推 origin）｜UPG-21 全链闭环**（审验员五步独立实</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1627,19 +1627,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-W11-20260905-001</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UPG-22</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>记忆尾单（UPG-05 遗留收口：COVER_HIT 装配打点 + 剧本断言 + 冗余清理）</t>
+          <t>MOV 域迁移（市场迁 mov-ai.cn，API 双跑兜底）</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1649,27 +1649,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>方案完成待派单（ICP 硬阻塞注记：09-04 备案号已上页脚，阻塞或已解除待核实）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-29 16:48**（feat/upg22 **aacb15b** 已 push origin，基线已 f</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>✅**验收员 R1 L2 复验通过 @2026-08-29**（三连全过：①装配打点落新 session jsonl memory/ref</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-29**（程序员代行设计师：rebase 87787b8 后 ff-only **495060f**</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-22_记忆尾单_派单_2026-08-29.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UPG-23</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>本地 tab「本机能力总览」+ 主页钉选小按钮</t>
+          <t>市场首页去 demo 化（接 registry + 空态诚实 + 死链清理）</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>修复完成@2026-08-29**（feat/upg23 **0bfa4fa** 已 push origin；`runOnUiThread</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>✅**验收员复验通过 @2026-08-29**（diff 恰 1 行无夹带 + L1 338/0/0 亲跑 + 真机 5556：钉选/取消</t>
+          <t>✅ 验收通过 @2026-08-29（公网+服务器双实证）</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>✅**审验通过 → 已合 main @2026-08-29**（查验员逐项亲核确认；设计师 §六抽查：R1_05 主页钉选排免重启当场可见亲</t>
+          <t>✅ 已闭环（服务端生效，无 main 合并对象）</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1728,12 +1728,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UPG-24</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MOV 设计规范 v1（风格定性 + token 坐标表）</t>
+          <t>市场站 bug 批修 + 死文件清理</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>❌ **已作废 @2026-09-02**（用户拍板：设计规范 v1 文档已删｜由 v2/v2.1+UPG-50 外观组件体系接替；本卡销账</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 程序员完成 @2026-08-29（87ec0a1；部署卡腾讯云扫码墙）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>设计师/方案设计/MOV设计规范_v1.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1775,42 +1775,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UPG-25</t>
+          <t>W-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UI 瑕疵批修（规范 v1 待并轨清单 13 项）</t>
+          <t>workbench 前端小修批</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>裁决=MainActivity/PhotoAskSheet 文本底色取 UiTokens、primary 保 upg40 mov_prima</t>
+          <t>方案完成待派单（P3 小修批）</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-29**（feat/upg25 **62986c2** 已推 origin｜含 merge origin/main</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>❌**打回@2026-08-30**：与已合 UPG-40 换肤**同文件双改**（WorkbenchPage/demo.js/MainAc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-30**（设计师 merge 8f8debd，含 2ccce25；§六 抽查通过 13 项+候选C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-25_重修_派单_2026-08-30.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UPG-26</t>
+          <t>S-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>侧边栏品牌区换 logo+黑字 + 抽屉展开占比 61.8%</t>
+          <t>MOV 公众官网一期（用户下载门户 + 创作者开发者中心）</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>裁决]；用户确认已实现 @2026-09-02）→</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>✅ 验收通过（用户确认「已实现」）@2026-09-02（feat/sidebar-brand 7a6dff6+0fdfe87：品牌区 lo</t>
+          <t>✅ 验收通过 @2026-08-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>**分支未合 main（162 分叉）｜已合 main@2026-09-02（feat/sidebar-brand 7a6dff6/0fdf</t>
+          <t>✅ 已合 main @ce1ab567</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1869,12 +1869,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UPG-28</t>
+          <t>UPG-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>obsidian.file.write 审批闸修复（isHarmless file.write 特判误捕）</t>
+          <t>应用图标换 MOV 竖眼 Logo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>✅**方案 v1 已出 @2026-08-29**（`设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md`）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>✅**程序员 C 完成 @2026-08-30 01:05**（feat/upg28 **443b288** 已 push origin，基</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>✅**验收员验收通过 @2026-08-30**（L1 377/0/0 亲跑+变异 M1/M2 双锚亲杀+L2 采纳模拟器证据[真机 ASK</t>
+          <t>✅**验收员复验通过 @2026-08-28**（验收对象=入库链 feat/upg19 fa8fdd1+2c6b777+82a5322：L</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>✅**已合 main @443b288**（ff-only 已推 origin，合后全量复跑 377/0/0 绿；worktree mov-</t>
+          <t>**设计师✅已合 main @2026-08-28**（merge 17b4e04 已推 origin；mov-upg19 worktree</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1916,12 +1916,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UPG-44</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AcceptanceJudge B1 观察层（UPG-06 批2 剩项）</t>
+          <t>官网「能力市场」页（/home/market/，与 App 市场同源）</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>裁决criteria+AI 回复→verdict/失败静默]；**投影剔键硬红**=Surface.deriveEventMessage 显</t>
+          <t>**转派 @2026-08-28 18:35（用户拍板）**：C 认领后零提交 11h（分支仍 8aaa999）、主线在 UPG-17｜转派</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C 完成@2026-08-30 04:05**（feat/upg44 **122945b** 基底 main 3263f10 已 push；</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8fc 已推</t>
+          <t>✅ 验收通过 @2026-08-28（471ae65 独立复核）</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>✅**验收+审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8</t>
+          <t>✅ 已合 main @dc1405bc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-44_AcceptanceJudge_B1_派单_2026-08-30.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1963,42 +1963,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UPG-45</t>
+          <t>UPG-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>审批 · Approval Capability Registry（权限能力注册表）</t>
+          <t>聊天页 chips 改造 v2（气泡式 切换模型+MCP 工具）</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>🔨**已派单 @2026-08-30**（用户已转派；派单文本 `设计师/派单/UPG-45_审批_ApprovalRegistry_派单</t>
+          <t>**转派 @2026-08-28 18:35（用户拍板）**：C 认领后零提交 11h（分支仍 8aaa999）、主线在 UPG-17｜转派</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔨 已派单，C 已认领在施 @2026-08-28 07:45（worktree=mov-upg20 branch=feat/upg20，</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>✅**验收员通过 @2026-08-30**（ACCEPTANCE_LOG UPG-45，commit edf86d9）：核物[54行=as</t>
+          <t>✅验收员复验通过 @2026-08-28 深夜（装机实证：二级 refit 重锚底部 2062≤chip 顶 2113 贴上沿不悬空、MCP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>**已合 main @2026-08-31 → 审验员**（approval 体系随 UPG-58/62/63 合入；ApprovalSer</t>
+          <t>✅**设计师已合 main @2026-08-28（merge 974f33a 已推 origin）｜UPG-20 全链闭环**（合前独立复</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>设计师\方案设计\审批弹窗_用户授权层_设计_v3_2026-08-30.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2010,42 +2010,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UPG-46</t>
+          <t>UPG-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>工具联动 Runtime 契约（Tool Orchestration）</t>
+          <t>聊天页输入框回车键=发送（IME 发送键修复）</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>🔄 **用户拍板转交 @2026-09-05 02:19**（原认领程序员 Claude/wmw0027 做不了，用户指令转交）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-09-05 03:02**（程序员 Kimi/kimi-cli，feat/upg46 **a8043aad**</t>
+          <t>✅程序员 C 完成 @2026-08-29（feat/upg21 a14ee64，基于 main 198e26f；报告 DELIVERY_U</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>✅ **验收员复验通过 @2026-09-05**（§P57 落档：六件核物全在/M-cycle 锚链成立/837 差 1 双方 P3 注记</t>
+          <t>验收员通过 @2026-08-29（</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>✅ **审验员确认+设计师合 main @7ccf0446**（2026-09-05：段①核心契约全链合入；段②=UPG-104） **卡点</t>
+          <t>✅**已合 main @2026-08-29（merge 5170421 已推 origin）｜UPG-21 全链闭环**（审验员五步独立实</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-46_工具联动Runtime契约_派单_2026-09-02.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2057,42 +2057,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UPG-47</t>
+          <t>UPG-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>主页胶囊系统（pin_type+stableId / 三区 / ＋管理弹层 / 点击分派 / 长按 / 第三态 / 气泡字数）</t>
+          <t>记忆尾单（UPG-05 遗留收口：COVER_HIT 装配打点 + 剧本断言 + 冗余清理）</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>🔨已派单</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>✅C 交付 @2026-08-30（feat/capsule-system **767228c+32ba01c** push；报告 程序员/</t>
+          <t>✅**C 完成 @2026-08-29 16:48**（feat/upg22 **aacb15b** 已 push origin，基线已 f</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P54：4e5a2f7c 隔离 worktree[申报</t>
+          <t>✅**验收员 R1 L2 复验通过 @2026-08-29**（三连全过：①装配打点落新 session jsonl memory/ref</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>✅后续美化已合 main @2026-08-31（dock 对齐 **afc1ccd**：＋号圆形·随胶囊横滑·气泡左对齐胶囊；管理面板设置</t>
+          <t>✅**已合 main @2026-08-29**（程序员代行设计师：rebase 87787b8 后 ff-only **495060f**</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-22_记忆尾单_派单_2026-08-29.md</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2104,37 +2104,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UPG-48</t>
+          <t>UPG-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Memory API 工程契约（记忆页:memory-core/memory-api 模块化）</t>
+          <t>本地 tab「本机能力总览」+ 主页钉选小按钮</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>🔨已派单 @2026-08-30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>修复完成@2026-08-29**（feat/upg23 **0bfa4fa** 已 push origin；`runOnUiThread</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>❌**审验打回@2026-08-30（P1 边界违例）**｜MainActivity:582-598 直引 com.hermes.mov.m</t>
+          <t>✅**验收员复验通过 @2026-08-29**（diff 恰 1 行无夹带 + L1 338/0/0 亲跑 + 真机 5556：钉选/取消</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-30**（设计师 merge 92d4c22[含 0aa0c07]，审验五步复核通过：零直触core</t>
+          <t>✅**审验通过 → 已合 main @2026-08-29**（查验员逐项亲核确认；设计师 §六抽查：R1_05 主页钉选排免重启当场可见亲</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2151,106 +2151,106 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UPG-49</t>
+          <t>UPG-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>记忆页「我的记忆」UI 分层管理</t>
+          <t>MOV 设计规范 v1（风格定性 + token 坐标表）</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>✅ 方案 v4 定稿（记忆页分层管理_设计_v4 大神 9.2 冻结）</t>
+          <t>❌ **已作废 @2026-09-02**（用户拍板：设计规范 v1 文档已删｜由 v2/v2.1+UPG-50 外观组件体系接替；本卡销账</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>🔨 **程序员 R2 修复交付 @2026-09-01**（feat/upg49-r2 **5640bce** 已 push origin</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>✅ **审验通过 @2026-09-01**（integrity_review=confirmed：P2-1a 72px 像素实证+删📌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>✅ **设计师终审合流 @2026-09-02**（B9edcc4 落档+工单库补登；2 治理项裁决见下）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/方案设计/MOV设计规范_v1.md</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DEL-UPG49-20260901-002</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UPG-50</t>
+          <t>UPG-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>外观·组件级显示（Display Appearance 工程契约）</t>
+          <t>UI 瑕疵批修（规范 v1 待并轨清单 13 项）</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>📌 **激活 @2026-09-02（用户拍板：出工单完善验收后派活）**</t>
+          <t>裁决=MainActivity/PhotoAskSheet 文本底色取 UiTokens、primary 保 upg40 mov_prima</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>**✅ C 交付 @2026-09-01**（branch=feat/upg50，commit ca984df+8e73e8d｜A UI 编</t>
+          <t>C 完成@2026-08-29**（feat/upg25 **62986c2** 已推 origin｜含 merge origin/main</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>✅ **阶段2 复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P25：feat/upg50-ph2 5248</t>
+          <t>❌**打回@2026-08-30**：与已合 UPG-40 换肤**同文件双改**（WorkbenchPage/demo.js/MainAc</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>✅ **阶段 1 全量已合 main @2026-09-02**（0ce0fd0 链：1A f3c0fda+1B bcb18f5+1C 1a</t>
+          <t>✅**已合 main @2026-08-30**（设计师 merge 8f8debd，含 2ccce25；§六 抽查通过 13 项+候选C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>设计师/派单/UPG-50_阶段2_MCP组件注册制开放_派单_2026-09-02.md</t>
+          <t>设计师/派单/UPG-25_重修_派单_2026-08-30.md</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DEL-UPG50-20260901-001</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UPG-51</t>
+          <t>UPG-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>用户画像标签池（Memory OS 商用投影 + 合规）</t>
+          <t>侧边栏品牌区换 logo+黑字 + 抽屉展开占比 61.8%</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2260,22 +2260,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>✅ 方案 v1（设计详设已补，并入 **`Memory_OS_完整设计_v2`** 附录「Commercial Projection」；定位</t>
+          <t>裁决]；用户确认已实现 @2026-09-02）→</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>**✅ C 交付 @2026-08-31**（worktree=mov-upg51 branch=feat/upg51，commit 见报告</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验</t>
+          <t>✅ 验收通过（用户确认「已实现」）@2026-09-02（feat/sidebar-brand 7a6dff6+0fdfe87：品牌区 lo</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>✅**验收+审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验独</t>
+          <t>**分支未合 main（162 分叉）｜已合 main@2026-09-02（feat/sidebar-brand 7a6dff6/0fdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2292,42 +2292,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>UPG-52</t>
+          <t>UPG-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Memory OS 生命链（Semantic 池子 + 生命周期 + Timeline + Retrieval + blockedSourceHashes）</t>
+          <t>obsidian.file.write 审批闸修复（isHarmless file.write 特判误捕）</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（设计依据＝`Memory_OS_完整设计_v2`，唯一口径；含验收方案）</t>
+          <t>✅**方案 v1 已出 @2026-08-29**（`设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md`）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（认领 C worktree=mov-upg52 branch=feat/upg52，**52-1</t>
+          <t>✅**程序员 C 完成 @2026-08-30 01:05**（feat/upg28 **443b288** 已 push origin，基</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>✅**审验通过 @2026-08-31**（独立 L2 模拟器复验：memory-os 目录建立/logcat 逐字吻合/空库零影响/4 只</t>
+          <t>✅**验收员验收通过 @2026-08-30**（L1 377/0/0 亲跑+变异 M1/M2 双锚亲杀+L2 采纳模拟器证据[真机 ASK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=actor 模型[AI 只 PROPOSED]/blockedSourc</t>
+          <t>✅**已合 main @443b288**（ff-only 已推 origin，合后全量复跑 377/0/0 绿；worktree mov-</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/方案设计/UPG-28_obsidian写入审批闸修复_方案设计.md</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2339,12 +2339,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UPG-53</t>
+          <t>UPG-44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>安全体验优化改造（该守才守 · 守得舒服）</t>
+          <t>AcceptanceJudge B1 观察层（UPG-06 批2 剩项）</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>✅ 方案 v1（依据 安全体系_设计_v2.1 §5.3 + mov_安全体验_demo.html；体验优化设计+验收标准已写入文档）</t>
+          <t>裁决criteria+AI 回复→verdict/失败静默]；**投影剔键硬红**=Surface.deriveEventMessage 显</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg53 **a665349** 已提交 3 commit[d434ab1 8场景落</t>
+          <t>C 完成@2026-08-30 04:05**（feat/upg44 **122945b** 基底 main 3263f10 已 push；</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>✅**验收员通过+审验通过 @2026-08-31**（L1 66 套件 473/0/0 独立重跑+变异 3/3[V3/V4a/V7]+L2</t>
+          <t>审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8fc 已推</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=豁免链 gate 永不豁免写入侧已拦/vault.delete·cred</t>
+          <t>✅**验收+审验通过 → 已合 main @2026-08-30**（设计师 §六抽查 + rebase 后 ff-only **801b8</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-44_AcceptanceJudge_B1_派单_2026-08-30.md</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2386,42 +2386,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UPG-54</t>
+          <t>UPG-45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>安全中心（设置 -&gt; 安全 二级 · 等级仪表盘 + 分组策略 + 硬边界）</t>
+          <t>审批 · Approval Capability Registry（权限能力注册表）</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>✅ 方案 v2（依据 安全中心_设计_v2 + 安全体系_设计_v2.1；评审通过·有条件冻结｜等级=结果仪表盘/策略摘要/分组/审计系统级</t>
+          <t>🔨**已派单 @2026-08-30**（用户已转派；派单文本 `设计师/派单/UPG-45_审批_ApprovalRegistry_派单</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg54 **9911e67** 已 push origin 3 commit[47</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>✅**验收通过+审验通过 @2026-08-31**（8 项核物+482/0/0+变异 W1/W8/W5 三杀+模拟器仪表盘/实时刷新/足迹</t>
+          <t>✅**验收员通过 @2026-08-30**（ACCEPTANCE_LOG UPG-45，commit edf86d9）：核物[54行=as</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SecurityCenter 等级结果仪表盘无 setGrade API</t>
+          <t>**已合 main @2026-08-31 → 审验员**（approval 体系随 UPG-58/62/63 合入；ApprovalSer</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师\方案设计\审批弹窗_用户授权层_设计_v3_2026-08-30.md</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2433,42 +2433,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UPG-55</t>
+          <t>UPG-46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>我的资产（资产管理项注册体系 · 基于安全体系 v2.1）</t>
+          <t>工具联动 Runtime 契约（Tool Orchestration）</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>✅**三轮评审采纳升 v2.2 工程冻结版 @2026-09-01**（评分 架构 9.2/安全 8.8/迁移 8.2/UI 9.1/工程</t>
+          <t>🔄 **用户拍板转交 @2026-09-05 02:19**（原认领程序员 Claude/wmw0027 做不了，用户指令转交）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-09-01**（feat/upg55 **e1f241e** 已 push；[67-A 框架+迁移] ①Asse</t>
+          <t>✅**C 完成 @2026-09-05 03:02**（程序员 Kimi/kimi-cli，feat/upg46 **a8043aad**</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在</t>
+          <t>✅ **验收员复验通过 @2026-09-05**（§P57 落档：六件核物全在/M-cycle 锚链成立/837 差 1 双方 P3 注记</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>已合 main@2026-09-01（e1f241e）｜无遗留卡点 ｜</t>
+          <t>✅ **审验员确认+设计师合 main @7ccf0446**（2026-09-05：段①核心契约全链合入；段②=UPG-104） **卡点</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>设计师\方案设计\07_资产\我的资产_资产管理项_设计_v2_2026-08-31.md</t>
+          <t>设计师/派单/UPG-46_工具联动Runtime契约_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2480,37 +2480,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UPG-56</t>
+          <t>UPG-47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>评测集盘点与 fixture 版本机制（改造计划第一阶段①⑤）</t>
+          <t>主页胶囊系统（pin_type+stableId / 三区 / ＋管理弹层 / 点击分派 / 长按 / 第三态 / 气泡字数）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 `工单方案\工单方案\改造计划+验收标准_合并版_AHE×EvoC2F_2026-08-31.md` v1.4 上篇 §</t>
+          <t>🔨已派单</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg56 **cc86fac** 已 push origin[1ed70a2 主体+</t>
+          <t>✅C 交付 @2026-08-30（feat/capsule-system **767228c+32ba01c** push；报告 程序员/</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG c25aacf）：feat/upg56 cc86fac</t>
+          <t>✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P54：4e5a2f7c 隔离 worktree[申报</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>✅**审验通过+已合 main @2026-08-31**（审验 33→34：盘点报告 6 节 12 条修正口径[实测 12 条非 13]+</t>
+          <t>✅后续美化已合 main @2026-08-31（dock 对齐 **afc1ccd**：＋号圆形·随胶囊横滑·气泡左对齐胶囊；管理面板设置</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2527,37 +2527,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UPG-57</t>
+          <t>UPG-48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Evolution Ledger 骨架（改造计划第一阶段②）</t>
+          <t>Memory API 工程契约（记忆页:memory-core/memory-api 模块化）</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 §6.1/§6.5 + 下篇 X-1/M-6；**架构约束=复用 TimelineLedger 基础设施，禁</t>
+          <t>🔨已派单 @2026-08-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg57 **f4bae35** 已 push origin[Evolution L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>【✅ **修复复验通过 @2026-08-31**（R1｜ACCEPTANCE_LOG 04fb19f）：feat/upg57 **fbcd</t>
+          <t>❌**审验打回@2026-08-30（P1 边界违例）**｜MainActivity:582-598 直引 com.hermes.mov.m</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>✅**R1 复验通过+审验通过+已合 main @2026-08-31**（审验 33→34：NS_EVOLUTION 12 事件+ACTO</t>
+          <t>✅**已合 main @2026-08-30**（设计师 merge 92d4c22[含 0aa0c07]，审验五步复核通过：零直触core</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2574,37 +2574,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UPG-58</t>
+          <t>UPG-49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A-1 Manifest 五步链脚本（改造计划第一阶段③）</t>
+          <t>记忆页「我的记忆」UI 分层管理</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-1 + 下篇 A1-1~A1-5/M-4/M-5；**硬验=零人工步骤**，≤20 行降为推荐约束[大神</t>
+          <t>✅ 方案 v4 定稿（记忆页分层管理_设计_v4 大神 9.2 冻结）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg58 **ac8d27d** 已 push origin[a62f904 主体+</t>
+          <t>🔨 **程序员 R2 修复交付 @2026-09-01**（feat/upg49-r2 **5640bce** 已 push origin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>审验36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledger 写入 actor=system-deriver]/L1</t>
+          <t>✅ **审验通过 @2026-09-01**（integrity_review=confirmed：P2-1a 72px 像素实证+删📌</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>✅**审验通过+已合 main @2026-08-31**（审验 36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledg</t>
+          <t>✅ **设计师终审合流 @2026-09-02**（B9edcc4 落档+工单库补登；2 治理项裁决见下）</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2614,66 +2614,66 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG49-20260901-002</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UPG-59</t>
+          <t>UPG-50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B 线蒸馏 MVP（改造计划第一阶段④ · 里程碑一承载）</t>
+          <t>外观·组件级显示（Display Appearance 工程契约）</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇改造线 B + 下篇 B-1~B-9；教训六字段/三分类/配额/过期）</t>
+          <t>📌 **激活 @2026-09-02（用户拍板：出工单完善验收后派活）**</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg59 **8da2907** 已 push origin 2 commit[2d</t>
+          <t>**✅ C 交付 @2026-09-01**（branch=feat/upg50，commit ca984df+8e73e8d｜A UI 编</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>✅**验收通过+审验通过 @2026-08-31**（9 项核物+73 套件 519/0/0 独立重跑+变异 V4/V3b/配额三杀独立复跑</t>
+          <t>✅ **阶段2 复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P25：feat/upg50-ph2 5248</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=V-4 ACTIVE-only 注入过滤/配额 MAX_LESSONS=</t>
+          <t>✅ **阶段 1 全量已合 main @2026-09-02**（0ce0fd0 链：1A f3c0fda+1B bcb18f5+1C 1a</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-50_阶段2_MCP组件注册制开放_派单_2026-09-02.md</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG50-20260901-001</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UPG-60</t>
+          <t>UPG-51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A-2 三道门实现+元验证（改造计划第一阶段⑥）</t>
+          <t>用户画像标签池（Memory OS 商用投影 + 合规）</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2683,22 +2683,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-2 + 下篇 A2-1~A2-6/M-1~M-6；**前置 UPG-56/58/59**）</t>
+          <t>✅ 方案 v1（设计详设已补，并入 **`Memory_OS_完整设计_v2`** 附录「Commercial Projection」；定位</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg60 **a8d1363** 已 push origin[5a7a576 三道门</t>
+          <t>**✅ C 交付 @2026-08-31**（worktree=mov-upg51 branch=feat/upg51，commit 见报告</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>✅**验收通过+审验通过 @2026-08-31**（9f9466d 落档：9 项测试锚+77 套件 546/0/0+变异 M1/M3v2</t>
+          <t>审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SkillGate JS_ARTIFACT 直接拒收[A2-2 落地]/</t>
+          <t>✅**验收+审验通过 → 已合 main @2026-08-31**（设计师：ACCEPTANCE_LOG ff23a88 落档 + 查验独</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2715,37 +2715,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UPG-61</t>
+          <t>UPG-52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>vault.get 伪放行修（记住豁免与 fail-closed handler 不一致 · UI 禁用豁免勾选）</t>
+          <t>Memory OS 生命链（Semantic 池子 + 生命周期 + Timeline + Retrieval + blockedSourceHashes）</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>定稿（UPG-53</t>
+          <t>✅ 方案定稿（设计依据＝`Memory_OS_完整设计_v2`，唯一口径；含验收方案）</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg61 **b7c2e9d** 已 push origin；**修法②落地·四范围</t>
+          <t>✅**C 完成 @2026-08-31**（认领 C worktree=mov-upg52 branch=feat/upg52，**52-1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（UPG-53 审验员 L2 实测新发现 P1 + 设计师定夺修法；源码锚 @main 2780961：`MainActivit</t>
+          <t>✅**审验通过 @2026-08-31**（独立 L2 模拟器复验：memory-os 目录建立/logcat 逐字吻合/空库零影响/4 只</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>✅**审验通过+已合 main @2026-08-31**（审验 35→36：四范围核物+L1 74 套件 523/0/0 独立重跑+变异</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=actor 模型[AI 只 PROPOSED]/blockedSourc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2762,12 +2762,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UPG-62</t>
+          <t>UPG-53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>多轮对话输入框失焦修（markstream WebView 抢焦点 · 焦点归还兜底）</t>
+          <t>安全体验优化改造（该守才守 · 守得舒服）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（用户真机实测报障 + 设计师溯源 @main f975437）</t>
+          <t>✅ 方案 v1（依据 安全体系_设计_v2.1 §5.3 + mov_安全体验_demo.html；体验优化设计+验收标准已写入文档）</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg53 **a665349** 已提交 3 commit[d434ab1 8场景落</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**验收员通过+审验通过 @2026-08-31**（L1 66 套件 473/0/0 独立重跑+变异 3/3[V3/V4a/V7]+L2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（ff-only **82c778b** 已推 origin[feat/upg61-rb 链</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=豁免链 gate 永不豁免写入侧已拦/vault.delete·cred</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UPG-63</t>
+          <t>UPG-54</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>第二阶段收口：弹窗基线 Z-5 + MULTI_CALL 分布统计 + M-1 真实重放补跑</t>
+          <t>安全中心（设置 -&gt; 安全 二级 · 等级仪表盘 + 分组策略 + 硬边界）</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批</t>
+          <t>✅ 方案 v2（依据 安全中心_设计_v2 + 安全体系_设计_v2.1；评审通过·有条件冻结｜等级=结果仪表盘/策略摘要/分组/审计系统级</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg54 **9911e67** 已 push origin 3 commit[47</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b</t>
+          <t>✅**验收通过+审验通过 @2026-08-31**（8 项核物+482/0/0+变异 W1/W8/W5 三杀+模拟器仪表盘/实时刷新/足迹</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SecurityCenter 等级结果仪表盘无 setGrade API</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2856,12 +2856,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UPG-64</t>
+          <t>UPG-55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C 线效应注解首批（改造计划第二阶段·C 线）</t>
+          <t>我的资产（资产管理项注册体系 · 基于安全体系 v2.1）</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2871,27 +2871,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批</t>
+          <t>✅**三轮评审采纳升 v2.2 工程冻结版 @2026-09-01**（评分 架构 9.2/安全 8.8/迁移 8.2/UI 9.1/工程</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
+          <t>✅**C 完成 @2026-09-01**（feat/upg55 **e1f241e** 已 push；[67-A 框架+迁移] ①Asse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b</t>
+          <t>📌 **登记丢失补录 @2026-09-02（验收员盘点发现）**：git 实证 61b2b87/27a744d/c8033b6 均已在</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
+          <t>已合 main@2026-09-01（e1f241e）｜无遗留卡点 ｜</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师\方案设计\07_资产\我的资产_资产管理项_设计_v2_2026-08-31.md</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2903,12 +2903,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UPG-65</t>
+          <t>UPG-56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A-2 门 3 灰度自动化（改造计划第二阶段·接 B 生产信号）</t>
+          <t>评测集盘点与 fixture 版本机制（改造计划第一阶段①⑤）</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2918,22 +2918,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>✅ **设计 v2 定稿 @2026-09-02**（大神二轮 12/12 全采纳｜统计口径 v2 定稿：按 skill 去重/min20+</t>
+          <t>✅ 方案定稿（依据 `工单方案\工单方案\改造计划+验收标准_合并版_AHE×EvoC2F_2026-08-31.md` v1.4 上篇 §</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg65 **f709ed9** 已 push origin[e4aa2a6 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg56 **cc86fac** 已 push origin[1ed70a2 主体+</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>⚠️ **错挂注记 @2026-09-05（设计师）**：以下打回段主体=feat/upg63 0580fa8，属 **UPG-63** 卡</t>
+          <t>【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG c25aacf）：feat/upg56 cc86fac</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>✅ **已合 main @34c37f54（补登 @2026-09-05，设计师核物）**：=交付提交 e4aa2a6 的 patch-id</t>
+          <t>✅**审验通过+已合 main @2026-08-31**（审验 33→34：盘点报告 6 节 12 条修正口径[实测 12 条非 13]+</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2950,37 +2950,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UPG-66</t>
+          <t>UPG-57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A-3 Judge 扩面（改造计划第二阶段·判定三类+反哺管道）</t>
+          <t>Evolution Ledger 骨架（改造计划第一阶段②）</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇 A-3 + 下篇 A3-1~A3-4；独立可随时插队）</t>
+          <t>✅ 方案定稿（依据 合并版上篇 §6.1/§6.5 + 下篇 X-1/M-6；**架构约束=复用 TimelineLedger 基础设施，禁</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg66 **1e604c7** 已 push origin[0438049 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg57 **f4bae35** 已 push origin[Evolution L</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg66 1e604c7</t>
+          <t>【✅ **修复复验通过 @2026-08-31**（R1｜ACCEPTANCE_LOG 04fb19f）：feat/upg57 **fbcd</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>✅ **已合 main@2026-09-01**（A-3 Judge 扩面｜AcceptanceJudge/M-JudgeModes/Age</t>
+          <t>✅**R1 复验通过+审验通过+已合 main @2026-08-31**（审验 33→34：NS_EVOLUTION 12 事件+ACTO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2997,37 +2997,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UPG-67</t>
+          <t>UPG-58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>D 线 DAG 编排试点（改造计划第三阶段 · 预立待前置）</t>
+          <t>A-1 Manifest 五步链脚本（改造计划第一阶段③）</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>✅ 方案定稿（依据 合并版上篇改造线 D + 下篇 D-1~D-5 + §十三 执行细则）</t>
+          <t>✅ 方案定稿（依据 合并版上篇 A-1 + 下篇 A1-1~A1-5/M-4/M-5；**硬验=零人工步骤**，≤20 行降为推荐约束[大神</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>✅**C 完成 @2026-08-31**（feat/upg67 **040c9d9** 已 push origin[a88510a 主体+</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg58 **ac8d27d** 已 push origin[a62f904 主体+</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG 6f330b5）：feat/upg67 040c9d9；</t>
+          <t>审验36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledger 写入 actor=system-deriver]/L1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>✅**已合 main @2026-08-31**（§六抽查=DagPlanner cycle 拒绝[Kahn 失败→Reject 不 han</t>
+          <t>✅**审验通过+已合 main @2026-08-31**（审验 36→37：五步链+跨单消费全坐实[56 Guard 即插/57 Ledg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>UPG-68</t>
+          <t>UPG-59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>商业安全闸（原「商业防线批」——W2 白名单自动闸 + 商业面 fail-open 集中收口）</t>
+          <t>B 线蒸馏 MVP（改造计划第一阶段④ · 里程碑一承载）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3059,27 +3059,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>✅ **设计 v1 定稿 @2026-09-01**（`设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026</t>
+          <t>✅ 方案定稿（依据 合并版上篇改造线 B + 下篇 B-1~B-9；教训六字段/三分类/配额/过期）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>✅ **C 完成 @2026-09-02**（补充节 V68-8/V69-4 补验：feat/upg68 `8380108`；变异亲杀 4/</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg59 **8da2907** 已 push origin 2 commit[2d</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>✅ R1 复验带缺陷通过 @2026-09-01（feat/upg68 35b0008｜HIGH/M1/M2 三缺口 security_re</t>
+          <t>✅**验收通过+审验通过 @2026-08-31**（9 项核物+73 套件 519/0/0 独立重跑+变异 V4/V3b/配额三杀独立复跑</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>✅ **已合 main @c2defad @2026-09-02**（rebase origin/main 零冲突 + ff；V68-8/V</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=V-4 ACTIVE-only 注入过滤/配额 MAX_LESSONS=</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026-09-01.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3091,12 +3091,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UPG-69</t>
+          <t>UPG-60</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WebMCP 站点试点（mow.kim 工单站「站点=业务工具」第一站）</t>
+          <t>A-2 三道门实现+元验证（改造计划第一阶段⑥）</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3106,22 +3106,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>已派单（用户直接外派 @2026-09-05——撤销改向挂起，原 mow.kim 工单站口径继续）</t>
+          <t>✅ 方案定稿（依据 合并版上篇 A-2 + 下篇 A2-1~A2-6/M-1~M-6；**前置 UPG-56/58/59**）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**C 完成 @2026-08-31**（feat/upg60 **a8d1363** 已 push origin[5a7a576 三道门</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅**验收通过+审验通过 @2026-08-31**（9f9466d 落档：9 项测试锚+77 套件 546/0/0+变异 M1/M3v2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>改向挂起：试点职能由 UPG-105 批二承接，工单三工具留商家后台线</t>
+          <t>✅**已合 main @2026-08-31**（设计师：§六抽查=SkillGate JS_ARTIFACT 直接拒收[A2-2 落地]/</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3138,15 +3138,438 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>UPG-61</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>vault.get 伪放行修（记住豁免与 fail-closed handler 不一致 · UI 禁用豁免勾选）</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>定稿（UPG-53</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-08-31**（feat/upg61 **b7c2e9d** 已 push origin；**修法②落地·四范围</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>✅ 方案定稿（UPG-53 审验员 L2 实测新发现 P1 + 设计师定夺修法；源码锚 @main 2780961：`MainActivit</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>✅**审验通过+已合 main @2026-08-31**（审验 35→36：四范围核物+L1 74 套件 523/0/0 独立重跑+变异</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UPG-62</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>多轮对话输入框失焦修（markstream WebView 抢焦点 · 焦点归还兜底）</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>✅ 方案定稿（用户真机实测报障 + 设计师溯源 @main f975437）</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>✅**已合 main @2026-08-31**（ff-only **82c778b** 已推 origin[feat/upg61-rb 链</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>UPG-63</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>第二阶段收口：弹窗基线 Z-5 + MULTI_CALL 分布统计 + M-1 真实重放补跑</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>UPG-64</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>C 线效应注解首批（改造计划第二阶段·C 线）</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>🔓 **五轮评审采纳升 v2.4 工程契约冻结（2026-08-31，MCP 治理评 9/10）**：67-B 范围随三细节钉死｜①审批</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-08-31**（feat/upg64 **115762d** 已 push origin[2d2444d 主体+</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>✅**验收+审验通过 @2026-08-31**（78 套 540/0/0+EffectSpecsTest 10/0+变异 M-64a/b</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>✅**已合 main @2026-08-31**（§六抽查=Registry 20 条全在+credSet/credDelete 在场[误报</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UPG-65</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A-2 门 3 灰度自动化（改造计划第二阶段·接 B 生产信号）</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>✅ **设计 v2 定稿 @2026-09-02**（大神二轮 12/12 全采纳｜统计口径 v2 定稿：按 skill 去重/min20+</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-08-31**（feat/upg65 **f709ed9** 已 push origin[e4aa2a6 主体+</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>⚠️ **错挂注记 @2026-09-05（设计师）**：以下打回段主体=feat/upg63 0580fa8，属 **UPG-63** 卡</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @34c37f54（补登 @2026-09-05，设计师核物）**：=交付提交 e4aa2a6 的 patch-id</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UPG-66</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A-3 Judge 扩面（改造计划第二阶段·判定三类+反哺管道）</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>✅ 方案定稿（依据 合并版上篇 A-3 + 下篇 A3-1~A3-4；独立可随时插队）</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-08-31**（feat/upg66 **1e604c7** 已 push origin[0438049 主体+</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>【✅ **验收员验收通过 @2026-08-31**（ACCEPTANCE_LOG 9e764fb）：feat/upg66 1e604c7</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>✅ **已合 main@2026-09-01**（A-3 Judge 扩面｜AcceptanceJudge/M-JudgeModes/Age</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UPG-67</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D 线 DAG 编排试点（改造计划第三阶段 · 预立待前置）</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>✅ 方案定稿（依据 合并版上篇改造线 D + 下篇 D-1~D-5 + §十三 执行细则）</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>✅**C 完成 @2026-08-31**（feat/upg67 **040c9d9** 已 push origin[a88510a 主体+</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>【✅ **验收员验收通过 @2026-09-01**（ACCEPTANCE_LOG 6f330b5）：feat/upg67 040c9d9；</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>✅**已合 main @2026-08-31**（§六抽查=DagPlanner cycle 拒绝[Kahn 失败→Reject 不 han</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UPG-68</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>商业安全闸（原「商业防线批」——W2 白名单自动闸 + 商业面 fail-open 集中收口）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>✅ **设计 v1 定稿 @2026-09-01**（`设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>✅ **C 完成 @2026-09-02**（补充节 V68-8/V69-4 补验：feat/upg68 `8380108`；变异亲杀 4/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>✅ R1 复验带缺陷通过 @2026-09-01（feat/upg68 35b0008｜HIGH/M1/M2 三缺口 security_re</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>✅ **已合 main @c2defad @2026-09-02**（rebase origin/main 零冲突 + ff；V68-8/V</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>设计师\方案设计\05_审批\审批白名单机器可读化与注册即校验_设计_v1_2026-09-01.md</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UPG-69</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>WebMCP 站点试点（mow.kim 工单站「站点=业务工具」第一站）</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>📌 已派单（用户直接外派）</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>✅ C 完成 @2026-09-05（f5e7212a——站点三件+3 端点+契约锚；DEL 挂起已随 STD 补冻解锁；待验收）</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>改向挂起：试点职能由 UPG-105 批二承接，工单三工具留商家后台线</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>DEL-UPG69-20260905-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>UPG-70</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>UI 组件化改造 · 地基（单一数据源/形态类归层/规范对齐）</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>P2
 → **审验**：✅ 通过 @2026-09-02（integrity_review=confirmed，与 ACCEPTANCE_LOG §P26 一致——合入版 667cc80 与 b47ecb8 patch-id 等价逐字节一致；基线 2 失败亲跑对照坐实=收拢版带病预存、UPG-70 零新增失败；A1/A2 核物全坐实）；3 条 P3 不阻塞（①交付报告落点已移 程序员\交付报告\ ②manifest 缺口→挂账 ③autocrlf 误报→CI 权威）
@@ -3156,190 +3579,190 @@
 → **依据**：2026-09-02 调研 GitHub 成熟方案</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>**裁决**（用户拍板 2026-09-02）：基线 2 失败=**契约锚同步修**（AppearanceContractTest 适配收拢</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>**验收**：验收员复验 带缺陷通过 @2026-09-02（ACCEPTANCE_LOG §P26：b47ecb8 隔离 worktree</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>✅ 已合 main @667cc80（feat/upg70 b47ecb8 cherry-pick 667cc80）｜ DONE</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>UPG-71</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>元能力注册表 · 地基（MVP 资产 + Schema + 校验脚本）</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>✅ **审验 通过 @2026-09-02**（integrity_review 与 §P27 一致｜L1①/②/④/⑤ 亲跑全坐实；观察</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>✅ 已合 main @43fd00a（feat/upg71 快进合入+已 push）｜ DONE</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>UPG-72</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>执行引擎 · S2 JobSpec+SchemaGate+READ 直跑（契约 v0.4 首接线单）</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>✅ **审验 通过 @2026-09-02**（§P28 一致：红线边界 diff 17 文件全模块零触碰、mov-exec-engine:</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>✅ **设计师合 main**：bd958d2（父=main 43fd00a，快进） **前置**：✅ UPG-71 已合 main @43</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>UPG-73</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>执行引擎 · S3 审批双快照核心（ApprovalSnapshot+首决胜+STALE）+ WRITE/MONEY 接审批（契约 v0.4 第二条接线单）</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>✅ **R1 修复交付 @2026-09-02**（程序员 feat/upg73 **add9e8c**：HIGH ApprovalBook</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>✅ **审验 通过 @2026-09-02**（§P29-R1 consistent：R1 范围 5 文件+273/-31 限 approv</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>✅ **已合 main @add9e8c**（快进合入+已 push；元能力线合序 71→72→73 完成）｜ DONE **前置**：✅</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>UPG-75</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>审批交互收口（弹窗队列/待办列表/渠道统一）</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>P1
 → **验收链**：验收员复验 带缺陷通过（§P30：A1 首决胜真 CAS[ApprovalService:196-200 AtomicReference + compareAndSet 非 check-then-act——UPG-73 教训内化]+FIFO 队列+待办 chip/面板+单源收口；A3-1 渠道端到端 JVM 无法覆盖[远程面触发不达 UI——模拟器环境阻塞]）→ ✅ 审验通过（014c10f 4 文件+650/-109 纯交互层；A1-1 变异亲杀[keep-latest→A1-1 红→还原复绿]；红线边界[only-once/fail-closed 零改动]）
@@ -3347,191 +3770,191 @@
 → **依据**：审批安全语义</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-02**（程序员 feat/upg75 **014c10f**，worktree mov-upg75，基</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>✅ **验收员复验 带缺陷通过 @2026-09-02**（ACCEPTANCE_LOG §P30：014c10f 隔离 worktree｜</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>✅ 已合 main @014c10f（feat/upg75 ff 合入；本地合入完成｜push 待网络恢复）｜ DONE（待 push）</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>UPG-76</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>审批预审单模式（先扫一遍→审批单→同意就做）</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>📎 **方案 v2 增补 @2026-09-03**（设计师B「四钉子」，用户已认可：`设计师\方案设计\审批预审单_UPG-76_方案v</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-03**（程序员 feat/upg76 **ed5088c**，worktree mov-upg76，基</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P32：ed5088c 隔离 worktree｜</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>✅ **已合 main @6dd9161 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-76_审批预审单_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>DEL-UPG76-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>UPG-77</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>审批判定单源化 + MCP 面死信通道处置 + SDK 契约纠偏（P0 安全）</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>📌 已派单·待认领（派单 `设计师\派单\UPG-77_审批判定单源化_派单_2026-09-03.md`；验收标准已冻结 `STD-UP</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-03**（程序员 feat/upg77 **a7736b3**，worktree mov-upg77，基</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P31：a7736b3 隔离 worktree｜全量</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>✅ **已合 main @a7736b3 @2026-09-03**（设计师B：ff-only 合入 + **已 push origin/m</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-77_审批判定单源化_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>DEL-UPG77-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>UPG-78</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>生成器派生项入库保鲜 + CI diff=0 门禁（ApprovalRegistry 系）</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P33：f1e2067 隔离 worktree 三锚行为级复现——A1 删 inventory→dependsOn 自动重建+722/2/1[GeneratorTest 不再红=**§P25 P2-A2 闭环**]+A3 连跑两遍 md5 一致+内容零 drift[status M=CRLF 假差异]+A2 CI git diff --exit-code 门禁；manifest_sha 一致 ok:True；**§P25/§P27/§P30 三处生成器漂移遗留根治闭环**；**达待合→设计师**[CI 首跑回看=A2 终证]）
 → ✅ **已合 main @f1e2067 @2026-09-03**</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（用户拍板「一起干了」；派单 `设计师\派单\UPG-78_生成器门禁_派单_2026-</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P33：f1e2067 隔离 worktree 三锚行</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>✅ **已合 main @f1e2067 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-78_生成器门禁_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>UPG-79</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>审批呈现层组件化（ApprovalSurface + CardShell v1 视觉 + 渠道三修）</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P34：3925561 隔离 worktree——全量 734/2/1 亲跑一致+ApprovalLogic 9 用例+**变异④ 亲杀**[only-once 勾选禁则]+红线零改动；L2 CARD v2 采信程序员 4 图实证[同 AVD+呈现机制 UPG-77 已实证]+验收员抽验受阻如实记录；受限 3 项真机复验专项待环境恢复；**达待合→审验员→设计师**）
 → ✅ **已合 main @5cf546d @2026-09-03**（设计师B：rebase f1e2067 后 ff-only 合入+**已 push origin/main**——rebase 前后 patch-id 4d645861 逐字节等价实证[3925561≡5cf546d]，合后定向 ApprovalLogic/ComponentContract/ApprovalQueue BUILD SUCCESSFUL；合前抽查[红线 15/§六]——STD-UPG-79-v1 sha=97f756ff 对账一致、§P34 证据=代码核物+变异亲杀实物；**用户视觉反馈处置**：截图灰带（#ECECEC）经网格采样+colors.xml+最终代码三方核对=**3925561 已无此灰带**（卡体纯白、勾选行无背景，与用户要求一致，截图疑为 WIP 版）——若新包仍见灰带按 P3 新单追）
@@ -3539,49 +3962,49 @@
 → **依据**：总纲 v1「L2 呈现层=体系唯一黑洞」+ 评审增补——UPG-75 呈现为散装内联实现</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（总纲 R1=审批体系最后一块，用户拍板派出；派单 `设计师\派单\UPG-79_审批呈</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P34：3925561 隔离 worktree｜</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>✅ **已合 main @5cf546d @2026-09-03**（设计师B：rebase f1e2067 后 ff-only 合入+**</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-79_审批呈现层组件化_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>UPG-80</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>AI 对话链路诊断修复（模拟器 DeepSeek 链路）+ 联动补验</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>P1（验证环境根） → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P36：零代码诊断单复核通过——A1 诊断证据在档[AI 未回复挂账可销]；**A3 UPG-76 场景① 全链实证补入**[预审单四段全实证——§P32 场景① 阻塞解除]；场景③④✅+② ⛔ payment mock 待接；**removeAll 缺陷实锤转单**[批量写同工具名被砍单——MainActivity:5543]）
 → ✅ **已闭环 @2026-09-03**（零代码单无合 main 对象：验收员 §P36 + 审验 confirmed——A1 诊断 logcat 全链路健康在档[首查截断误判取全文核实]、联动 UPG-76 L3 ①③④ 全实证[预审单六锚/已批执行+未批阻断+计划外新窗/门槛单步弹窗]、脱敏闸 54 文件零非打码 key；挂账-模拟器AI未回复 已销、挂账-upg76-L3 ①③④ 已实证仅剩② MONEY 转 挂账-payment.pay handler缺失；审验发现① removeAll 缺陷已转 UPG-85 P1）
@@ -3590,191 +4013,191 @@
 → ✅ **C 交付 @2026-09-03**</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-80_AI对话链路修复_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-03**（程序员 Claude/wmw0027，**零代码改动**｜A2 判定纯环境/配置面，无代码缺陷</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P36：零代码诊断单复核通过｜A1 诊断证据在档[AI</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>✅ **已闭环 @2026-09-03**（零代码单无合 main 对象：验收员 §P36 + 审验 confirmed｜A1 诊断 log</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-80_AI对话链路修复_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>UPG-81</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>基线 2 失败契约锚同步修（AppearanceContractTest 适配收拢版现实）</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-81_基线契约锚同步修_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-03 09:19**（程序员 Claude/wmw0027，commit 3339c4b @feat/u</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P39：8609d69 隔离 worktree</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>✅ **已合 main（补登 @2026-09-05）**（审验员 09-05 核实：3339c4b patch-id≡**fab7d29*</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-81_基线契约锚同步修_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>DEL-UPG81-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>UPG-82</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>执行引擎 S4：ApprovalGroup 双状态机 + EXPIRED + EdgePolicy 失败传播（能力级）</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree——模块 88/0 亲跑[S2/S3 60 零回归+S4 28]+组簿 compute 单桶锁（§P29 教训前置）+**M3 亲杀**[组闸删除→2 红——S3 绕道封死]+M1/M2/M4 采信+S2/S3 零改动辨析+coverage FULL；**达待合→审验员→设计师[合序 71→72→73R1→82]**）
 → ✅ **已合 main @fe8cd45 @2026-09-03**</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-82_执行引擎S4_派单_2026-09-03.md`；</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-03 10:17**（feat/upg82 **6e9f90e** 已 push origin，基底 ma</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P38：6e9f90e 隔离 worktree｜模块</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>✅ **已合 main @fe8cd45 @2026-09-03**（设计师B：验收 §P38+审验 confirmed 达待合后｜reba</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-82_执行引擎S4_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>DEL-UPG82-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>UPG-83</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>CODE 模式 tool.call 受控通道（SDK 弃 curl 匝道）</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>拍板「只要两种模式：经典+极简，极简只是画面极简不阉割能力」｜5→2 模式收敛转 UPG-84：code 模式退役，本单修复对象消失，根因消</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>UPG-84</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>模式收敛 5→2（工具面去模式化 + SDK 匝道段删除）</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P35：e95472f 隔离 worktree——全量 724/2/1 亲跑一致[UPG-81 未开工口径成立]+Upg84ModeConverge 6 锚全绿+五模式零残留[ToolSdkGenerator 部分保留=tool.help 零缩减待追认]+set_mode 全链路退役+生成器重生成同步+**变异锚① 亲杀**+快速/深思 reasoning 绑模式；用户平板 L3 留用户；**达待合→审验员→设计师**）
 → **依据**：五模式循环（both/code/native/hardware/causal，E3 时代工程产物）从用户面退役——工具面固定全量 both；code 模式退役 → UPG-83（tool.call 补丁单）取消（根因消除优于补丁）；两态开关「经典⇄极简」归极简批阶段 1（送审稿入口决策点，不在本单）
@@ -3782,241 +4205,241 @@
 → ✅ **C 交付 @2026-09-03 08:33**</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（用户拍板「只要两种模式：经典+极简，极简只是画面极简不能阉割能力」；派单 `设计师\派</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-03 08:33**（程序员 Claude/wmw0027，commit e95472f @feat/u</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>✅ **验收员复验+审验 通过 @2026-09-03**（ACCEPTANCE_LOG §P35 + 审验 confirmed：e9547</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>✅ **已合 main @8647ee9 @2026-09-03**（设计师B：ff-only 合入+**已 push origin/mai</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-84_模式收敛_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>DEL-UPG84-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>UPG-85</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>预审单 removeAll 缺陷修复（同 tool 多步骤被误移除）</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-85_预审单removeAll缺陷修复_派单_2026-</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-03 17:05**（feat/upg85 **8609d69** 已 push origin，基底 ma</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>✅ **已闭环（补登 @2026-09-05）**（审验员 09-05 核实：本单实物=8609d69 预审单 removeAll 修复[r</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>✅ **已合 main @ad1e0a8 @2026-09-03**（设计师B：rebase fab7d29 零冲突+patch-id 37</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-85_预审单removeAll缺陷修复_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>DEL-UPG85-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>UPG-86</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>manifest 治理（存量补齐 + 审验.py 机器可验性强化）</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>P2
 → ✅ **已闭环 @2026-09-03**（验收+审验通过：--manifest-self-test PASS 4/4+存量治理亲验[82/85/87 重验 ok:True 三连+缺失显式 missing 不造假]+双挂账销项落表；工单系统侧无合 main 对象）
 → 🆕 **已认领 @2026-09-03 18:50**</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（派单 `设计师\派单\UPG-86_manifest治理_派单_2026-09-03.</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-03 19:0x**（治理 commit **13434e7**[工单系统仓库]；三件全交：①**审验.p</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>✅ **已闭环 @2026-09-03**（验收+审验通过：--manifest-self-test PASS 4/4+存量治理亲验[82/</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>合 main对象）</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-86_manifest治理_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>DEL-UPG86-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>UPG-87</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>内置包启停真实生效（宿主工具组纳入 builtin 包机制）</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree——全量 **741/0/1 亲跑[0 失败基线兑现首单]**+四件核物[三宿主组纳入/hostPackTools 单源/syncHostBuiltinTools 启停链/默认全量]+McpMarketTest 2→5 零回归[挂账-upg41v2 销项]+**变异复杀如实**[M3 机制采信/M1 未复现红采信 XML 口径]；真机启停 UI 走查=验收员持有待办；**达待合→审验员→设计师[verify-hash 终态]**）
 → ✅ **已合 main @fea2fae @2026-09-03**</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（设计师B 溯源实证后出卡；派单 `设计师\派单\UPG-87_内置包启停_派单_202</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-03 18:4x**（feat/upg87 **fea2fae** 已 push origin，基底 ma</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P41：fea2fae 隔离 worktree｜全量</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>✅ **已合 main @fea2fae @2026-09-03**（设计师B：验收 §P41+审验 confirmed[变异环 M1/M3</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-87_内置包启停_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>DEL-UPG87-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>UPG-88</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>极简批阶段 1（ASR + 极简主页生产化 + 两态开关点亮 + 快速提示词）</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P42：43e5756 三提交链隔离 worktree——全量 **748/0/1 亲跑一致**+Upg84ModeConverge 6 锚全绿[契约升级非消音复核]+R1 自纠实锤+**变异复验 5 轮未复现红如实标注**[采信程序员红案]+L2 四场景采信[未独立复跑如实标注]；coverage PARTIAL 裁决位维持[ASR 真人发声]；**达待合→审验员→设计师**）
 → ✅ **已合 main @43e5756 @2026-09-03**</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（产品主线；设计文=极简送审稿+用户拍板「两模式/不阉割能力」；派单 `设计师\派单\U</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-03 23:0x**（feat/upg88 **43e5756** 已 push origin[施工 90</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>**用户指示模拟器自测**（ASR 真实语音转写=物理受限转验收员持有｜coverage PARTIAL 设计师裁决位申报在报告 §七）；T</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>✅ **已合 main @43e5756 @2026-09-03**（设计师B：验收 §P42+审验 confirmed[契约升级非消音精读</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-88_极简批阶段1_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>DEL-UPG88-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>UPG-89</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>极简呈现引擎（PresentationRegistry + core.js 呈现栈 + Intent Router + Response Splitter + 三骨架）</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P46：f616b38f 分支头隔离 worktree——bun 12/12 亲跑+JVM 759/0/1 亲跑[AssetsHomeEngineContract 4 锚]+**PV-01 变异亲杀**[2 fail→还原]；锚⑥死变异裁决转设计师[测试有效性非产品缺陷]；homeWeb 接线下批申报一致；L2 七场景持有；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 带缺陷通过 @2026-09-04**（PV-01 亲杀独立复验双红+锚⑥更精确定性=layer 死状态只写不读+四项发现登记）→ ✅ **已合 main @fe258949 @2026-09-04**（设计师B：rebase 254d6caf 零冲突[原链 a51238dd→615f3590→f616b38f 重写成 84d11731→1e90bf44→fe258949——DEL 绑 615f359 漂移随 UPG-92 硬规则处置]+ff-only+push origin/main+verify-hash HASH_OK 闭环；MainActivity 零触碰=UPG-93 防撞兑现；L2 真机七场景[含 ASR⑦]验收员持有维持；锚⑥ layer 死字段删除随批 P3）→ ✅ **P3 尾巴合入 @0aad7980 @2026-09-04**（程序员锚⑥处置收尾：①核实「断言无需重设计——z 数值断言直调 zSnapshot=方案 a 本在链」②删 surface.layer 死字段[core.js 2 行纯删除，diff 核实一致]+DEL 按新硬规则重绑分支头 4fd540a6；设计师轻量通道：diff 精读[仅 2 删行]+rebase main 单提交回放[旧三链 patch-id 自动跳过]+ff-only+push+verify-hash HASH_OK；锚⑥本活实证[决策丢失变异→zSnapshot topKind=content→RED]在案——「审批永远压内容」安全不变量有杀）
 → 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg89，branch feat/upg89，基 main 39b17c4[UPG-90 已合]；按 STD-UPG-89-v2 施工：PresentationRegistry 九字段+style_tokens 白名单+core.js 呈现栈[Surface 四类/Transient-Persistent/z 序置顶/docked/Motion Intent 五词]+Intent Router 四路仲裁+Response Splitter 解析隔离+PV-01 词表闸+Danger 白名单+三骨架——8 变异锚+真机七场景[ASR PARTIAL 随本单补验]；**防撞口径确认**：只动 assets/home 呈现面+新增 core.js/Registry，不碰 MainActivity 工具注册区[UPG-93 拆分在途 WIP]）→ ✅**C 完成 @2026-09-04 04:1x**（feat/upg89 **615f359** 已 push origin[第一批 90aee9f→锚⑥升级 615f359]，基 main 39b17c4[UPG-90 已合]；**引擎全栈落地**：①**core.js 呈现引擎核心**[受信样式词汇表七命名空间 21 词 version 1.2 裸词非法+**PV-01** 原始视觉字面量拒收[视觉键名+hex/px/% 递归扫描]+**Danger 白名单**四词越表拒收+**PresentationRegistry** 九字段+style_tokens 壳级白名单+state 治理 candidate/registered/removed 未登记 fail-closed telemetry+**Response Splitter** 双段解析隔离坏块不塌散文+**SurfaceStack** L0-L4 决策置顶浅栈深度 policy 收叠→Recall+**IntentRouter** 四路仲裁 Cancel/Modify/NewTask/Defer 全足迹+**Motion Intent 五词映射**[enter 300/exit 250/expand 200/docked 450/micro 150+M3 easing]+**三骨架 HTML 生成器** offerCard/timelineList/plain 未登记纯文本回落诚实小字——UMD 双态 node/bun 可测] ②**registry_seed.js** 三骨架登记[offerCard.v1/timelineList.v1/plain.v1 registered+壳白名单] ③**home.html 引擎接入**[core.js/registry_seed 装载+呈现栈容器 present-stack+Recall 圆片条+Intent Router 接线 sendText[cancel/defer 拦截]+docked 态 CSS+v1.2 卡面 token 圆角 22/无描边/--card-shadow-lg/caps 10.5·700·.12em/pill 主钮纯黑+prefers-reduced-motion 退化] ④**测试双层**[bun tests/upg89_core.test.mjs **12/12**[逻辑级 8 锚全对应]+JVM 源码锚 AssetsHomeEngineContractTest **4**[Registry 九字段/三道闸/Motion 五词/Splitter 形态]]；**变异 8 锚：7 实杀 RED**[M1 renderRaw 不抛/M2 扫描恒空/M3 词表恒 ok/M4 Danger 恒放行/M5 未登记不回落/M7 仲裁恒 normal/M8 栈深不收叠——全部 bun RED]+**锚⑥死变异暴露→测试有效性升级**[zSnapshot layer-aware 排序+z 数值断言（决策 L3≥30/内容&lt;30）——加强变异仍 NOT-RED 复跑转复验在案 commit 615f359]；全量 **105 套件 759/0/1 全绿**[755[U90]+4 JVM 锚=759]；**逻辑面四场景机制实证**[①底座输入常驻继承 U88/③审批置顶+Danger 红 bun/④仲裁足迹 bun/⑤未登记回落 bun——真机七场景**转验收员持有**[②agent 流接线+⑦ASR 真人发声——如实申报]；**防撞兑现**[MainActivity 零触碰纯 CRLF+UPG-93 工具注册区零交集]；Token 双段零额外轮次+voice_hint 确定性槽/KV 0；coverage_status=**PARTIAL**[JS 引擎逻辑面 FULL[bun 12/12+7 锚实杀]/原生 agent chunk→homeWeb 接线未做=真机批/下批——设计师裁决位申报]；DEL-UPG89-20260904-001[code=**4fd540a6** 锚⑥处置收尾重绑/artifact=ba3d877dad14c566（APK 前 16）/manifest_sha 见案——**按新硬规则分支头重绑 @2026-09-04**（前头 615f359=f616b38f 链已废，本头含 surface.layer 死字段删除+锚⑥ z 数值断言收口）]；报告 DELIVERY_UPG89_2026-09-04.md；**已登记两个表**）——待验收员验收（L1 复核+变异复杀[bun]+真机七场景[含 agent 接线下批]+合后 verify-hash 终态复核）
@@ -4024,193 +4447,193 @@
 → **防撞**：UPG-88 已合 main</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**（**v2 正式派发**：启动条件齐=尾巴批清完+UPG-88 已合 main 43e5</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04 04:1x**（feat/upg89 **615f359** 已 push origin[第一批 9</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>✅ **审验 confirmed 带缺陷通过 @2026-09-04**（PV-01 亲杀独立复验双红+锚⑥更精确定性=layer 死状态只</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>✅ **已合 main @fe258949 @2026-09-04**（设计师B：rebase 254d6caf 零冲突[原链 a51238</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-89_极简呈现引擎_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>DEL-UPG89-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>UPG-90</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>尾巴批修（S-06 打回项 ②⑧ + C7 基线测试非确定性）</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>P2 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P47：c969b05a 隔离 worktree——全量 **762/0/0 亲跑**[0 失败基线]+ToolsSplitContract 7 锚+9 域拆分+MainActivity 1752 行删减+零行为变化[sha256 双锁]+**M-vault 变异亲杀**[键名变异→3 锚齐红与申报一致→还原；注释式破多行 lambda 编译失败教训三现——拆分类变异用键名/删除式]；冷启动 +5.1%&lt;10%；真机三场景采信；**达待合→审验员→设计师**[阶段 2 后续]）
 → ✅ **已合 main @39b17c4 @2026-09-03**</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（尾巴清零批；派单 `设计师\派单\UPG-90_尾巴批修_派单_2026-09-03.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04 00:1x**（feat/upg90 **1845cb7** 已 push origin，基 mai</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P47：c969b05a 隔离 worktree｜全量</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>✅ **已合 main @39b17c4 @2026-09-03**（设计师B：验收 §P43+审验 confirmed 达待合后｜reba</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-90_尾巴批修_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>DEL-UPG90-20260903-001</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>UPG-91</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>我的资产页注册制重排（tab 导航+二级收缩裸列表+点值脱敏+诚实空态+假数据回落删除+令牌迁移）</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>P2 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P44：4dc19e7 三提交链隔离 worktree——全量 **752/0/1 亲跑一致**+demoBridge 假数据零残留 grep[红线 18 同族根除]+锚④强化实录复核+R1 自纠[1C 形态消费恢复]；变异 M4 未复现如实[采信程序员 4/4 XML]；真机五场景持有维持；**达待合→审验员→设计师**）
 → ✅ **已合 main @4dc19e7 @2026-09-03**</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（用户实测「体验感很差」→ 四病灶诊断 → 六轮迭代 demo v6 拍板；派单 `设计</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04 01:4x**（feat/upg91 **34a2dda** 已 push origin[远端顶=4</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P44：4dc19e7 三提交链隔离 workt</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>✅ **已合 main @4dc19e7 @2026-09-03**（设计师B：验收 §P44+审验 confirmed[M4 复杀补强｜验</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-91_我的资产页重排_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>DEL-UPG91-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>UPG-92</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>manifest 硬闸化（deliver-gen 源头合规 + 自检内置）</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P45：39039ef 工单系统仓隔离 worktree——**deliver-gen --self-test 4/4 亲跑 PASS**[源头合规/硬闸注入红×2 exit=1 残件清除/骨架回归]+硬闸「拒绝产出非警告」机制化——**第六现根因闭环**；DEL-UPG92 狗粮自证；观察转办：sync 锚词表「✅K 完成」代号→设计师；**达待合→设计师**）
 → ✅ **已合 main</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（manifest 同族第六现｜红线 23 自检步声称未执行，改机制硬闸；派单 `设计师</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04 00:0x**（程序员 Kimi/kimi-cli，feat/upg92 **39039ef** 已</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-03**（ACCEPTANCE_LOG §P45：39039ef 工单系统仓隔离 worktre</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>✅ **已合 main（工单系统仓）@beb2777 @2026-09-03**（设计师B：验收 §P45+审验 confirmed 后｜f</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-92_manifest硬闸化_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>DEL-UPG92-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>UPG-93</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>MainActivity 拆分·阶段 1（工具注册面搬移 + 拆分蓝图落档）</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>P1
 → 🆕 **已认领 @2026-09-04 01:5x**（程序员 Claude/wmw0027，worktree mov-upg93，branch feat/upg93，基 main 254d6ca[军规 commit 顶]；按派单施工：185 handler 盘点落蓝图+ToolsRegistry 聚合+分域 Registrar 搬移+3 变异锚+测试金字塔——纯搬移零逻辑改动）→ ⚠️**WIP 回滚 @2026-09-04 02:3x**（程序员 C：盘点/口径闭合/提取器基建完成入库[commit 76c91cb：169 注册点三态扫描盘点+9 域归类+185 口径闭合核对]；**搬移实施中途回滚**——三态提取器跑出的 9 域文件存在块边界错位残片[ModelRegistry 循环/obsidian 段等 5-8 处——三方对账未完成]，**不带入半成品**，工作区已还原 7666 行原始态；工程形态已定案=Kotlin 扩展函数分域文件[receiver=this 零改动零持有]，WIP 资产与修复路径在案[upg93-拆分wip 记忆+upg93_inventory.json]）——**重新认领需独立完整会话**（剩余：错位残片三方对账→测试金字塔→3 变异锚→冷启动锚）
@@ -4221,49 +4644,49 @@
 → 🆕 **已认领 @2026-09-04 01:58·重新接管**</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-03**（架构图实证「图上分层、代码一锅」｜用户拍板「先解决这个」；派单 `设计师\派单\UPG</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04 03:3x**（程序员 Kimi/kimi-cli，feat/upg93 **c969b05a**</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>✅ **验收员复验通过（§P47）→ 审验 confirmed 通过 @2026-09-04**（M-vault 键名变异亲杀 3 锚齐红独</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>✅ **已合 main @3315bff0 @2026-09-04**（设计师B：rebase 0aad7980 零冲突[c969b05a→</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-93_MainActivity拆分阶段1_派单_2026-09-03.md</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>DEL-UPG93-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>UPG-94</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>极简主页真机观感修复（dock 隐藏 + logo 去框去影 + hint 删除 + 发送钮归 token）</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P48：分支头 25f73fe0[申报 746b20ec≠分支头二现]隔离 worktree——全量 763/0/1 亲跑一致+契约锚 4/4+**M1 删除式亲杀**[failures=1→还原；注释式免疫四现终纳]+四件观感修复核物；**P3×2：U89 引擎恢复自纠未申报**[透明度义务]+logo 168px 追加后截图未更新；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 带缺陷通过 @2026-09-04**（四件坐实+U89 恢复自纠亲核正确完整+四项发现登记）
 → ⚠️ **WIP 回滚 @2026-09-04**（UPG-98 拆分批②市场面——程序员 C：7 块搬移+13 提升+MarketTools 恢复完成[compileDebugKotlin EXIT=0]；**但 5 个测试失败**[锚定面迁移问题——HostBuiltin 2+ToolMeta 2+SceneWiring 1——非产品缺陷]；**toolFaceSrc 加 market/ 联合读源+MarketTools.kt 恢复 ac7495fb 版已 commit dff0ba8a/push**——**实施转独立会话**（锚定面迁移第二批+全量验证+冷启动锚+真机冒烟——上下文预算耗尽不带入半成品）；WIP 资产在案[upg98-拆分批2市场面交付记忆]）——**重新认领需独立完整会话**→ ✅ **已合 main @806bb01c @2026-09-04**（设计师B：rebase 3315bff0 三提交重写[25f73fe0→806bb01c——MainActivity 与 93 双改不同区域自动合并 clean]+ff-only+push+verify-hash HASH_OK；**设计师追加项验收缺口实录**：seed 合并进 engine.registry+timelineList 骨架 CSS 两项[2026-09-04 设计师裁决并 94 随批]未随本单落地——转出至 UPG-96 范围[接线单前置一件]，STD-96 追加说明区已注记；4 项发现裁决见问题区）
@@ -4272,49 +4695,49 @@
 → **防撞**：MainActivity 只动 applyPresentationMode/dock 字段化</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**（用户真机实测踩中[2026-09-04 03:27 包]：极简态经典 dock 飘顶[</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg94，branch fe</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>✅ **审验 confirmed 带缺陷通过 @2026-09-04**（四件坐实+U89 恢复自纠亲核正确完整+四项发现登记）</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>✅ **已合 main @806bb01c @2026-09-04**（设计师B：rebase 3315bff0 三提交重写[25f73fe</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-94_极简主页真机观感修复_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>UPG-95</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>个性化槽位选择（care profile 提炼 + 可选槽池 + LLM 编辑层 + ticketCard/rideCard 骨架落地）</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P49：979bf6bf 三批隔离 worktree——**bun 18/18 亲跑**+全量 **786/0/1 亲跑**[Care 双类 20 用例]+**M-11 变异亲杀**[敏感闸放行→红→还原]+编辑层接线[设计师裁决已接]；其余 3 锚采信；L2 出卡走查持有；**达待合→审验员→设计师**）→ ✅ **审验 confirmed 通过 @2026-09-04**（bun 18/18+全量 786/0/1 双亲跑+M-11 敏感闸亲杀独立复验+DEL 绑定无漂移正面记录[三连回潮后首单做对]）→ ✅ **已合 main @ac7495fb @2026-09-04**（设计师B：rebase 806bb01c 人工解真冲突 2 处[index.html CSS 段取 main 位置+并入 95 amenities/route/driver/pref-chip 装载块+顺带补回 94 恢复时漏网的 docked 态两条 CSS]+解后复跑闸：bun 12+6 全绿+全量 **790/0/1** 绿→ff-only+push+verify-hash HASH_OK；3 项发现裁决见问题区；持有项=L2 出卡 CDP 走查[随 96]+ASR PARTIAL[96 场景⑦]） → ✅ **验收员复验 带缺陷通过 @2026-09-03**（ACCEPTANCE_LOG §P50：cdf769a9 隔离 worktree——全量 **775/0/1 亲跑一致**+**HomeDeliveryContractTest 5/5 亲跑确认**[homeWeb 接线契约落位——UPI-89/95 遗留闭环]+红线/诚实申报复核；**M2 复杀 3 式未复现如实标注**[多行 evaluateJavascript 适配成本超阈值——采信程序员 XML]+L2 模拟器环境阻塞登记；**达待合→审验员→设计师**）
 → 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg95，branch feat/upg95，基 main 3315bff0[含 UPG-93 拆分]；施工：提炼层六域规则扩展（hotel/food/rail/ride/travel/shopping 纯函数）+offerCard amenities 槽（≤3）+ticketCard/rideCard candidate 登记+编辑层提示词节[全量事实×画像→槽池内选择；标签注入原文不进]——种子集 11 断言+4 变异锚；与 UPG-94 同 index.html 面按裁决串行）
@@ -4322,96 +4745,96 @@
 → **复用**：UPG-51 提炼器扩展点 + UPG-89 引擎/Registry + UPG-05 基因红线</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**（用户拍板方向「商户信息尽量全+用户侧个性化显示」；设计口径=v1.2 增补附录 B[三</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg95，branch fe</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>✅ **审验 confirmed 通过 @2026-09-04**（bun 18/18+全量 786/0/1 双亲跑+M-11 敏感闸亲杀独</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>✅ **已合 main @ac7495fb @2026-09-04**（设计师B：rebase 806bb01c 人工解真冲突 2 处[in</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-95_个性化槽位选择_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>UPG-96</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>homeWeb 呈现回路接线（极简发送不回落 + LLM 回复回流出卡 + 真机批收口）</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-04**</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>裁决位]；DEL-UPG96-20260904-001[code=cdf769a9/artifact=04f48903/manifest_s</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04**（feat/upg96 **cdf769a9** 已 push origin[远端顶；基 main</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>✅ **审验 通过 @2026-09-04**（integrity_review=confirmed：与 §P50 一致，变异环比验收员更深</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>✅ 已合 main @6dcfbac9（feat/upg96 cdf769a9 合入+已 push；rebase ac7495fb 零冲突实</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-96_homeWeb呈现回路接线_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>DEL-UPG96-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>UPG-97</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>侧边栏工作台三入口接线（我的记忆/我的资产/我的能力）+ comingSoon 兜底可见性</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 带缺陷通过 @2026-09-04**（ACCEPTANCE_LOG §P51：9010075d 工单系统仓隔离 worktree——全量 794/0/0 亲跑一致+**变异双锚亲杀**[分派锚 failures=2/兜底锚 failures=1→还原]+openBuiltin 三 case+comingSoon showDialog+i18n 双字典；**L2 真机四点验实证**[市场/资产/能力/订单]+**我的记忆行 5556 未呈现疑点转办**[平板五点验过——澄清后终判]；**达待合→审验员→设计师**）
 → **防撞**：纯前端单（mov-vue 源+产物同步）；MainActivity/tools 零行；与 95/96 零交集
@@ -4420,49 +4843,49 @@
 → ✅ **已合 main @04ca51ab</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**（用户真机报障「侧边栏有的按钮失灵」→ 设计师 adb 实测复现+根因定位：Sideba</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04 06:5x**（程序员 Kimi/kimi-cli，feat/upg97 **9010075d**</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>✅ **验收员复验 带缺陷通过 @2026-09-04**（ACCEPTANCE_LOG §P51：9010075d 工单系统仓隔离 wor</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>✅ **已合 main @04ca51ab（2026-09-04 设计师合入）**：rebase origin/main 6dcfbac9</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-97_侧边栏三入口接线_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>DEL-UPG97-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>UPG-98</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>MainActivity 拆分·批② 市场面搬移（→ market/ 模块）</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>P1 → ❌ **验收员打回 @2026-09-03**（ACCEPTANCE_LOG §P51b：**P1 提交版测试文件编译不过**——d96ade5d HostBuiltinPackContractTest mainSrc() 裸换行截断字符串→compileDebugUnitTestKotlin FAILED→全量在提交版无法执行；对照实锤：程序员 worktree 同路径=正确版未提交——**提交版≠验证版实锤**；七块搬移结构核过[工作区读源+MarketTools.kt 恢复 U93 遗漏自查]；修=工作区正确版 commit+新 commit 交付+DEL 重绑+R1 全新检出复验；**打回→程序员**） → ⚠️ **§P51c 中间态核验 @2026-09-03**（ACCEPTANCE_LOG 补记：dff0ba8a mainSrc 修复实锤[:27 单行]采纳 §P51b；全量 795/6/1——4 类失败定性=**锚定面迁移未完成**[HostBuiltin seg 锚失效/MarketSplit 集合缺元素/ToolMeta internal 锚未更新/ToolsSplit 1 红——非产品缺陷]；**维持打回（WIP）**——锚定面迁移完成（0 失败）再交 R1 复验） → 📌 **二次 WIP 如实申报处置 @2026-09-03**（脚本自动化搬移失败如实[fun 声明复杂度四条根因入册]——工作区还原 04ca51ab；**验收员核出申报不实一项**：6 文件 D 残留[gen93/scan93b/mut93 等 UPG-93 方法论资产被工作区删除未提交]——已代为恢复[git checkout，资产保全]；UPG-98 状态=**待重新认领·人工逐块搬移路径**[程序员建议：IDE 重构或手工 copy-paste 每块编译一次，30 分钟级]；工作树现状=feat/upg98@04ca51ab 干净） → ✅ **交付·待验收 @2026-09-04**（程序员重做完成[用户直派]：cherry-pick 上轮人工搬移 2787b73a[编译实证过的人工件非脚本]+锚定面迁移全收口=4b279e0a+d11509cc——全量 804/0/1（112 套件 --rerun-tasks）+3 变异锚亲杀红绿闭环[保真点名 buildLocalOverview/名单多挂点名 zzMutant/唯一写点点名 syncBuiltinPackTools]+冷启动双侧 5 次中位 940→932ms（Δ-0.9% 在带内）+真机三场景全过[市场页渲染/启停 185↔172 精确-13/logcat 双行/market.status 直呼]+assembleDebug 绿+Token/KV 0/0；**DEL-UPG98-001 绑分支头 d11509cc**（红线 23 推进=重绑）；manifest=deliver-gen 硬闸产出 ok:True[standard_id 内嵌 sha 交叉校验过]；报告 `程序员\交付报告\DELIVERY_UPG98_2026-09-04.md`；R1 复验→审验员→设计师） → ✅ **R1 复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P52：d11509cc 全新检出 **804/0/1 亲跑终验**[P1 提交版编译不过修复闭环]+MarketSplitContract 5 锚全绿[搬移保真契约锁]+变异 3 锚采信如实[验收员注入 3 轮未达真红——XML+契约双证采信]+L2 真机三场景采信[模拟器四度下线环境阻塞登记]；两观察转办[isAppVisible 不稳定/registry 依赖]；**达待合→审验员→设计师**） → ✅ **审验 confirmed 通过 @2026-09-04**（审验员：从零编译 804/0/0+1 跳过亲跑+变异采信升级亲杀[KDoc 改字→保真锚真红]+拆前 sha 独立抽查=冻结值+问题区 3 项） → ✅ **已合 main @d11509cc @2026-09-04**（04ca51ab→d11509cc 直接快进零冲突，verify-hash 通过；问题区 3 项裁决落档[isAppVisible 呈现通道缺口升级 P2 入审批收口议题/registry 依赖挂账残留面登记/3 函数 public 豁免注记入债务清单]；里程碑：上帝文件 7666→6016→5929 行；批③页面桥待派）
 → **范围**：市场总览区（buildLocalOverview/启停/安装投影）→ market/ 模块；纯搬移零逻辑改动；保真锚=块归一化 sha256 前后全等
@@ -4470,192 +4893,192 @@
 → 🆕 **已认领 @2026-09-04 07:18**</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**（拆分主线批②/共 8 批｜串行纪律：一批一派合后再基[UPG-95 真冲突实证后立]；</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>🆕 **已认领 @2026-09-04 07:18**（程序员 C/Claude-wmw0027，worktree mov-upg98，b</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>✅ **审验 confirmed 通过 @2026-09-04**（审验员：从零编译 804/0/0+1 跳过亲跑+变异采信升级亲杀[KDo</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>✅ **已合 main @d11509cc @2026-09-04**（04ca51ab→d11509cc 直接快进零冲突，verify-h</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-98_MainActivity拆分批2市场面_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>UPG-99</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>工单系统工具链硬闸批（DEL 分支头校验 + standard_id 交叉校验 + 报告模板强制段 + 红线 23 落规）</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>P2
 → **范围**：sync-orders DEL==分支头校验 / 审验.py standard_id 交叉校验 / deliver-gen 模板强制段 / 红线 23 两条明文
 → **纪律**：既有闸零回归；报错人话化；改库卡先备份；sync 后 --check diff=0</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>✅ **设计师直修完成 @2026-09-04**（用户拍板「你自己修吧，不搞工单」｜不走流转流程，设计师直接落地四件：①deliver-g</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>**范围**：sync-orders DEL==分支头校验 / 审验.py standard_id 交叉校验 / deliver-gen 模</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>已合 main@hash」在祖先链/存量 cherry-pick 卡豁免/显式豁免跳过]｜首跑即抓 7 条存量异常全归因[5 存量豁免+1</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>UPG-100</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>锚②半弱锚升级（count/match 组合断言）</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>📌 已派单（用户直接外派）</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>✅ C 完成 @2026-09-05（kimi-cli，a63b7088——锚②升级 count/match；待验收）</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>📌 已立卡·待派 ⏳ @2026-09-04（UPG-96 审验发现项①转正：contains 组合锚对单点破坏免疫）｜ 待派单</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>DEL-UPG100-20260905-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>UPG-101</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>侧边栏默认插件种子清单（「我的记忆」入口是否纳入 defaults）</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>拍板@2026-09-04（UPG-97 合 main 随批</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>📌 挂单·待用户拍板 @2026-09-04（UPG-97 合 main 随批裁决转立；产品决策项非缺陷）</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>UPG-102</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>MainActivity 拆分·批③ 页面桥面搬移（→ pages/ 模块）</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>P1 → ✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P53：**真交付=d77dae2a**[申报 cfa7d607 错误——申报 sha 错误 P3]隔离 worktree——全量 **809/0/1 亲跑一致**+PagesSplitContractTest 5 用例[申报 6 差 1 注记]+**M2 亲杀**[browser.forward 行置空→「漏搬 browser handler」红→还原]+approvalService internal 复核；两块搬移纯搬移核物；**达待合→审验员→设计师**）
 → 🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg102，branch feat/upg102，基 main d11509cc；施工：browserHandlers 注册块[14 个 browser.*]+WebMcpHub.mountCallback 块→pages/ 模块顶层扩展——纯搬移零逻辑改动+3 变异锚+锚定面迁移收口[全量 0 失败硬门槛]+搬出函数显式 internal）
@@ -4665,361 +5088,361 @@
 → **防撞**：本批独占 MainActivity 页面桥区；与在飞单零交集；批④</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**（拆分主线批③/共 8 批｜串行纪律：批② d11509cc 已合，本批基=main 顶</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>🆕 **已认领 @2026-09-04**（程序员 Claude/wmw0027，worktree mov-upg102，branch f</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>✅ **审验员独立复核 通过 @2026-09-04**（§P53 审验终态：从零编译 809/0/0+1 跳过 + 契约锚 5/5 + M</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>✅ **已合 main @cfa7d607（2026-09-04 设计师合入：fast-forward d11509cc→cfa7d607</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-102_MainActivity拆分批3页面桥_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>UPG-103</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>MainActivity 拆分·批④ chips/胶囊面搬移（→ ui/chips/ + ui/capsule/）</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>P1 → 🆕 **已认领 @2026-09-04 20:50**</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>📌 **已派单·待认领 @2026-09-04**</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>✅ **C 交付 @2026-09-04 23:05**（feat/upg103 **4e5a2f7c** 已 push origin；设计</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>✅ **审验员转通过 @2026-09-05**（四断收口逐项复核全绿：STD v2 重冻=51584a7d 一致/DEL 绑定 manif</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>✅ **设计师合 main @97d7ca31**（2026-09-05：批④ chips/胶囊面搬移全链合入；合后 verify-hash</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>设计师\派单\UPG-103_MainActivity拆分批4芯片胶囊_派单_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>DEL-UPG103-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>UPG-104</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>工具联动 Runtime 契约·段②（评测集+安全门+编排+记忆回流）</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>设计 v3/v3.1 全量保留归本单；待 UPG-46 段①</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>合 main后拆派单）</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>UPG-105</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>MOV 官网·容器面（给 AI 读）建设</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>📌 **已立卡·待派 @2026-09-04**（设计 v3 定稿：`设计师/方案设计/工单方案/官网容器面_给AI看内容_设计_v3_2</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-04**（feat/upg105 **841f591d** 已 push origin，基 main c5</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>✅ **验收员复验 通过 @2026-09-04**（ACCEPTANCE_LOG §P55：841f591d 隔离 worktree｜全量</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>✅ **已合 main @2026-09-04**（设计师 ff `c5bb94af..841f591d` 已推 origin；批二即 UP</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>设计师/方案设计/工单方案/官网容器面_给AI看内容_设计_v3_2026-09-04.md</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>DEL-UPG105-20260904-001</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>UPG-106</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>数字人体 V1（2D 全身部位图 + 健身挂点）</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
         <is>
           <t>✅ **大神评审通过 8.8/10（有条件）@2026-09-05 → v2.1 冻结稿已出**：`人体载体/数字人体_融入MOV架构_评审</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>UPG-107</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Memory OS 类型化 payload（Semantic 池子结构化演进）</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>裁决位]；DEL-UPG107-20260905-001[code=31640fc8/artifact=fc07ee63/manifest=</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>✅**C 完成 @2026-09-05**（feat/upg107 **31640fc8** 已 push origin[origin=gi</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>审验ok:true]/报告=程序员/交付报告/DELIVERY_UPG107_2026-09-05.md｜状态区投影锚+交付段详）</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>已合 main @31640fc8（ff-only；P 段数 56→56 无丢失；验收+审验全链闭环）</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>设计师/方案设计/04_记忆/Memory_OS_类型化payload_设计_v1_2026-09-05.md</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>DEL-UPG107-20260905-001</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>UPG-108</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>手机即服务器·官网用户面（扫码配对 + 手机内容投影上站）</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>UPG-109</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>第三方站 WebMCP 接入性扫描（agent 浏览器前置探测）</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5443,6 +5443,53 @@
         </is>
       </c>
       <c r="I106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UPG-110</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>官网容器面·批二 A 通道（MCP Streamable HTTP 活端点）</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>已派单（批二 A 通道，STD-UPG-110-v1 已冻结 99b78881）</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>方案完成待派单（P2）</t>
+          <t>❌ 已销单 @2026-09-05（用户拍板+设计师评估）</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>销单</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>方案完成待派单（P2）</t>
+          <t>❌ 已销单 @2026-09-05（用户拍板+设计师评估）</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>销单</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已合 main（655b148d ∈ main；审验实质面全绿+manifest 补档 ok:True 闭环）</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>方案完成待派单（ICP 硬阻塞注记：09-04 备案号已上页脚，阻塞或已解除待核实）</t>
+          <t>❌ 已销单 @2026-09-05（用户拍板——目标事实达成：备案+官网在线+容器面已部署）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>销单：域迁移目标已由演进达成，卡面流程未施工</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 已合 main @489398f6 + 已部署生产 @2026-09-05（双域 /tools+mov-ai-public 实证 sub</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>方案完成待派单（P3 小修批）</t>
+          <t>❌ 已销单 @2026-09-05（用户拍板+设计师评估）</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>销单</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>已交付</t>
+          <t>✅ C 完成 @2026-09-05（1df4a3e3，2 文件+401；生产已上线实证）</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 验收员复验通过 §P61（生产 curl 三连+同源对账逐字段）</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已合 main @eebbd57a（merge；§P61 落档随行[c3098eb9 本地支链 bdfa4f3a 一并带上]；生产端点设计师</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5490,6 +5490,53 @@
         </is>
       </c>
       <c r="I107" t="inlineStr">
+        <is>
+          <t>DEL-UPG110-20260905-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>UPG-111</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>契约测试死角扫尾（UPG-100 A3 结论 18 处——Appearance 族优先）</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5392,7 +5392,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/方案设计/工单方案/官网用户面_手机即服务器_设计_v1_2026-09-05.md</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/方案设计/工单方案/第三方站WebMCP扫描器_设计_v1_2026-09-05.md</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已认领</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已认领</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>已认领</t>
+          <t>已交付</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4152,7 +4152,8 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1（作废留档）
+→ **依据**：用户实测</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4991,17 +4992,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>📌 已派单（用户直接外派）</t>
+          <t>📌 已派单（用户直接外派）+ STD 追认冻结 @2026-09-05（简式）</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>✅ C 完成 @2026-09-05（kimi-cli，a63b7088——锚②升级 count/match；待验收）</t>
+          <t>✅ C 完成 @2026-09-05（kimi-cli，a63b7088——锚②升级 count/match）</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>📌 已立卡·待派 ⏳ @2026-09-04（UPG-96 审验发现项①转正：contains 组合锚对单点破坏免疫）｜ 待派单</t>
+          <t>✅ 复验通过 @2026-09-05（§P62 双变异亲杀+3 连跑零 flaky；达待合→审验员）</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5179,12 +5180,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 → ✅ **段①解锁 @2026-09-05**</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>设计 v3/v3.1 全量保留归本单；待 UPG-46 段①</t>
+          <t>📌 已派单·待认领 @2026-09-05（段① UPG-46 已合 main @7ccf0446 解锁；STD-UPG-104-v1 冻</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5199,12 +5200,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>合 main后拆派单）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>设计师/派单/UPG-104_工具联动段2_派单_2026-09-05.md</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5273,7 +5274,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5419,7 +5420,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📌 已派单·待认领 @2026-09-05（派单 `设计师/派单/UPG-109_第三方站WebMCP扫描器_派单_2026-09-05.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5508,22 +5509,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📌 立卡 @2026-09-05（P3——UPG-100 A3 死角扫尾转办）</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>已交付</t>
+          <t>✅ C 完成 @2026-09-05（e396fab3——18 处弱锚升级+3 代表变异亲杀）</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 复验通过 @2026-09-05（§P64 定向 16/0+9/0+双刀抽杀亲红；达待合→审验员）</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5180,7 +5180,8 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>P2 → ✅ **段①解锁 @2026-09-05**</t>
+          <t>P2 → ✅ **段①解锁 @2026-09-05**（UPG-46 已合 main @7ccf0446）→ 📌 **已派单·待认领 @2026-09-05**（设计师：派单 `设计师/派单/UPG-104_工具联动段2_派单_2026-09-05.md`——四件 A1-A4+红线+交付链；**STD-UPG-104-v1 已冻结** sha=e6d8a7f960dad4d12a60fa5b105898d694f908ec0fae11b5c6205b6755e2b5b5b5）
+→ 🔄 **认领+盘点完成 @2026-09-05</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5190,7 +5191,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已认领</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已认领</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P3 → ✅ **审验通过 @2026-09-05**</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>✅ 复验通过 @2026-09-05（§P64 定向 16/0+9/0+双刀抽杀亲红；达待合→审验员）</t>
+          <t>✅ 复验 §P64 + 审验 ✅通过 @2026-09-05（integrity_review=confirmed——STD 简式豁免成立/</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t xml:space="preserve">✅ 已合 main @baa71627（merge fada223b+L2-9 锚收口；终态 verify-hash HASH_OK；全量 </t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG111-20260905-001</t>
         </is>
       </c>
     </row>

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5478,12 +5478,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>✅ 验收员复验通过 §P61（生产 curl 三连+同源对账逐字段）</t>
+          <t>✅ 复验 §P61 + 终态复核 §P61-T 通过 @2026-09-05（合入实证+5/5 实物双端 sha+生产 200 同源——审验</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>已合 main @eebbd57a（merge；§P61 落档随行[c3098eb9 本地支链 bdfa4f3a 一并带上]；生产端点设计师</t>
+          <t>已合 main @eebbd57a + 终态复核闭环 @2026-09-05（§P61-T 全生命周期确认；P3 勘误 952225f1→b</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5191,7 +5191,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>已认领</t>
+          <t>已交付</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -4992,7 +4992,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>📌 已派单（用户直接外派）+ STD 追认冻结 @2026-09-05（简式）</t>
+          <t>📌 已派单（用户直接外派）+ STD 追认冻结 @2026-09-05（简式，sha=96c6bce1 会签已补）</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>✅ 复验通过 @2026-09-05（§P62 双变异亲杀+3 连跑零 flaky；达待合→审验员）</t>
+          <t>✅ 复验 §P62 + 审验✅ @2026-09-05（独立四态亲杀+A3 18 处表+STD 重算一致——integrity_review</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ 已合 main @2886821d（隔离全量 844/0/1；终态 verify-hash HASH_OK；P3×2 随批处置——man</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">

--- a/工单系统/工单表.xlsx
+++ b/工单系统/工单表.xlsx
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>已认领</t>
+          <t>阶段1 demo 交付：L1 22/22+全量862/0/1+变异5刀全红+信令线上全链curl闭环+8389双地址真机实证+部署mov-a</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEL-UPG-108-20260906-001</t>
         </is>
       </c>
     </row>
